--- a/HBX Commissioning Review.xlsx
+++ b/HBX Commissioning Review.xlsx
@@ -7,12 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="HBX Commissioning Review" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Lists" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Meeting Log" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Meeting Report" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lists &amp; Config" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="LIST_TOPIC">'Lists'!$B$6:$B$13</definedName>
-    <definedName name="LIST_SUBTOPIC">'Lists'!$C$6:$C$16</definedName>
+    <definedName name="LIST_SUBJECT">'Lists &amp; Config'!$B$6:$B$16</definedName>
+    <definedName name="LIST_SUBTOPIC">'Lists &amp; Config'!$C$6:$C$20</definedName>
+    <definedName name="LIST_OWNER">'Lists &amp; Config'!$D$6:$D$14</definedName>
+    <definedName name="LIST_STATUS">'Lists &amp; Config'!$E$6:$E$10</definedName>
+    <definedName name="LIST_PRIORITY">'Lists &amp; Config'!$F$6:$F$9</definedName>
+    <definedName name="LIST_MEETING_TYPE">'Lists &amp; Config'!$G$6:$G$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,14 +26,29 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="8">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd-mmm-yy"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00BFD3F2"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -69,8 +90,74 @@
       <color rgb="001155CC"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0044546A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B00020"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001E7B34"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C6500"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="005B7FB5"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0044546A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -84,7 +171,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="003B6EC4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F2F5FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0044546A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F9FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -114,30 +226,123 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00B00020"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FBE4E4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00B00020"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FBE4E4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="001E7B34"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E2F0E4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <i val="1"/>
+        <color rgb="006E6E6E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E8E8E8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -211,14 +416,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="HBX_Tracker" displayName="HBX_Tracker" ref="B6:F7" headerRowCount="1">
-  <autoFilter ref="B6:F7"/>
-  <tableColumns count="5">
-    <tableColumn id="2" name="Topic"/>
-    <tableColumn id="3" name="Sub-Topic"/>
-    <tableColumn id="4" name="Owner"/>
-    <tableColumn id="5" name="Notes"/>
-    <tableColumn id="6" name="Action"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Meeting_Log" displayName="Meeting_Log" ref="B7:O10" headerRowCount="1">
+  <autoFilter ref="B7:O10"/>
+  <tableColumns count="14">
+    <tableColumn id="2" name="Meeting ID"/>
+    <tableColumn id="3" name="Meeting Date"/>
+    <tableColumn id="4" name="Meeting Type"/>
+    <tableColumn id="5" name="Subject"/>
+    <tableColumn id="6" name="Sub-topic"/>
+    <tableColumn id="7" name="Owner"/>
+    <tableColumn id="8" name="Discussion / Notes"/>
+    <tableColumn id="9" name="Agreed Action"/>
+    <tableColumn id="10" name="Due Date"/>
+    <tableColumn id="11" name="Status"/>
+    <tableColumn id="12" name="Priority"/>
+    <tableColumn id="13" name="Follow-up / Update"/>
+    <tableColumn id="14" name="Topic Key"/>
+    <tableColumn id="15" name="Overdue?"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -513,93 +727,1029 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F9"/>
+  <dimension ref="B1:R48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Meeting Log</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Meeting Report</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Lists &amp; Config</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>HBX Commissioning Review</t>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>HBX Commissioning Review - Overview</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>One row per subject discussed. Pick Topic/Sub-Topic from the dropdown, note who owns it, take notes as you go, and record the action agreed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Topic</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Sub-Topic</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Open this before a meeting: pick the meeting date below and everything updates automatically from Meeting Log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Current Meeting Date:</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7">
+        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5)))</f>
+        <v/>
+      </c>
+      <c r="C8" s="8" t="n"/>
+      <c r="E8" s="7">
+        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"))</f>
+        <v/>
+      </c>
+      <c r="F8" s="8" t="n"/>
+      <c r="H8" s="9">
+        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Overdue?]="Yes"))</f>
+        <v/>
+      </c>
+      <c r="I8" s="8" t="n"/>
+      <c r="K8" s="10">
+        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]="Closed"))</f>
+        <v/>
+      </c>
+      <c r="L8" s="8" t="n"/>
+      <c r="N8" s="11">
+        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"))</f>
+        <v/>
+      </c>
+      <c r="O8" s="8" t="n"/>
+      <c r="Q8" s="12">
+        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0))</f>
+        <v/>
+      </c>
+      <c r="R8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="8" t="n"/>
+      <c r="K9" s="8" t="n"/>
+      <c r="L9" s="8" t="n"/>
+      <c r="N9" s="8" t="n"/>
+      <c r="O9" s="8" t="n"/>
+      <c r="Q9" s="8" t="n"/>
+      <c r="R9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="8" t="n"/>
+      <c r="Q10" s="8" t="n"/>
+      <c r="R10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Total Subjects</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Open Actions</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>Overdue Actions</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>Carried Over from Previous Meeting</t>
+        </is>
+      </c>
+      <c r="Q11" s="13" t="inlineStr">
+        <is>
+          <t>New Topics This Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>1. FOLLOW-UP FROM PREVIOUS MEETING</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="14" t="n"/>
+      <c r="H13" s="14" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Sub-topic</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Previous Discussion</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>Previous Action</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>Previous Due Date</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>Previous Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="B15" s="16">
+        <f t="array" ref="B15">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="C15" s="16">
+        <f t="array" ref="C15">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="16">
+        <f t="array" ref="D15">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="E15" s="16">
+        <f t="array" ref="E15">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="16">
+        <f t="array" ref="F15">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="17">
+        <f t="array" ref="G15">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="16">
+        <f t="array" ref="H15">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="B16" s="18">
+        <f t="array" ref="B16">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="C16" s="18">
+        <f t="array" ref="C16">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="18">
+        <f t="array" ref="D16">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="18">
+        <f t="array" ref="E16">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="18">
+        <f t="array" ref="F16">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="19">
+        <f t="array" ref="G16">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="18">
+        <f t="array" ref="H16">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="16">
+        <f t="array" ref="B17">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="C17" s="16">
+        <f t="array" ref="C17">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="16">
+        <f t="array" ref="D17">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="16">
+        <f t="array" ref="E17">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="16">
+        <f t="array" ref="F17">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="17">
+        <f t="array" ref="G17">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="16">
+        <f t="array" ref="H17">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="B18" s="18">
+        <f t="array" ref="B18">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="C18" s="18">
+        <f t="array" ref="C18">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="D18" s="18">
+        <f t="array" ref="D18">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="18">
+        <f t="array" ref="E18">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="18">
+        <f t="array" ref="F18">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="19">
+        <f t="array" ref="G18">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="18">
+        <f t="array" ref="H18">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="16">
+        <f t="array" ref="B19">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="C19" s="16">
+        <f t="array" ref="C19">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="16">
+        <f t="array" ref="D19">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="16">
+        <f t="array" ref="E19">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="16">
+        <f t="array" ref="F19">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="17">
+        <f t="array" ref="G19">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="16">
+        <f t="array" ref="H19">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="B20" s="18">
+        <f t="array" ref="B20">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="C20" s="18">
+        <f t="array" ref="C20">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="18">
+        <f t="array" ref="D20">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="18">
+        <f t="array" ref="E20">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="18">
+        <f t="array" ref="F20">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="19">
+        <f t="array" ref="G20">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="18">
+        <f t="array" ref="H20">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="B21" s="16">
+        <f t="array" ref="B21">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="16">
+        <f t="array" ref="C21">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="16">
+        <f t="array" ref="D21">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="16">
+        <f t="array" ref="E21">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="16">
+        <f t="array" ref="F21">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="17">
+        <f t="array" ref="G21">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="16">
+        <f t="array" ref="H21">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="B22" s="18">
+        <f t="array" ref="B22">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="C22" s="18">
+        <f t="array" ref="C22">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="18">
+        <f t="array" ref="D22">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="18">
+        <f t="array" ref="E22">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="18">
+        <f t="array" ref="F22">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="19">
+        <f t="array" ref="G22">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="18">
+        <f t="array" ref="H22">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>2. NEW TOPICS</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Sub-topic</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Discussion</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="50" customHeight="1">
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Commissioning Documentation</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Execution Plan - Scope Gaps</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Legend: Blue = fill in yourself | New row: type directly below the table and Excel extends it automatically</t>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>Due Date</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="B26" s="16">
+        <f t="array" ref="B26">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="16">
+        <f t="array" ref="C26">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="16">
+        <f t="array" ref="D26">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="16">
+        <f t="array" ref="E26">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="16">
+        <f t="array" ref="F26">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="17">
+        <f t="array" ref="G26">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="16">
+        <f t="array" ref="H26">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="B27" s="18">
+        <f t="array" ref="B27">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="C27" s="18">
+        <f t="array" ref="C27">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="18">
+        <f t="array" ref="D27">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="18">
+        <f t="array" ref="E27">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="18">
+        <f t="array" ref="F27">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="19">
+        <f t="array" ref="G27">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="18">
+        <f t="array" ref="H27">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="B28" s="16">
+        <f t="array" ref="B28">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="16">
+        <f t="array" ref="C28">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="16">
+        <f t="array" ref="D28">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="16">
+        <f t="array" ref="E28">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="16">
+        <f t="array" ref="F28">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="17">
+        <f t="array" ref="G28">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="16">
+        <f t="array" ref="H28">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="18">
+        <f t="array" ref="B29">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="18">
+        <f t="array" ref="C29">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="18">
+        <f t="array" ref="D29">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="18">
+        <f t="array" ref="E29">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="18">
+        <f t="array" ref="F29">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="19">
+        <f t="array" ref="G29">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="18">
+        <f t="array" ref="H29">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="B30" s="16">
+        <f t="array" ref="B30">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="16">
+        <f t="array" ref="C30">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="16">
+        <f t="array" ref="D30">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="16">
+        <f t="array" ref="E30">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="16">
+        <f t="array" ref="F30">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="17">
+        <f t="array" ref="G30">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="16">
+        <f t="array" ref="H30">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="B31" s="18">
+        <f t="array" ref="B31">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="C31" s="18">
+        <f t="array" ref="C31">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="18">
+        <f t="array" ref="D31">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="18">
+        <f t="array" ref="E31">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="18">
+        <f t="array" ref="F31">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="19">
+        <f t="array" ref="G31">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="18">
+        <f t="array" ref="H31">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>Add new topics directly in Meeting Log with today's date - they will appear above automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>3. ACTIONS TO FOLLOW (all open actions, latest status)</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="14" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>Due Date</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="B37" s="16">
+        <f t="array" ref="B37">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="16">
+        <f t="array" ref="C37">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="16">
+        <f t="array" ref="D37">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="17">
+        <f t="array" ref="E37">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="16">
+        <f t="array" ref="F37">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="16">
+        <f t="array" ref="G37">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="B38" s="18">
+        <f t="array" ref="B38">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="18">
+        <f t="array" ref="C38">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="18">
+        <f t="array" ref="D38">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="19">
+        <f t="array" ref="E38">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="18">
+        <f t="array" ref="F38">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="18">
+        <f t="array" ref="G38">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="B39" s="16">
+        <f t="array" ref="B39">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="C39" s="16">
+        <f t="array" ref="C39">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="16">
+        <f t="array" ref="D39">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="17">
+        <f t="array" ref="E39">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="16">
+        <f t="array" ref="F39">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="16">
+        <f t="array" ref="G39">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="B40" s="18">
+        <f t="array" ref="B40">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="C40" s="18">
+        <f t="array" ref="C40">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="D40" s="18">
+        <f t="array" ref="D40">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="19">
+        <f t="array" ref="E40">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="18">
+        <f t="array" ref="F40">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="18">
+        <f t="array" ref="G40">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="B41" s="16">
+        <f t="array" ref="B41">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="16">
+        <f t="array" ref="C41">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="16">
+        <f t="array" ref="D41">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="17">
+        <f t="array" ref="E41">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="16">
+        <f t="array" ref="F41">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="16">
+        <f t="array" ref="G41">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="B42" s="18">
+        <f t="array" ref="B42">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="C42" s="18">
+        <f t="array" ref="C42">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="D42" s="18">
+        <f t="array" ref="D42">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="19">
+        <f t="array" ref="E42">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="18">
+        <f t="array" ref="F42">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="18">
+        <f t="array" ref="G42">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="B43" s="16">
+        <f t="array" ref="B43">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="16">
+        <f t="array" ref="C43">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="16">
+        <f t="array" ref="D43">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="17">
+        <f t="array" ref="E43">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="16">
+        <f t="array" ref="F43">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="16">
+        <f t="array" ref="G43">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="B44" s="18">
+        <f t="array" ref="B44">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="18">
+        <f t="array" ref="C44">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="18">
+        <f t="array" ref="D44">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="19">
+        <f t="array" ref="E44">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="18">
+        <f t="array" ref="F44">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="18">
+        <f t="array" ref="G44">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="B45" s="16">
+        <f t="array" ref="B45">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="16">
+        <f t="array" ref="C45">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <v/>
+      </c>
+      <c r="D45" s="16">
+        <f t="array" ref="D45">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="17">
+        <f t="array" ref="E45">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="16">
+        <f t="array" ref="F45">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="16">
+        <f t="array" ref="G45">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="B46" s="18">
+        <f t="array" ref="B46">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <v/>
+      </c>
+      <c r="C46" s="18">
+        <f t="array" ref="C46">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="18">
+        <f t="array" ref="D46">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="19">
+        <f t="array" ref="E46">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="18">
+        <f t="array" ref="F46">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="18">
+        <f t="array" ref="G46">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>Legend: Blue = fill in yourself | Black = automatic, do not overtype | Grey columns = automation helpers, leave untouched | New row: type directly below the table and Excel extends it automatically</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=LIST_TOPIC</formula1>
-    </dataValidation>
-    <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=LIST_SUBTOPIC</formula1>
-    </dataValidation>
-  </dataValidations>
+  <mergeCells count="12">
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="N8:O10"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="K8:L10"/>
+    <mergeCell ref="H8:I10"/>
+    <mergeCell ref="Q8:R10"/>
+    <mergeCell ref="E8:F10"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G37:G46">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"Critical"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -609,165 +1759,1741 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C18"/>
+  <dimension ref="B1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Meeting Log</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Meeting Report</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Lists &amp; Config</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Lists</t>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Meeting Log</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Dropdown options for the tracker. Add or remove values here - every dropdown updates automatically.</t>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>The single database. One row = one subject discussed at one meeting. Continuity across meetings is found automatically via Subject + Sub-topic - just add a new row with the same Subject/Sub-topic to continue a topic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>Meeting ID</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>Meeting Date</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>Meeting Type</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>Sub-topic</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>Discussion / Notes</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>Agreed Action</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>Due Date</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="M7" s="21" t="inlineStr">
+        <is>
+          <t>Follow-up / Update</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t>Topic Key</t>
+        </is>
+      </c>
+      <c r="O7" s="21" t="inlineStr">
+        <is>
+          <t>Overdue?</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1">
+      <c r="B8" s="16">
+        <f>IF($E8="","","M"&amp;TEXT(ROW()-7,"000"))</f>
+        <v/>
+      </c>
+      <c r="C8" s="22" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>Documents missing for the commissioning dossier.</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>Engineering to provide the missing documents.</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="n">
+        <v>46280</v>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M8" s="23" t="inlineStr"/>
+      <c r="N8" s="24">
+        <f>IF($E8="","",$E8&amp;"|"&amp;$F8)</f>
+        <v/>
+      </c>
+      <c r="O8" s="16">
+        <f>IF($E8="","",IF(AND($K8&lt;&gt;"Closed",$K8&lt;&gt;"Cancelled",$J8&lt;&gt;"",$J8&lt;TODAY()),"Yes","No"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="B9" s="16">
+        <f>IF($E9="","","M"&amp;TEXT(ROW()-7,"000"))</f>
+        <v/>
+      </c>
+      <c r="C9" s="22" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>Engineering confirmed the documents are being finalised.</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>Engineering to issue the documents.</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="n">
+        <v>46310</v>
+      </c>
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="L9" s="23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M9" s="23" t="inlineStr">
+        <is>
+          <t>Continued from the 01-Sep meeting - still outstanding.</t>
+        </is>
+      </c>
+      <c r="N9" s="24">
+        <f>IF($E9="","",$E9&amp;"|"&amp;$F9)</f>
+        <v/>
+      </c>
+      <c r="O9" s="16">
+        <f>IF($E9="","",IF(AND($K9&lt;&gt;"Closed",$K9&lt;&gt;"Cancelled",$J9&lt;&gt;"",$J9&lt;TODAY()),"Yes","No"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="B10" s="16">
+        <f>IF($E10="","","M"&amp;TEXT(ROW()-7,"000"))</f>
+        <v/>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>Testing / Results</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>Commissioning</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>First functional test results reviewed.</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>Commissioning to issue the test report.</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="n">
+        <v>46315</v>
+      </c>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" s="23" t="inlineStr"/>
+      <c r="N10" s="24">
+        <f>IF($E10="","",$E10&amp;"|"&amp;$F10)</f>
+        <v/>
+      </c>
+      <c r="O10" s="16">
+        <f>IF($E10="","",IF(AND($K10&lt;&gt;"Closed",$K10&lt;&gt;"Cancelled",$J10&lt;&gt;"",$J10&lt;TODAY()),"Yes","No"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>Legend: Blue = fill in yourself | Black = automatic, do not overtype | Grey columns = automation helpers, leave untouched | New row: type directly below the table and Excel extends it automatically</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B8:O10">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>AND($K8&lt;&gt;"Closed",$O8="Yes")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>$K8="Closed"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="3">
+      <formula>OR($K8="On Hold",$K8="Cancelled")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="6">
+    <dataValidation sqref="D8:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=LIST_MEETING_TYPE</formula1>
+    </dataValidation>
+    <dataValidation sqref="E8:E10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=LIST_SUBJECT</formula1>
+    </dataValidation>
+    <dataValidation sqref="F8:F10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=LIST_SUBTOPIC</formula1>
+    </dataValidation>
+    <dataValidation sqref="G8:G10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=LIST_OWNER</formula1>
+    </dataValidation>
+    <dataValidation sqref="K8:K10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=LIST_STATUS</formula1>
+    </dataValidation>
+    <dataValidation sqref="L8:L10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=LIST_PRIORITY</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:H49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.5" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Meeting Log</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Meeting Report</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Lists &amp; Config</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Meeting Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Mirrors the meeting date selected on Overview - change it there to generate a report for a different meeting. Short enough to copy straight into minutes or an email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Meeting Date:</t>
+        </is>
+      </c>
+      <c r="C5" s="25">
+        <f>'Overview'!$C$5</f>
+        <v/>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Meeting Type:</t>
+        </is>
+      </c>
+      <c r="F5" s="26">
+        <f>IFERROR(INDEX(Meeting_Log[Meeting Type],MATCH($C$5,Meeting_Log[Meeting Date],0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>1. FOLLOW-UP FROM PREVIOUS MEETING</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="14" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Sub-topic</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Previous Discussion</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Previous Action</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>Previous Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="B9" s="16">
+        <f t="array" ref="B9">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="C9" s="16">
+        <f t="array" ref="C9">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="16">
+        <f t="array" ref="D9">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="16">
+        <f t="array" ref="E9">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="16">
+        <f t="array" ref="F9">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="16">
+        <f t="array" ref="G9">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="18">
+        <f t="array" ref="B10">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="18">
+        <f t="array" ref="C10">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="18">
+        <f t="array" ref="D10">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="18">
+        <f t="array" ref="E10">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="18">
+        <f t="array" ref="F10">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="18">
+        <f t="array" ref="G10">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="B11" s="16">
+        <f t="array" ref="B11">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="C11" s="16">
+        <f t="array" ref="C11">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="16">
+        <f t="array" ref="D11">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="16">
+        <f t="array" ref="E11">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="16">
+        <f t="array" ref="F11">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="16">
+        <f t="array" ref="G11">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="B12" s="18">
+        <f t="array" ref="B12">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="18">
+        <f t="array" ref="C12">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="18">
+        <f t="array" ref="D12">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="18">
+        <f t="array" ref="E12">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="18">
+        <f t="array" ref="F12">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="18">
+        <f t="array" ref="G12">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="B13" s="16">
+        <f t="array" ref="B13">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="C13" s="16">
+        <f t="array" ref="C13">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="D13" s="16">
+        <f t="array" ref="D13">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="E13" s="16">
+        <f t="array" ref="E13">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="16">
+        <f t="array" ref="F13">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="16">
+        <f t="array" ref="G13">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="B14" s="18">
+        <f t="array" ref="B14">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="18">
+        <f t="array" ref="C14">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="18">
+        <f t="array" ref="D14">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="18">
+        <f t="array" ref="E14">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="18">
+        <f t="array" ref="F14">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="18">
+        <f t="array" ref="G14">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="B15" s="16">
+        <f t="array" ref="B15">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="C15" s="16">
+        <f t="array" ref="C15">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="16">
+        <f t="array" ref="D15">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="E15" s="16">
+        <f t="array" ref="E15">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="16">
+        <f t="array" ref="F15">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="16">
+        <f t="array" ref="G15">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="B16" s="18">
+        <f t="array" ref="B16">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="C16" s="18">
+        <f t="array" ref="C16">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="18">
+        <f t="array" ref="D16">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="18">
+        <f t="array" ref="E16">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="18">
+        <f t="array" ref="F16">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="18">
+        <f t="array" ref="G16">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>2. NEW TOPICS</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Sub-topic</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Discussion / Notes</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>Agreed Action</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>Due Date</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="B20" s="16">
+        <f t="array" ref="B20">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="C20" s="16">
+        <f t="array" ref="C20">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="16">
+        <f t="array" ref="D20">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="16">
+        <f t="array" ref="E20">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="16">
+        <f t="array" ref="F20">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="17">
+        <f t="array" ref="G20">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="16">
+        <f t="array" ref="H20">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="B21" s="18">
+        <f t="array" ref="B21">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="18">
+        <f t="array" ref="C21">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="18">
+        <f t="array" ref="D21">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="18">
+        <f t="array" ref="E21">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="18">
+        <f t="array" ref="F21">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="19">
+        <f t="array" ref="G21">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="18">
+        <f t="array" ref="H21">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="B22" s="16">
+        <f t="array" ref="B22">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="C22" s="16">
+        <f t="array" ref="C22">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="16">
+        <f t="array" ref="D22">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="16">
+        <f t="array" ref="E22">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="16">
+        <f t="array" ref="F22">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="17">
+        <f t="array" ref="G22">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="16">
+        <f t="array" ref="H22">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="B23" s="18">
+        <f t="array" ref="B23">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="18">
+        <f t="array" ref="C23">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="18">
+        <f t="array" ref="D23">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="18">
+        <f t="array" ref="E23">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="18">
+        <f t="array" ref="F23">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="19">
+        <f t="array" ref="G23">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="18">
+        <f t="array" ref="H23">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="B24" s="16">
+        <f t="array" ref="B24">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="C24" s="16">
+        <f t="array" ref="C24">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="D24" s="16">
+        <f t="array" ref="D24">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="16">
+        <f t="array" ref="E24">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="16">
+        <f t="array" ref="F24">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="17">
+        <f t="array" ref="G24">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="16">
+        <f t="array" ref="H24">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="B25" s="18">
+        <f t="array" ref="B25">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="C25" s="18">
+        <f t="array" ref="C25">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="D25" s="18">
+        <f t="array" ref="D25">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="18">
+        <f t="array" ref="E25">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="18">
+        <f t="array" ref="F25">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="19">
+        <f t="array" ref="G25">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="18">
+        <f t="array" ref="H25">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>3. ACTION SUMMARY</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="14" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>Due Date</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="16">
+        <f t="array" ref="B29">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="16">
+        <f t="array" ref="C29">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="17">
+        <f t="array" ref="D29">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="16">
+        <f t="array" ref="E29">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="16">
+        <f t="array" ref="F29">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="B30" s="18">
+        <f t="array" ref="B30">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="18">
+        <f t="array" ref="C30">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="19">
+        <f t="array" ref="D30">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="18">
+        <f t="array" ref="E30">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="18">
+        <f t="array" ref="F30">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="B31" s="16">
+        <f t="array" ref="B31">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="C31" s="16">
+        <f t="array" ref="C31">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="17">
+        <f t="array" ref="D31">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="16">
+        <f t="array" ref="E31">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="16">
+        <f t="array" ref="F31">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="B32" s="18">
+        <f t="array" ref="B32">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="18">
+        <f t="array" ref="C32">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="19">
+        <f t="array" ref="D32">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="18">
+        <f t="array" ref="E32">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="18">
+        <f t="array" ref="F32">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="B33" s="16">
+        <f t="array" ref="B33">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="16">
+        <f t="array" ref="C33">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="17">
+        <f t="array" ref="D33">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="16">
+        <f t="array" ref="E33">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="16">
+        <f t="array" ref="F33">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="B34" s="18">
+        <f t="array" ref="B34">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="18">
+        <f t="array" ref="C34">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="19">
+        <f t="array" ref="D34">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="18">
+        <f t="array" ref="E34">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="18">
+        <f t="array" ref="F34">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="B35" s="16">
+        <f t="array" ref="B35">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="16">
+        <f t="array" ref="C35">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="17">
+        <f t="array" ref="D35">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="16">
+        <f t="array" ref="E35">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="16">
+        <f t="array" ref="F35">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="B36" s="18">
+        <f t="array" ref="B36">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="18">
+        <f t="array" ref="C36">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="19">
+        <f t="array" ref="D36">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="18">
+        <f t="array" ref="E36">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="18">
+        <f t="array" ref="F36">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>4. OPEN / OVERDUE ACTIONS</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="14" t="n"/>
+      <c r="F38" s="14" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>Due Date</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="B40" s="16">
+        <f t="array" ref="B40">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="C40" s="16">
+        <f t="array" ref="C40">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="D40" s="16">
+        <f t="array" ref="D40">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="17">
+        <f t="array" ref="E40">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="16">
+        <f t="array" ref="F40">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="B41" s="18">
+        <f t="array" ref="B41">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="18">
+        <f t="array" ref="C41">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="18">
+        <f t="array" ref="D41">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="19">
+        <f t="array" ref="E41">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="18">
+        <f t="array" ref="F41">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="B42" s="16">
+        <f t="array" ref="B42">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="C42" s="16">
+        <f t="array" ref="C42">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="D42" s="16">
+        <f t="array" ref="D42">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="17">
+        <f t="array" ref="E42">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="16">
+        <f t="array" ref="F42">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="B43" s="18">
+        <f t="array" ref="B43">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="18">
+        <f t="array" ref="C43">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="18">
+        <f t="array" ref="D43">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="19">
+        <f t="array" ref="E43">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="18">
+        <f t="array" ref="F43">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="B44" s="16">
+        <f t="array" ref="B44">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="16">
+        <f t="array" ref="C44">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="16">
+        <f t="array" ref="D44">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17">
+        <f t="array" ref="E44">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="16">
+        <f t="array" ref="F44">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="B45" s="18">
+        <f t="array" ref="B45">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="18">
+        <f t="array" ref="C45">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="D45" s="18">
+        <f t="array" ref="D45">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="19">
+        <f t="array" ref="E45">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="18">
+        <f t="array" ref="F45">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="B46" s="16">
+        <f t="array" ref="B46">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="C46" s="16">
+        <f t="array" ref="C46">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="16">
+        <f t="array" ref="D46">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="17">
+        <f t="array" ref="E46">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="16">
+        <f t="array" ref="F46">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="B47" s="18">
+        <f t="array" ref="B47">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="C47" s="18">
+        <f t="array" ref="C47">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="D47" s="18">
+        <f t="array" ref="D47">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="19">
+        <f t="array" ref="E47">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="18">
+        <f t="array" ref="F47">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>Legend: Blue = fill in yourself | Black = automatic, do not overtype | Grey columns = automation helpers, leave untouched | New row: type directly below the table and Excel extends it automatically</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Meeting Log</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Meeting Report</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Lists &amp; Config</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Lists &amp; Config</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Dropdown values used on Meeting Log. Add or remove values here - every dropdown updates automatically. No formulas here need to change.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Topic</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Sub-Topic</t>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Sub-topic</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G5" s="27" t="inlineStr">
+        <is>
+          <t>Meeting Type</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Commissioning Documentation</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Execution Plan - Scope Gaps</t>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Commissioning Planning</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Planning</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>Commissioning</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Reviews and Surveillance</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Other Documentation</t>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>Site / Field Activities</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>Progress</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F7" s="29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G7" s="29" t="inlineStr">
+        <is>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>ECS / System Codes</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Partitioning Strategy, EESRs, ITPs</t>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>Preparation</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>Ad hoc</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>Testing / Results</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E9" s="29" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="F9" s="29" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Interfaces</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>HSE</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>Punch List</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>Planning</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>Document Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>NCR / Quality</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>Project Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Resources / Manpower</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>Design / Engineering</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>SONIMs</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Safe System of Work</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>ECS codes for building assets</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Interfaces</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Commissioning Start Dates / Sequence</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Quality Audit</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Journey / Fishbone</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="8" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>Interface</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>SSOW Approval</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Interface Schedule / Execution Plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Pre-Commissioning Audit</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>Resource</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="28" t="inlineStr">
+        <is>
+          <t>Risk / Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Legend: Blue = fill in yourself | New row: type directly below the table and Excel extends it automatically</t>
+    <row r="22">
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Legend: Blue = fill in yourself | Black = automatic, do not overtype | Grey columns = automation helpers, leave untouched | New row: type directly below the table and Excel extends it automatically</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/HBX Commissioning Review.xlsx
+++ b/HBX Commissioning Review.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd-mmm-yy"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -141,6 +141,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
@@ -226,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -257,8 +263,18 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -274,18 +290,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -416,7 +423,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Meeting_Log" displayName="Meeting_Log" ref="B7:O10" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Attendees_Log" displayName="Attendees_Log" ref="B14:C15" headerRowCount="1">
+  <autoFilter ref="B14:C15"/>
+  <tableColumns count="2">
+    <tableColumn id="2" name="Meeting Date"/>
+    <tableColumn id="3" name="Attendees"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Meeting_Log" displayName="Meeting_Log" ref="B7:O10" headerRowCount="1">
   <autoFilter ref="B7:O10"/>
   <tableColumns count="14">
     <tableColumn id="2" name="Meeting ID"/>
@@ -727,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:R48"/>
+  <dimension ref="B1:R52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -885,839 +903,868 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1">
+    <row r="13">
       <c r="B13" s="14" t="inlineStr">
         <is>
+          <t>Attendees</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Meeting Date</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Attendees</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="16" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Person A, Person B, Contractor A representative</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="18" t="inlineStr">
+        <is>
           <t>1. FOLLOW-UP FROM PREVIOUS MEETING</t>
         </is>
       </c>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="14" t="n"/>
-      <c r="E13" s="14" t="n"/>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
-      <c r="H13" s="14" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="15" t="inlineStr">
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>Sub-topic</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>Previous Discussion</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>Previous Action</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="G18" s="19" t="inlineStr">
         <is>
           <t>Previous Due Date</t>
         </is>
       </c>
-      <c r="H14" s="15" t="inlineStr">
+      <c r="H18" s="19" t="inlineStr">
         <is>
           <t>Previous Status</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="B15" s="16">
-        <f t="array" ref="B15">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="C15" s="16">
-        <f t="array" ref="C15">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="16">
-        <f t="array" ref="D15">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="E15" s="16">
-        <f t="array" ref="E15">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="F15" s="16">
-        <f t="array" ref="F15">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="G15" s="17">
-        <f t="array" ref="G15">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="16">
-        <f t="array" ref="H15">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="B16" s="18">
-        <f t="array" ref="B16">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="C16" s="18">
-        <f t="array" ref="C16">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="18">
-        <f t="array" ref="D16">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="E16" s="18">
-        <f t="array" ref="E16">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="F16" s="18">
-        <f t="array" ref="F16">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="19">
-        <f t="array" ref="G16">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="18">
-        <f t="array" ref="H16">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="B17" s="16">
-        <f t="array" ref="B17">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="C17" s="16">
-        <f t="array" ref="C17">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="D17" s="16">
-        <f t="array" ref="D17">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="E17" s="16">
-        <f t="array" ref="E17">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="F17" s="16">
-        <f t="array" ref="F17">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="17">
-        <f t="array" ref="G17">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="16">
-        <f t="array" ref="H17">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="B18" s="18">
-        <f t="array" ref="B18">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="C18" s="18">
-        <f t="array" ref="C18">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="18">
-        <f t="array" ref="D18">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="E18" s="18">
-        <f t="array" ref="E18">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="18">
-        <f t="array" ref="F18">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="G18" s="19">
-        <f t="array" ref="G18">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="18">
-        <f t="array" ref="H18">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-    </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="B19" s="16">
-        <f t="array" ref="B19">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="C19" s="16">
-        <f t="array" ref="C19">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="D19" s="16">
-        <f t="array" ref="D19">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="E19" s="16">
-        <f t="array" ref="E19">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="F19" s="16">
-        <f t="array" ref="F19">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="G19" s="17">
-        <f t="array" ref="G19">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="16">
-        <f t="array" ref="H19">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+      <c r="B19" s="20">
+        <f t="array" ref="B19">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="C19" s="20">
+        <f t="array" ref="C19">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="20">
+        <f t="array" ref="D19">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="20">
+        <f t="array" ref="E19">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="20">
+        <f t="array" ref="F19">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="21">
+        <f t="array" ref="G19">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="20">
+        <f t="array" ref="H19">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="B20" s="18">
-        <f t="array" ref="B20">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="C20" s="18">
-        <f t="array" ref="C20">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="D20" s="18">
-        <f t="array" ref="D20">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="E20" s="18">
-        <f t="array" ref="E20">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="F20" s="18">
-        <f t="array" ref="F20">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="G20" s="19">
-        <f t="array" ref="G20">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="18">
-        <f t="array" ref="H20">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+      <c r="B20" s="22">
+        <f t="array" ref="B20">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="C20" s="22">
+        <f t="array" ref="C20">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="22">
+        <f t="array" ref="D20">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="22">
+        <f t="array" ref="E20">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="22">
+        <f t="array" ref="F20">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="23">
+        <f t="array" ref="G20">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="22">
+        <f t="array" ref="H20">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="B21" s="16">
-        <f t="array" ref="B21">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="C21" s="16">
-        <f t="array" ref="C21">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="D21" s="16">
-        <f t="array" ref="D21">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="E21" s="16">
-        <f t="array" ref="E21">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="F21" s="16">
-        <f t="array" ref="F21">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="G21" s="17">
-        <f t="array" ref="G21">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="16">
-        <f t="array" ref="H21">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+      <c r="B21" s="20">
+        <f t="array" ref="B21">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="20">
+        <f t="array" ref="C21">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="20">
+        <f t="array" ref="D21">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="20">
+        <f t="array" ref="E21">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="20">
+        <f t="array" ref="F21">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="21">
+        <f t="array" ref="G21">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="20">
+        <f t="array" ref="H21">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="B22" s="18">
-        <f t="array" ref="B22">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="C22" s="18">
-        <f t="array" ref="C22">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="D22" s="18">
-        <f t="array" ref="D22">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="E22" s="18">
-        <f t="array" ref="E22">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="F22" s="18">
-        <f t="array" ref="F22">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="G22" s="19">
-        <f t="array" ref="G22">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="18">
-        <f t="array" ref="H22">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B22" s="22">
+        <f t="array" ref="B22">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="C22" s="22">
+        <f t="array" ref="C22">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="22">
+        <f t="array" ref="D22">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="22">
+        <f t="array" ref="E22">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="22">
+        <f t="array" ref="F22">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="23">
+        <f t="array" ref="G22">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="22">
+        <f t="array" ref="H22">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="B23" s="20">
+        <f t="array" ref="B23">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="20">
+        <f t="array" ref="C23">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="20">
+        <f t="array" ref="D23">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="20">
+        <f t="array" ref="E23">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="20">
+        <f t="array" ref="F23">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="21">
+        <f t="array" ref="G23">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="20">
+        <f t="array" ref="H23">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="B24" s="22">
+        <f t="array" ref="B24">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="C24" s="22">
+        <f t="array" ref="C24">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="D24" s="22">
+        <f t="array" ref="D24">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="22">
+        <f t="array" ref="E24">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="22">
+        <f t="array" ref="F24">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="23">
+        <f t="array" ref="G24">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="22">
+        <f t="array" ref="H24">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="B25" s="20">
+        <f t="array" ref="B25">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="C25" s="20">
+        <f t="array" ref="C25">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="D25" s="20">
+        <f t="array" ref="D25">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="20">
+        <f t="array" ref="E25">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="20">
+        <f t="array" ref="F25">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="21">
+        <f t="array" ref="G25">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="20">
+        <f t="array" ref="H25">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="B26" s="22">
+        <f t="array" ref="B26">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="22">
+        <f t="array" ref="C26">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="22">
+        <f t="array" ref="D26">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="22">
+        <f t="array" ref="E26">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="22">
+        <f t="array" ref="F26">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="23">
+        <f t="array" ref="G26">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="22">
+        <f t="array" ref="H26">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>2. NEW TOPICS</t>
         </is>
       </c>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="14" t="n"/>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="14" t="n"/>
-      <c r="H24" s="14" t="n"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="15" t="inlineStr">
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="18" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>Sub-topic</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Discussion</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E29" s="19" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="F25" s="15" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="G25" s="15" t="inlineStr">
+      <c r="G29" s="19" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="H25" s="15" t="inlineStr">
+      <c r="H29" s="19" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="26" customHeight="1">
-      <c r="B26" s="16">
-        <f t="array" ref="B26">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="C26" s="16">
-        <f t="array" ref="C26">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="D26" s="16">
-        <f t="array" ref="D26">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="E26" s="16">
-        <f t="array" ref="E26">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="F26" s="16">
-        <f t="array" ref="F26">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="17">
-        <f t="array" ref="G26">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="16">
-        <f t="array" ref="H26">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="B27" s="18">
-        <f t="array" ref="B27">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="C27" s="18">
-        <f t="array" ref="C27">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="D27" s="18">
-        <f t="array" ref="D27">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="E27" s="18">
-        <f t="array" ref="E27">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="18">
-        <f t="array" ref="F27">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="19">
-        <f t="array" ref="G27">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="18">
-        <f t="array" ref="H27">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="B28" s="16">
-        <f t="array" ref="B28">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="C28" s="16">
-        <f t="array" ref="C28">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="D28" s="16">
-        <f t="array" ref="D28">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="E28" s="16">
-        <f t="array" ref="E28">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="16">
-        <f t="array" ref="F28">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="17">
-        <f t="array" ref="G28">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="16">
-        <f t="array" ref="H28">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="B29" s="18">
-        <f t="array" ref="B29">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="C29" s="18">
-        <f t="array" ref="C29">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="D29" s="18">
-        <f t="array" ref="D29">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="E29" s="18">
-        <f t="array" ref="E29">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="18">
-        <f t="array" ref="F29">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="19">
-        <f t="array" ref="G29">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="18">
-        <f t="array" ref="H29">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-    </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="B30" s="16">
-        <f t="array" ref="B30">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="C30" s="16">
-        <f t="array" ref="C30">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="D30" s="16">
-        <f t="array" ref="D30">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="E30" s="16">
-        <f t="array" ref="E30">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="F30" s="16">
-        <f t="array" ref="F30">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="G30" s="17">
-        <f t="array" ref="G30">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="16">
-        <f t="array" ref="H30">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+      <c r="B30" s="20">
+        <f t="array" ref="B30">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="20">
+        <f t="array" ref="C30">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="20">
+        <f t="array" ref="D30">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="20">
+        <f t="array" ref="E30">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="20">
+        <f t="array" ref="F30">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="21">
+        <f t="array" ref="G30">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="20">
+        <f t="array" ref="H30">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="B31" s="18">
-        <f t="array" ref="B31">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="C31" s="18">
-        <f t="array" ref="C31">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="D31" s="18">
-        <f t="array" ref="D31">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="E31" s="18">
-        <f t="array" ref="E31">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="F31" s="18">
-        <f t="array" ref="F31">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="19">
-        <f t="array" ref="G31">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="18">
-        <f t="array" ref="H31">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B31" s="22">
+        <f t="array" ref="B31">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="C31" s="22">
+        <f t="array" ref="C31">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="22">
+        <f t="array" ref="D31">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="22">
+        <f t="array" ref="E31">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="22">
+        <f t="array" ref="F31">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="23">
+        <f t="array" ref="G31">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="22">
+        <f t="array" ref="H31">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="B32" s="20">
+        <f t="array" ref="B32">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="20">
+        <f t="array" ref="C32">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="20">
+        <f t="array" ref="D32">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="20">
+        <f t="array" ref="E32">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="20">
+        <f t="array" ref="F32">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="21">
+        <f t="array" ref="G32">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="20">
+        <f t="array" ref="H32">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="B33" s="22">
+        <f t="array" ref="B33">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="22">
+        <f t="array" ref="C33">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="22">
+        <f t="array" ref="D33">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="22">
+        <f t="array" ref="E33">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="22">
+        <f t="array" ref="F33">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="23">
+        <f t="array" ref="G33">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="22">
+        <f t="array" ref="H33">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="B34" s="20">
+        <f t="array" ref="B34">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="20">
+        <f t="array" ref="C34">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="20">
+        <f t="array" ref="D34">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="20">
+        <f t="array" ref="E34">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="20">
+        <f t="array" ref="F34">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="21">
+        <f t="array" ref="G34">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="20">
+        <f t="array" ref="H34">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="B35" s="22">
+        <f t="array" ref="B35">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="22">
+        <f t="array" ref="C35">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="22">
+        <f t="array" ref="D35">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="22">
+        <f t="array" ref="E35">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="22">
+        <f t="array" ref="F35">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="23">
+        <f t="array" ref="G35">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="22">
+        <f t="array" ref="H35">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="24" t="inlineStr">
         <is>
           <t>Add new topics directly in Meeting Log with today's date - they will appear above automatically.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="B35" s="14" t="inlineStr">
+    <row r="39" ht="22" customHeight="1">
+      <c r="B39" s="18" t="inlineStr">
         <is>
           <t>3. ACTIONS TO FOLLOW (all open actions, latest status)</t>
         </is>
       </c>
-      <c r="C35" s="14" t="n"/>
-      <c r="D35" s="14" t="n"/>
-      <c r="E35" s="14" t="n"/>
-      <c r="F35" s="14" t="n"/>
-      <c r="G35" s="14" t="n"/>
-    </row>
-    <row r="36">
-      <c r="B36" s="15" t="inlineStr">
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="18" t="n"/>
+      <c r="G39" s="18" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D36" s="15" t="inlineStr">
+      <c r="D40" s="19" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E36" s="15" t="inlineStr">
+      <c r="E40" s="19" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="F36" s="15" t="inlineStr">
+      <c r="F40" s="19" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G36" s="15" t="inlineStr">
+      <c r="G40" s="19" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="26" customHeight="1">
-      <c r="B37" s="16">
-        <f t="array" ref="B37">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="C37" s="16">
-        <f t="array" ref="C37">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="D37" s="16">
-        <f t="array" ref="D37">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="E37" s="17">
-        <f t="array" ref="E37">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="16">
-        <f t="array" ref="F37">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="16">
-        <f t="array" ref="G37">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="B38" s="18">
-        <f t="array" ref="B38">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="C38" s="18">
-        <f t="array" ref="C38">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="D38" s="18">
-        <f t="array" ref="D38">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="E38" s="19">
-        <f t="array" ref="E38">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="F38" s="18">
-        <f t="array" ref="F38">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="G38" s="18">
-        <f t="array" ref="G38">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="B39" s="16">
-        <f t="array" ref="B39">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="C39" s="16">
-        <f t="array" ref="C39">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="D39" s="16">
-        <f t="array" ref="D39">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="E39" s="17">
-        <f t="array" ref="E39">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="F39" s="16">
-        <f t="array" ref="F39">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="G39" s="16">
-        <f t="array" ref="G39">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="26" customHeight="1">
-      <c r="B40" s="18">
-        <f t="array" ref="B40">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="18">
-        <f t="array" ref="C40">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="18">
-        <f t="array" ref="D40">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="19">
-        <f t="array" ref="E40">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="18">
-        <f t="array" ref="F40">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="18">
-        <f t="array" ref="G40">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-    </row>
     <row r="41" ht="26" customHeight="1">
-      <c r="B41" s="16">
-        <f t="array" ref="B41">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="C41" s="16">
-        <f t="array" ref="C41">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="D41" s="16">
-        <f t="array" ref="D41">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="E41" s="17">
-        <f t="array" ref="E41">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="F41" s="16">
-        <f t="array" ref="F41">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="16">
-        <f t="array" ref="G41">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+      <c r="B41" s="20">
+        <f t="array" ref="B41">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="20">
+        <f t="array" ref="C41">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="20">
+        <f t="array" ref="D41">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="21">
+        <f t="array" ref="E41">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="20">
+        <f t="array" ref="F41">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="20">
+        <f t="array" ref="G41">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
-      <c r="B42" s="18">
-        <f t="array" ref="B42">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="C42" s="18">
-        <f t="array" ref="C42">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="D42" s="18">
-        <f t="array" ref="D42">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="E42" s="19">
-        <f t="array" ref="E42">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="18">
-        <f t="array" ref="F42">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="18">
-        <f t="array" ref="G42">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+      <c r="B42" s="22">
+        <f t="array" ref="B42">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="C42" s="22">
+        <f t="array" ref="C42">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="D42" s="22">
+        <f t="array" ref="D42">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="23">
+        <f t="array" ref="E42">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="22">
+        <f t="array" ref="F42">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="22">
+        <f t="array" ref="G42">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="B43" s="16">
-        <f t="array" ref="B43">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="C43" s="16">
-        <f t="array" ref="C43">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="D43" s="16">
-        <f t="array" ref="D43">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="E43" s="17">
-        <f t="array" ref="E43">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="16">
-        <f t="array" ref="F43">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="16">
-        <f t="array" ref="G43">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+      <c r="B43" s="20">
+        <f t="array" ref="B43">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="20">
+        <f t="array" ref="C43">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="20">
+        <f t="array" ref="D43">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="21">
+        <f t="array" ref="E43">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="20">
+        <f t="array" ref="F43">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="20">
+        <f t="array" ref="G43">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
-      <c r="B44" s="18">
-        <f t="array" ref="B44">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="C44" s="18">
-        <f t="array" ref="C44">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="D44" s="18">
-        <f t="array" ref="D44">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="E44" s="19">
-        <f t="array" ref="E44">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="F44" s="18">
-        <f t="array" ref="F44">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="G44" s="18">
-        <f t="array" ref="G44">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+      <c r="B44" s="22">
+        <f t="array" ref="B44">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="22">
+        <f t="array" ref="C44">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="22">
+        <f t="array" ref="D44">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="23">
+        <f t="array" ref="E44">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="22">
+        <f t="array" ref="F44">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="22">
+        <f t="array" ref="G44">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
-      <c r="B45" s="16">
-        <f t="array" ref="B45">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
-        <v/>
-      </c>
-      <c r="C45" s="16">
-        <f t="array" ref="C45">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
-        <v/>
-      </c>
-      <c r="D45" s="16">
-        <f t="array" ref="D45">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="17">
-        <f t="array" ref="E45">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="16">
-        <f t="array" ref="F45">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
-        <v/>
-      </c>
-      <c r="G45" s="16">
-        <f t="array" ref="G45">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+      <c r="B45" s="20">
+        <f t="array" ref="B45">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="20">
+        <f t="array" ref="C45">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="D45" s="20">
+        <f t="array" ref="D45">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="21">
+        <f t="array" ref="E45">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="20">
+        <f t="array" ref="F45">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="20">
+        <f t="array" ref="G45">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
-      <c r="B46" s="18">
-        <f t="array" ref="B46">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
-        <v/>
-      </c>
-      <c r="C46" s="18">
-        <f t="array" ref="C46">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
-        <v/>
-      </c>
-      <c r="D46" s="18">
-        <f t="array" ref="D46">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
-        <v/>
-      </c>
-      <c r="E46" s="19">
-        <f t="array" ref="E46">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
-        <v/>
-      </c>
-      <c r="F46" s="18">
-        <f t="array" ref="F46">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
-        <v/>
-      </c>
-      <c r="G46" s="18">
-        <f t="array" ref="G46">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="20" t="inlineStr">
+      <c r="B46" s="22">
+        <f t="array" ref="B46">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="C46" s="22">
+        <f t="array" ref="C46">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="22">
+        <f t="array" ref="D46">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="23">
+        <f t="array" ref="E46">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="22">
+        <f t="array" ref="F46">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="22">
+        <f t="array" ref="G46">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="B47" s="20">
+        <f t="array" ref="B47">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="C47" s="20">
+        <f t="array" ref="C47">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="D47" s="20">
+        <f t="array" ref="D47">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="21">
+        <f t="array" ref="E47">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="20">
+        <f t="array" ref="F47">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="20">
+        <f t="array" ref="G47">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="B48" s="22">
+        <f t="array" ref="B48">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="C48" s="22">
+        <f t="array" ref="C48">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="D48" s="22">
+        <f t="array" ref="D48">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="E48" s="23">
+        <f t="array" ref="E48">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="F48" s="22">
+        <f t="array" ref="F48">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="22">
+        <f t="array" ref="G48">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="B49" s="20">
+        <f t="array" ref="B49">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <v/>
+      </c>
+      <c r="C49" s="20">
+        <f t="array" ref="C49">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <v/>
+      </c>
+      <c r="D49" s="20">
+        <f t="array" ref="D49">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <v/>
+      </c>
+      <c r="E49" s="21">
+        <f t="array" ref="E49">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="20">
+        <f t="array" ref="F49">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="20">
+        <f t="array" ref="G49">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="B50" s="22">
+        <f t="array" ref="B50">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <v/>
+      </c>
+      <c r="C50" s="22">
+        <f t="array" ref="C50">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <v/>
+      </c>
+      <c r="D50" s="22">
+        <f t="array" ref="D50">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <v/>
+      </c>
+      <c r="E50" s="23">
+        <f t="array" ref="E50">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <v/>
+      </c>
+      <c r="F50" s="22">
+        <f t="array" ref="F50">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="22">
+        <f t="array" ref="G50">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="24" t="inlineStr">
         <is>
           <t>Legend: Blue = fill in yourself | Black = automatic, do not overtype | Grey columns = automation helpers, leave untouched | New row: type directly below the table and Excel extends it automatically</t>
         </is>
@@ -1738,7 +1785,7 @@
     <mergeCell ref="Q8:R10"/>
     <mergeCell ref="E8:F10"/>
   </mergeCells>
-  <conditionalFormatting sqref="G37:G46">
+  <conditionalFormatting sqref="G41:G50">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Critical"</formula>
     </cfRule>
@@ -1750,6 +1797,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1816,266 +1866,266 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Meeting ID</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Meeting Date</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>Meeting Type</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>Sub-topic</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>Discussion / Notes</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t>Agreed Action</t>
         </is>
       </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="J7" s="15" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="K7" s="21" t="inlineStr">
+      <c r="K7" s="15" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L7" s="21" t="inlineStr">
+      <c r="L7" s="15" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="M7" s="21" t="inlineStr">
+      <c r="M7" s="15" t="inlineStr">
         <is>
           <t>Follow-up / Update</t>
         </is>
       </c>
-      <c r="N7" s="21" t="inlineStr">
+      <c r="N7" s="15" t="inlineStr">
         <is>
           <t>Topic Key</t>
         </is>
       </c>
-      <c r="O7" s="21" t="inlineStr">
+      <c r="O7" s="15" t="inlineStr">
         <is>
           <t>Overdue?</t>
         </is>
       </c>
     </row>
     <row r="8" ht="50" customHeight="1">
-      <c r="B8" s="16">
+      <c r="B8" s="20">
         <f>IF($E8="","","M"&amp;TEXT(ROW()-7,"000"))</f>
         <v/>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="16" t="n">
         <v>46266</v>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>Documents missing for the commissioning dossier.</t>
         </is>
       </c>
-      <c r="I8" s="23" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>Engineering to provide the missing documents.</t>
         </is>
       </c>
-      <c r="J8" s="22" t="n">
+      <c r="J8" s="16" t="n">
         <v>46280</v>
       </c>
-      <c r="K8" s="23" t="inlineStr">
+      <c r="K8" s="17" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L8" s="23" t="inlineStr">
+      <c r="L8" s="17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M8" s="23" t="inlineStr"/>
-      <c r="N8" s="24">
+      <c r="M8" s="17" t="inlineStr"/>
+      <c r="N8" s="25">
         <f>IF($E8="","",$E8&amp;"|"&amp;$F8)</f>
         <v/>
       </c>
-      <c r="O8" s="16">
+      <c r="O8" s="20">
         <f>IF($E8="","",IF(AND($K8&lt;&gt;"Closed",$K8&lt;&gt;"Cancelled",$J8&lt;&gt;"",$J8&lt;TODAY()),"Yes","No"))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="50" customHeight="1">
-      <c r="B9" s="16">
+      <c r="B9" s="20">
         <f>IF($E9="","","M"&amp;TEXT(ROW()-7,"000"))</f>
         <v/>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="16" t="n">
         <v>46296</v>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>Engineering confirmed the documents are being finalised.</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>Engineering to issue the documents.</t>
         </is>
       </c>
-      <c r="J9" s="22" t="n">
+      <c r="J9" s="16" t="n">
         <v>46310</v>
       </c>
-      <c r="K9" s="23" t="inlineStr">
+      <c r="K9" s="17" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="L9" s="23" t="inlineStr">
+      <c r="L9" s="17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M9" s="23" t="inlineStr">
+      <c r="M9" s="17" t="inlineStr">
         <is>
           <t>Continued from the 01-Sep meeting - still outstanding.</t>
         </is>
       </c>
-      <c r="N9" s="24">
+      <c r="N9" s="25">
         <f>IF($E9="","",$E9&amp;"|"&amp;$F9)</f>
         <v/>
       </c>
-      <c r="O9" s="16">
+      <c r="O9" s="20">
         <f>IF($E9="","",IF(AND($K9&lt;&gt;"Closed",$K9&lt;&gt;"Cancelled",$J9&lt;&gt;"",$J9&lt;TODAY()),"Yes","No"))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="50" customHeight="1">
-      <c r="B10" s="16">
+      <c r="B10" s="20">
         <f>IF($E10="","","M"&amp;TEXT(ROW()-7,"000"))</f>
         <v/>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="16" t="n">
         <v>46296</v>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>Testing / Results</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>Commissioning</t>
         </is>
       </c>
-      <c r="H10" s="23" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>First functional test results reviewed.</t>
         </is>
       </c>
-      <c r="I10" s="23" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>Commissioning to issue the test report.</t>
         </is>
       </c>
-      <c r="J10" s="22" t="n">
+      <c r="J10" s="16" t="n">
         <v>46315</v>
       </c>
-      <c r="K10" s="23" t="inlineStr">
+      <c r="K10" s="17" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L10" s="23" t="inlineStr">
+      <c r="L10" s="17" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M10" s="23" t="inlineStr"/>
-      <c r="N10" s="24">
+      <c r="M10" s="17" t="inlineStr"/>
+      <c r="N10" s="25">
         <f>IF($E10="","",$E10&amp;"|"&amp;$F10)</f>
         <v/>
       </c>
-      <c r="O10" s="16">
+      <c r="O10" s="20">
         <f>IF($E10="","",IF(AND($K10&lt;&gt;"Closed",$K10&lt;&gt;"Cancelled",$J10&lt;&gt;"",$J10&lt;TODAY()),"Yes","No"))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>Legend: Blue = fill in yourself | Black = automatic, do not overtype | Grey columns = automation helpers, leave untouched | New row: type directly below the table and Excel extends it automatically</t>
         </is>
@@ -2187,7 +2237,7 @@
           <t>Meeting Date:</t>
         </is>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <f>'Overview'!$C$5</f>
         <v/>
       </c>
@@ -2196,923 +2246,923 @@
           <t>Meeting Type:</t>
         </is>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="27">
         <f>IFERROR(INDEX(Meeting_Log[Meeting Type],MATCH($C$5,Meeting_Log[Meeting Date],0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>1. FOLLOW-UP FROM PREVIOUS MEETING</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="14" t="n"/>
-      <c r="E7" s="14" t="n"/>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="C7" s="18" t="n"/>
+      <c r="D7" s="18" t="n"/>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="18" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Sub-topic</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Previous Discussion</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>Previous Action</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>Previous Status</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="16">
+      <c r="B9" s="20">
         <f t="array" ref="B9">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="20">
         <f t="array" ref="C9">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="20">
         <f t="array" ref="D9">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="20">
         <f t="array" ref="E9">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="20">
         <f t="array" ref="F9">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="20">
         <f t="array" ref="G9">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="18">
+      <c r="B10" s="22">
         <f t="array" ref="B10">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="22">
         <f t="array" ref="C10">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="22">
         <f t="array" ref="D10">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="22">
         <f t="array" ref="E10">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="22">
         <f t="array" ref="F10">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="22">
         <f t="array" ref="G10">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="B11" s="16">
+      <c r="B11" s="20">
         <f t="array" ref="B11">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="20">
         <f t="array" ref="C11">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="20">
         <f t="array" ref="D11">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="20">
         <f t="array" ref="E11">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="20">
         <f t="array" ref="F11">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="20">
         <f t="array" ref="G11">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="B12" s="18">
+      <c r="B12" s="22">
         <f t="array" ref="B12">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="22">
         <f t="array" ref="C12">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="22">
         <f t="array" ref="D12">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="22">
         <f t="array" ref="E12">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="22">
         <f t="array" ref="F12">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="22">
         <f t="array" ref="G12">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="B13" s="16">
+      <c r="B13" s="20">
         <f t="array" ref="B13">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="20">
         <f t="array" ref="C13">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="20">
         <f t="array" ref="D13">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="20">
         <f t="array" ref="E13">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="20">
         <f t="array" ref="F13">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="20">
         <f t="array" ref="G13">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="B14" s="18">
+      <c r="B14" s="22">
         <f t="array" ref="B14">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="22">
         <f t="array" ref="C14">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="22">
         <f t="array" ref="D14">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="22">
         <f t="array" ref="E14">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="22">
         <f t="array" ref="F14">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="22">
         <f t="array" ref="G14">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="B15" s="16">
+      <c r="B15" s="20">
         <f t="array" ref="B15">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="20">
         <f t="array" ref="C15">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="20">
         <f t="array" ref="D15">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="20">
         <f t="array" ref="E15">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="20">
         <f t="array" ref="F15">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="20">
         <f t="array" ref="G15">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="B16" s="18">
+      <c r="B16" s="22">
         <f t="array" ref="B16">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="22">
         <f t="array" ref="C16">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="22">
         <f t="array" ref="D16">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="22">
         <f t="array" ref="E16">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="22">
         <f t="array" ref="F16">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="22">
         <f t="array" ref="G16">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>2. NEW TOPICS</t>
         </is>
       </c>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="14" t="n"/>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="14" t="n"/>
-      <c r="H18" s="14" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="18" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>Sub-topic</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Discussion / Notes</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" s="19" t="inlineStr">
         <is>
           <t>Agreed Action</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr">
+      <c r="G19" s="19" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="H19" s="15" t="inlineStr">
+      <c r="H19" s="19" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="B20" s="16">
+      <c r="B20" s="20">
         <f t="array" ref="B20">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="20">
         <f t="array" ref="C20">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="20">
         <f t="array" ref="D20">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="20">
         <f t="array" ref="E20">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="20">
         <f t="array" ref="F20">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="21">
         <f t="array" ref="G20">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="20">
         <f t="array" ref="H20">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="B21" s="18">
+      <c r="B21" s="22">
         <f t="array" ref="B21">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="22">
         <f t="array" ref="C21">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="22">
         <f t="array" ref="D21">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="22">
         <f t="array" ref="E21">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="22">
         <f t="array" ref="F21">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="23">
         <f t="array" ref="G21">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
-      <c r="H21" s="18">
+      <c r="H21" s="22">
         <f t="array" ref="H21">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="B22" s="16">
+      <c r="B22" s="20">
         <f t="array" ref="B22">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="20">
         <f t="array" ref="C22">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="20">
         <f t="array" ref="D22">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="20">
         <f t="array" ref="E22">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="20">
         <f t="array" ref="F22">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="21">
         <f t="array" ref="G22">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="20">
         <f t="array" ref="H22">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="B23" s="18">
+      <c r="B23" s="22">
         <f t="array" ref="B23">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="22">
         <f t="array" ref="C23">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
-      <c r="D23" s="18">
+      <c r="D23" s="22">
         <f t="array" ref="D23">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="22">
         <f t="array" ref="E23">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="22">
         <f t="array" ref="F23">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="23">
         <f t="array" ref="G23">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
-      <c r="H23" s="18">
+      <c r="H23" s="22">
         <f t="array" ref="H23">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="B24" s="16">
+      <c r="B24" s="20">
         <f t="array" ref="B24">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="20">
         <f t="array" ref="C24">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="20">
         <f t="array" ref="D24">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="20">
         <f t="array" ref="E24">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="20">
         <f t="array" ref="F24">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="21">
         <f t="array" ref="G24">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="20">
         <f t="array" ref="H24">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="B25" s="18">
+      <c r="B25" s="22">
         <f t="array" ref="B25">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="22">
         <f t="array" ref="C25">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
-      <c r="D25" s="18">
+      <c r="D25" s="22">
         <f t="array" ref="D25">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="22">
         <f t="array" ref="E25">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="22">
         <f t="array" ref="F25">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="23">
         <f t="array" ref="G25">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
-      <c r="H25" s="18">
+      <c r="H25" s="22">
         <f t="array" ref="H25">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>3. ACTION SUMMARY</t>
         </is>
       </c>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="14" t="n"/>
-      <c r="E27" s="14" t="n"/>
-      <c r="F27" s="14" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D28" s="19" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="E28" s="19" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F28" s="15" t="inlineStr">
+      <c r="F28" s="19" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
-      <c r="B29" s="16">
+      <c r="B29" s="20">
         <f t="array" ref="B29">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="20">
         <f t="array" ref="C29">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="21">
         <f t="array" ref="D29">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="20">
         <f t="array" ref="E29">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="20">
         <f t="array" ref="F29">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="B30" s="18">
+      <c r="B30" s="22">
         <f t="array" ref="B30">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
-      <c r="C30" s="18">
+      <c r="C30" s="22">
         <f t="array" ref="C30">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="23">
         <f t="array" ref="D30">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
-      <c r="E30" s="18">
+      <c r="E30" s="22">
         <f t="array" ref="E30">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
-      <c r="F30" s="18">
+      <c r="F30" s="22">
         <f t="array" ref="F30">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="B31" s="16">
+      <c r="B31" s="20">
         <f t="array" ref="B31">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
-      <c r="C31" s="16">
+      <c r="C31" s="20">
         <f t="array" ref="C31">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="21">
         <f t="array" ref="D31">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="20">
         <f t="array" ref="E31">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="20">
         <f t="array" ref="F31">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="B32" s="18">
+      <c r="B32" s="22">
         <f t="array" ref="B32">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
-      <c r="C32" s="18">
+      <c r="C32" s="22">
         <f t="array" ref="C32">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="23">
         <f t="array" ref="D32">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
-      <c r="E32" s="18">
+      <c r="E32" s="22">
         <f t="array" ref="E32">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
-      <c r="F32" s="18">
+      <c r="F32" s="22">
         <f t="array" ref="F32">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="B33" s="16">
+      <c r="B33" s="20">
         <f t="array" ref="B33">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="20">
         <f t="array" ref="C33">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
-      <c r="D33" s="17">
+      <c r="D33" s="21">
         <f t="array" ref="D33">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="20">
         <f t="array" ref="E33">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="20">
         <f t="array" ref="F33">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="B34" s="18">
+      <c r="B34" s="22">
         <f t="array" ref="B34">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
-      <c r="C34" s="18">
+      <c r="C34" s="22">
         <f t="array" ref="C34">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="23">
         <f t="array" ref="D34">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="22">
         <f t="array" ref="E34">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
-      <c r="F34" s="18">
+      <c r="F34" s="22">
         <f t="array" ref="F34">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="B35" s="16">
+      <c r="B35" s="20">
         <f t="array" ref="B35">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
-      <c r="C35" s="16">
+      <c r="C35" s="20">
         <f t="array" ref="C35">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
-      <c r="D35" s="17">
+      <c r="D35" s="21">
         <f t="array" ref="D35">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="20">
         <f t="array" ref="E35">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="20">
         <f t="array" ref="F35">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
-      <c r="B36" s="18">
+      <c r="B36" s="22">
         <f t="array" ref="B36">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
-      <c r="C36" s="18">
+      <c r="C36" s="22">
         <f t="array" ref="C36">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="23">
         <f t="array" ref="D36">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="22">
         <f t="array" ref="E36">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
-      <c r="F36" s="18">
+      <c r="F36" s="22">
         <f t="array" ref="F36">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>4. OPEN / OVERDUE ACTIONS</t>
         </is>
       </c>
-      <c r="C38" s="14" t="n"/>
-      <c r="D38" s="14" t="n"/>
-      <c r="E38" s="14" t="n"/>
-      <c r="F38" s="14" t="n"/>
+      <c r="C38" s="18" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="18" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="C39" s="15" t="inlineStr">
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D39" s="15" t="inlineStr">
+      <c r="D39" s="19" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E39" s="15" t="inlineStr">
+      <c r="E39" s="19" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="F39" s="15" t="inlineStr">
+      <c r="F39" s="19" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
-      <c r="B40" s="16">
+      <c r="B40" s="20">
         <f t="array" ref="B40">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="20">
         <f t="array" ref="C40">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
-      <c r="D40" s="16">
+      <c r="D40" s="20">
         <f t="array" ref="D40">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
-      <c r="E40" s="17">
+      <c r="E40" s="21">
         <f t="array" ref="E40">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="20">
         <f t="array" ref="F40">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="26" customHeight="1">
-      <c r="B41" s="18">
+      <c r="B41" s="22">
         <f t="array" ref="B41">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
-      <c r="C41" s="18">
+      <c r="C41" s="22">
         <f t="array" ref="C41">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
-      <c r="D41" s="18">
+      <c r="D41" s="22">
         <f t="array" ref="D41">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
-      <c r="E41" s="19">
+      <c r="E41" s="23">
         <f t="array" ref="E41">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
-      <c r="F41" s="18">
+      <c r="F41" s="22">
         <f t="array" ref="F41">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
-      <c r="B42" s="16">
+      <c r="B42" s="20">
         <f t="array" ref="B42">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="20">
         <f t="array" ref="C42">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="20">
         <f t="array" ref="D42">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
-      <c r="E42" s="17">
+      <c r="E42" s="21">
         <f t="array" ref="E42">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="20">
         <f t="array" ref="F42">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="B43" s="18">
+      <c r="B43" s="22">
         <f t="array" ref="B43">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
-      <c r="C43" s="18">
+      <c r="C43" s="22">
         <f t="array" ref="C43">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
-      <c r="D43" s="18">
+      <c r="D43" s="22">
         <f t="array" ref="D43">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
-      <c r="E43" s="19">
+      <c r="E43" s="23">
         <f t="array" ref="E43">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
-      <c r="F43" s="18">
+      <c r="F43" s="22">
         <f t="array" ref="F43">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
-      <c r="B44" s="16">
+      <c r="B44" s="20">
         <f t="array" ref="B44">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
-      <c r="C44" s="16">
+      <c r="C44" s="20">
         <f t="array" ref="C44">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
-      <c r="D44" s="16">
+      <c r="D44" s="20">
         <f t="array" ref="D44">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
-      <c r="E44" s="17">
+      <c r="E44" s="21">
         <f t="array" ref="E44">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="20">
         <f t="array" ref="F44">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
-      <c r="B45" s="18">
+      <c r="B45" s="22">
         <f t="array" ref="B45">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
-      <c r="C45" s="18">
+      <c r="C45" s="22">
         <f t="array" ref="C45">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
-      <c r="D45" s="18">
+      <c r="D45" s="22">
         <f t="array" ref="D45">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
-      <c r="E45" s="19">
+      <c r="E45" s="23">
         <f t="array" ref="E45">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
-      <c r="F45" s="18">
+      <c r="F45" s="22">
         <f t="array" ref="F45">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
-      <c r="B46" s="16">
+      <c r="B46" s="20">
         <f t="array" ref="B46">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
-      <c r="C46" s="16">
+      <c r="C46" s="20">
         <f t="array" ref="C46">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
-      <c r="D46" s="16">
+      <c r="D46" s="20">
         <f t="array" ref="D46">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
-      <c r="E46" s="17">
+      <c r="E46" s="21">
         <f t="array" ref="E46">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
-      <c r="F46" s="16">
+      <c r="F46" s="20">
         <f t="array" ref="F46">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="26" customHeight="1">
-      <c r="B47" s="18">
+      <c r="B47" s="22">
         <f t="array" ref="B47">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
-      <c r="C47" s="18">
+      <c r="C47" s="22">
         <f t="array" ref="C47">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
-      <c r="D47" s="18">
+      <c r="D47" s="22">
         <f t="array" ref="D47">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
-      <c r="E47" s="19">
+      <c r="E47" s="23">
         <f t="array" ref="E47">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
-      <c r="F47" s="18">
+      <c r="F47" s="22">
         <f t="array" ref="F47">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="20" t="inlineStr">
+      <c r="B49" s="24" t="inlineStr">
         <is>
           <t>Legend: Blue = fill in yourself | Black = automatic, do not overtype | Grey columns = automation helpers, leave untouched | New row: type directly below the table and Excel extends it automatically</t>
         </is>
@@ -3184,304 +3234,304 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>Sub-topic</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t>Meeting Type</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Commissioning Planning</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Commissioning</t>
         </is>
       </c>
-      <c r="E6" s="28" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="F6" s="28" t="inlineStr">
+      <c r="F6" s="29" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G6" s="28" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Site / Field Activities</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
-      <c r="D7" s="29" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="E7" s="29" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F7" s="29" t="inlineStr">
+      <c r="F7" s="30" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G7" s="29" t="inlineStr">
+      <c r="G7" s="30" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Preparation</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Construction</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="F8" s="29" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G8" s="28" t="inlineStr">
+      <c r="G8" s="29" t="inlineStr">
         <is>
           <t>Ad hoc</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Testing / Results</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>Execution</t>
         </is>
       </c>
-      <c r="D9" s="29" t="inlineStr">
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="E9" s="29" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>On Hold</t>
         </is>
       </c>
-      <c r="F9" s="29" t="inlineStr">
+      <c r="F9" s="30" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>Interfaces</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
-      <c r="D10" s="28" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>HSE</t>
         </is>
       </c>
-      <c r="E10" s="28" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>Cancelled</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="C11" s="29" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>Punch List</t>
         </is>
       </c>
-      <c r="D11" s="29" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="D12" s="28" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>Document Control</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>NCR / Quality</t>
         </is>
       </c>
-      <c r="D13" s="29" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>Project Team</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Resources / Manpower</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Design / Engineering</t>
         </is>
       </c>
-      <c r="D14" s="28" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="29" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="C15" s="29" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
         <is>
           <t>Interface</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C16" s="28" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>Resource</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="29" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="28" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>Risk / Issue</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="29" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="28" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Legend: Blue = fill in yourself | Black = automatic, do not overtype | Grey columns = automation helpers, leave untouched | New row: type directly below the table and Excel extends it automatically</t>
         </is>

--- a/HBX Commissioning Review.xlsx
+++ b/HBX Commissioning Review.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd-mmm-yy"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,12 +89,6 @@
       <name val="Arial"/>
       <color rgb="001155CC"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00808080"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -163,7 +157,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -183,11 +177,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F5FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
     <fill>
@@ -242,12 +231,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -257,13 +249,10 @@
     <xf numFmtId="1" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -273,8 +262,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -283,16 +272,16 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -423,34 +412,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Attendees_Log" displayName="Attendees_Log" ref="B14:C15" headerRowCount="1">
-  <autoFilter ref="B14:C15"/>
-  <tableColumns count="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Attendees_Log" displayName="Attendees_Log" ref="B14:D15" headerRowCount="1">
+  <autoFilter ref="B14:D15"/>
+  <tableColumns count="3">
     <tableColumn id="2" name="Meeting Date"/>
-    <tableColumn id="3" name="Attendees"/>
+    <tableColumn id="3" name="Meeting Type"/>
+    <tableColumn id="4" name="Attendees"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Meeting_Log" displayName="Meeting_Log" ref="B7:O10" headerRowCount="1">
-  <autoFilter ref="B7:O10"/>
-  <tableColumns count="14">
-    <tableColumn id="2" name="Meeting ID"/>
-    <tableColumn id="3" name="Meeting Date"/>
-    <tableColumn id="4" name="Meeting Type"/>
-    <tableColumn id="5" name="Subject"/>
-    <tableColumn id="6" name="Sub-topic"/>
-    <tableColumn id="7" name="Owner"/>
-    <tableColumn id="8" name="Discussion / Notes"/>
-    <tableColumn id="9" name="Agreed Action"/>
-    <tableColumn id="10" name="Due Date"/>
-    <tableColumn id="11" name="Status"/>
-    <tableColumn id="12" name="Priority"/>
-    <tableColumn id="13" name="Follow-up / Update"/>
-    <tableColumn id="14" name="Topic Key"/>
-    <tableColumn id="15" name="Overdue?"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Meeting_Log" displayName="Meeting_Log" ref="B7:M10" headerRowCount="1">
+  <autoFilter ref="B7:M10"/>
+  <tableColumns count="12">
+    <tableColumn id="2" name="Subject"/>
+    <tableColumn id="3" name="Sub-topic"/>
+    <tableColumn id="4" name="Owner"/>
+    <tableColumn id="5" name="Discussion / Notes"/>
+    <tableColumn id="6" name="Agreed Action"/>
+    <tableColumn id="7" name="Due Date"/>
+    <tableColumn id="8" name="Status"/>
+    <tableColumn id="9" name="Priority"/>
+    <tableColumn id="10" name="Follow-up / Update"/>
+    <tableColumn id="11" name="Added Date"/>
+    <tableColumn id="12" name="Last Update Date"/>
+    <tableColumn id="13" name="Overdue?"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -813,32 +801,32 @@
     </row>
     <row r="8">
       <c r="B8" s="7">
-        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5)))</f>
+        <f>SUMPRODUCT((Meeting_Log[Subject]&lt;&gt;""))</f>
         <v/>
       </c>
       <c r="C8" s="8" t="n"/>
       <c r="E8" s="7">
-        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"))</f>
+        <f>SUMPRODUCT((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"))</f>
         <v/>
       </c>
       <c r="F8" s="8" t="n"/>
       <c r="H8" s="9">
-        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Overdue?]="Yes"))</f>
+        <f>SUMPRODUCT((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Overdue?]="Yes"))</f>
         <v/>
       </c>
       <c r="I8" s="8" t="n"/>
       <c r="K8" s="10">
-        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]="Closed"))</f>
+        <f>SUMPRODUCT((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]="Closed"))</f>
         <v/>
       </c>
       <c r="L8" s="8" t="n"/>
       <c r="N8" s="11">
-        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"))</f>
+        <f>SUMPRODUCT((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5))</f>
         <v/>
       </c>
       <c r="O8" s="8" t="n"/>
       <c r="Q8" s="12">
-        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0))</f>
+        <f>SUMPRODUCT((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5))</f>
         <v/>
       </c>
       <c r="R8" s="8" t="n"/>
@@ -918,6 +906,11 @@
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
+          <t>Meeting Type</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
           <t>Attendees</t>
         </is>
       </c>
@@ -928,6 +921,11 @@
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
           <t>Person A, Person B, Contractor A representative</t>
         </is>
       </c>
@@ -935,7 +933,7 @@
     <row r="17" ht="22" customHeight="1">
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>1. FOLLOW-UP FROM PREVIOUS MEETING</t>
+          <t>1. FOLLOW-UP FROM PREVIOUS MEETING (open, not yet touched today)</t>
         </is>
       </c>
       <c r="C17" s="18" t="n"/>
@@ -958,12 +956,12 @@
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>Previous Discussion</t>
+          <t>Discussion</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>Previous Action</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="F18" s="19" t="inlineStr">
@@ -973,259 +971,259 @@
       </c>
       <c r="G18" s="19" t="inlineStr">
         <is>
-          <t>Previous Due Date</t>
+          <t>Due Date</t>
         </is>
       </c>
       <c r="H18" s="19" t="inlineStr">
         <is>
-          <t>Previous Status</t>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="B19" s="20">
-        <f t="array" ref="B19">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="B19">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="C19" s="20">
-        <f t="array" ref="C19">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="C19">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="D19" s="20">
-        <f t="array" ref="D19">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="D19">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="E19" s="20">
-        <f t="array" ref="E19">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="E19">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="F19" s="20">
-        <f t="array" ref="F19">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="F19">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="G19" s="21">
-        <f t="array" ref="G19">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="G19">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="H19" s="20">
-        <f t="array" ref="H19">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="H19">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="B20" s="22">
-        <f t="array" ref="B20">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="B20">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="C20" s="22">
-        <f t="array" ref="C20">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="C20">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="D20" s="22">
-        <f t="array" ref="D20">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="D20">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="E20" s="22">
-        <f t="array" ref="E20">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="E20">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="F20" s="22">
-        <f t="array" ref="F20">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="F20">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="G20" s="23">
-        <f t="array" ref="G20">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="G20">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="H20" s="22">
-        <f t="array" ref="H20">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="H20">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="B21" s="20">
-        <f t="array" ref="B21">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="B21">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="C21" s="20">
-        <f t="array" ref="C21">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="C21">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="D21" s="20">
-        <f t="array" ref="D21">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="D21">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="E21" s="20">
-        <f t="array" ref="E21">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="E21">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="F21" s="20">
-        <f t="array" ref="F21">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="F21">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="G21" s="21">
-        <f t="array" ref="G21">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="G21">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="H21" s="20">
-        <f t="array" ref="H21">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="H21">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="B22" s="22">
-        <f t="array" ref="B22">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="B22">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="C22" s="22">
-        <f t="array" ref="C22">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="C22">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="D22" s="22">
-        <f t="array" ref="D22">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="D22">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="E22" s="22">
-        <f t="array" ref="E22">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="E22">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="F22" s="22">
-        <f t="array" ref="F22">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="F22">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="G22" s="23">
-        <f t="array" ref="G22">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="G22">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="H22" s="22">
-        <f t="array" ref="H22">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="H22">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="B23" s="20">
-        <f t="array" ref="B23">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="B23">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="C23" s="20">
-        <f t="array" ref="C23">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="C23">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="D23" s="20">
-        <f t="array" ref="D23">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="D23">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="E23" s="20">
-        <f t="array" ref="E23">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="E23">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="F23" s="20">
-        <f t="array" ref="F23">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="F23">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="G23" s="21">
-        <f t="array" ref="G23">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="G23">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="H23" s="20">
-        <f t="array" ref="H23">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="H23">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="B24" s="22">
-        <f t="array" ref="B24">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="B24">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="C24" s="22">
-        <f t="array" ref="C24">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="C24">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="D24" s="22">
-        <f t="array" ref="D24">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="D24">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="E24" s="22">
-        <f t="array" ref="E24">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="E24">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="F24" s="22">
-        <f t="array" ref="F24">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="F24">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="G24" s="23">
-        <f t="array" ref="G24">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="G24">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="H24" s="22">
-        <f t="array" ref="H24">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="H24">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="B25" s="20">
-        <f t="array" ref="B25">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="B25">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="C25" s="20">
-        <f t="array" ref="C25">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="C25">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="D25" s="20">
-        <f t="array" ref="D25">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="D25">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="E25" s="20">
-        <f t="array" ref="E25">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="E25">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="F25" s="20">
-        <f t="array" ref="F25">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="F25">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="G25" s="21">
-        <f t="array" ref="G25">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="G25">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="H25" s="20">
-        <f t="array" ref="H25">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="H25">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="B26" s="22">
-        <f t="array" ref="B26">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="B26">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="C26" s="22">
-        <f t="array" ref="C26">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="C26">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="D26" s="22">
-        <f t="array" ref="D26">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="D26">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="E26" s="22">
-        <f t="array" ref="E26">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="E26">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="F26" s="22">
-        <f t="array" ref="F26">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="F26">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="G26" s="23">
-        <f t="array" ref="G26">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="G26">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="H26" s="22">
-        <f t="array" ref="H26">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="H26">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>2. NEW TOPICS</t>
+          <t>2. NEW TOPICS (raised today)</t>
         </is>
       </c>
       <c r="C28" s="18" t="n"/>
@@ -1274,195 +1272,195 @@
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="B30" s="20">
-        <f t="array" ref="B30">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="B30">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="C30" s="20">
-        <f t="array" ref="C30">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="C30">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="D30" s="20">
-        <f t="array" ref="D30">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="D30">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="E30" s="20">
-        <f t="array" ref="E30">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="E30">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="F30" s="20">
-        <f t="array" ref="F30">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="F30">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="G30" s="21">
-        <f t="array" ref="G30">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="G30">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="H30" s="20">
-        <f t="array" ref="H30">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="H30">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="B31" s="22">
-        <f t="array" ref="B31">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="B31">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="C31" s="22">
-        <f t="array" ref="C31">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="C31">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="D31" s="22">
-        <f t="array" ref="D31">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="D31">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="E31" s="22">
-        <f t="array" ref="E31">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="E31">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="F31" s="22">
-        <f t="array" ref="F31">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="F31">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="G31" s="23">
-        <f t="array" ref="G31">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="G31">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="H31" s="22">
-        <f t="array" ref="H31">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="H31">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="B32" s="20">
-        <f t="array" ref="B32">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="B32">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="C32" s="20">
-        <f t="array" ref="C32">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="C32">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="D32" s="20">
-        <f t="array" ref="D32">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="D32">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="E32" s="20">
-        <f t="array" ref="E32">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="E32">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="F32" s="20">
-        <f t="array" ref="F32">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="F32">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="G32" s="21">
-        <f t="array" ref="G32">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="G32">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="H32" s="20">
-        <f t="array" ref="H32">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="H32">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="B33" s="22">
-        <f t="array" ref="B33">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="B33">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="C33" s="22">
-        <f t="array" ref="C33">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="C33">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="D33" s="22">
-        <f t="array" ref="D33">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="D33">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="E33" s="22">
-        <f t="array" ref="E33">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="E33">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="F33" s="22">
-        <f t="array" ref="F33">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="F33">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="G33" s="23">
-        <f t="array" ref="G33">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="G33">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="H33" s="22">
-        <f t="array" ref="H33">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="H33">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="B34" s="20">
-        <f t="array" ref="B34">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="B34">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="C34" s="20">
-        <f t="array" ref="C34">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="C34">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="D34" s="20">
-        <f t="array" ref="D34">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="D34">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="E34" s="20">
-        <f t="array" ref="E34">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="E34">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="F34" s="20">
-        <f t="array" ref="F34">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="F34">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="G34" s="21">
-        <f t="array" ref="G34">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="G34">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="H34" s="20">
-        <f t="array" ref="H34">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="H34">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="B35" s="22">
-        <f t="array" ref="B35">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="B35">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="C35" s="22">
-        <f t="array" ref="C35">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="C35">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="D35" s="22">
-        <f t="array" ref="D35">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="D35">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="E35" s="22">
-        <f t="array" ref="E35">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="E35">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="F35" s="22">
-        <f t="array" ref="F35">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="F35">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="G35" s="23">
-        <f t="array" ref="G35">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="G35">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="H35" s="22">
-        <f t="array" ref="H35">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="H35">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>Add new topics directly in Meeting Log with today's date - they will appear above automatically.</t>
+          <t>To continue a topic above: edit its row directly in Meeting Log (Discussion/Action/Status/Due Date) and set Last Update Date to today - do not create a new row. Only add a new row for a topic never raised before, with today as its Added Date.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="B39" s="18" t="inlineStr">
         <is>
-          <t>3. ACTIONS TO FOLLOW (all open actions, latest status)</t>
+          <t>3. ACTIONS TO FOLLOW (all currently open topics)</t>
         </is>
       </c>
       <c r="C39" s="18" t="n"/>
@@ -1505,261 +1503,261 @@
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="B41" s="20">
-        <f t="array" ref="B41">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="B41">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="C41" s="20">
-        <f t="array" ref="C41">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="C41">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="D41" s="20">
-        <f t="array" ref="D41">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="D41">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="E41" s="21">
-        <f t="array" ref="E41">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="E41">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="F41" s="20">
-        <f t="array" ref="F41">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="F41">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="G41" s="20">
-        <f t="array" ref="G41">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="G41">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="B42" s="22">
-        <f t="array" ref="B42">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="B42">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="C42" s="22">
-        <f t="array" ref="C42">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="C42">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f t="array" ref="D42">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="D42">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f t="array" ref="E42">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="E42">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f t="array" ref="F42">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="F42">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f t="array" ref="G42">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="G42">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="B43" s="20">
-        <f t="array" ref="B43">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="B43">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="C43" s="20">
-        <f t="array" ref="C43">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="C43">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="D43" s="20">
-        <f t="array" ref="D43">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="D43">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="E43" s="21">
-        <f t="array" ref="E43">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="E43">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="F43" s="20">
-        <f t="array" ref="F43">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="F43">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="G43" s="20">
-        <f t="array" ref="G43">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="G43">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="B44" s="22">
-        <f t="array" ref="B44">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="B44">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="C44" s="22">
-        <f t="array" ref="C44">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="C44">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f t="array" ref="D44">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="D44">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="E44" s="23">
-        <f t="array" ref="E44">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="E44">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f t="array" ref="F44">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="F44">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f t="array" ref="G44">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="G44">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="B45" s="20">
-        <f t="array" ref="B45">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="B45">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="C45" s="20">
-        <f t="array" ref="C45">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="C45">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="D45" s="20">
-        <f t="array" ref="D45">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="D45">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="E45" s="21">
-        <f t="array" ref="E45">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="E45">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="F45" s="20">
-        <f t="array" ref="F45">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="F45">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="G45" s="20">
-        <f t="array" ref="G45">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="G45">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="B46" s="22">
-        <f t="array" ref="B46">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="B46">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="C46" s="22">
-        <f t="array" ref="C46">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="C46">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="D46" s="22">
-        <f t="array" ref="D46">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="D46">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="E46" s="23">
-        <f t="array" ref="E46">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="E46">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="F46" s="22">
-        <f t="array" ref="F46">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="F46">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="G46" s="22">
-        <f t="array" ref="G46">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="G46">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="B47" s="20">
-        <f t="array" ref="B47">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="B47">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="C47" s="20">
-        <f t="array" ref="C47">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="C47">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="D47" s="20">
-        <f t="array" ref="D47">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="D47">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="E47" s="21">
-        <f t="array" ref="E47">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="E47">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="F47" s="20">
-        <f t="array" ref="F47">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="F47">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="G47" s="20">
-        <f t="array" ref="G47">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="G47">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="26" customHeight="1">
       <c r="B48" s="22">
-        <f t="array" ref="B48">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="B48">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="C48" s="22">
-        <f t="array" ref="C48">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="C48">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="D48" s="22">
-        <f t="array" ref="D48">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="D48">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="E48" s="23">
-        <f t="array" ref="E48">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="E48">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="F48" s="22">
-        <f t="array" ref="F48">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="F48">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="G48" s="22">
-        <f t="array" ref="G48">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="G48">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="B49" s="20">
-        <f t="array" ref="B49">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <f t="array" ref="B49">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),9)),"")</f>
         <v/>
       </c>
       <c r="C49" s="20">
-        <f t="array" ref="C49">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <f t="array" ref="C49">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),9)),"")</f>
         <v/>
       </c>
       <c r="D49" s="20">
-        <f t="array" ref="D49">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <f t="array" ref="D49">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),9)),"")</f>
         <v/>
       </c>
       <c r="E49" s="21">
-        <f t="array" ref="E49">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <f t="array" ref="E49">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),9)),"")</f>
         <v/>
       </c>
       <c r="F49" s="20">
-        <f t="array" ref="F49">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <f t="array" ref="F49">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),9)),"")</f>
         <v/>
       </c>
       <c r="G49" s="20">
-        <f t="array" ref="G49">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <f t="array" ref="G49">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),9)),"")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="B50" s="22">
-        <f t="array" ref="B50">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <f t="array" ref="B50">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),10)),"")</f>
         <v/>
       </c>
       <c r="C50" s="22">
-        <f t="array" ref="C50">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <f t="array" ref="C50">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),10)),"")</f>
         <v/>
       </c>
       <c r="D50" s="22">
-        <f t="array" ref="D50">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <f t="array" ref="D50">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),10)),"")</f>
         <v/>
       </c>
       <c r="E50" s="23">
-        <f t="array" ref="E50">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <f t="array" ref="E50">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),10)),"")</f>
         <v/>
       </c>
       <c r="F50" s="22">
-        <f t="array" ref="F50">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <f t="array" ref="F50">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),10)),"")</f>
         <v/>
       </c>
       <c r="G50" s="22">
-        <f t="array" ref="G50">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <f t="array" ref="G50">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),10)),"")</f>
         <v/>
       </c>
     </row>
@@ -1790,6 +1788,11 @@
       <formula>"Critical"</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="C15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=LIST_MEETING_TYPE</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
@@ -1809,24 +1812,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O12"/>
+  <dimension ref="B1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -1861,266 +1862,226 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>The single database. One row = one subject discussed at one meeting. Continuity across meetings is found automatically via Subject + Sub-topic - just add a new row with the same Subject/Sub-topic to continue a topic.</t>
+          <t>The single database. One row per topic, forever - never recreate a row to continue a topic. Each meeting, just update Discussion/Action/Status/Due Date on the topic's existing row and set Last Update Date to today. Add a brand new row only for a topic that has never been raised before.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Meeting ID</t>
+          <t>Subject</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Meeting Date</t>
+          <t>Sub-topic</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>Meeting Type</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>Subject</t>
+          <t>Discussion / Notes</t>
         </is>
       </c>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>Sub-topic</t>
+          <t>Agreed Action</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Due Date</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>Discussion / Notes</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
         <is>
-          <t>Agreed Action</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
-          <t>Due Date</t>
+          <t>Follow-up / Update</t>
         </is>
       </c>
       <c r="K7" s="15" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Added Date</t>
         </is>
       </c>
       <c r="L7" s="15" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Last Update Date</t>
         </is>
       </c>
       <c r="M7" s="15" t="inlineStr">
         <is>
-          <t>Follow-up / Update</t>
-        </is>
-      </c>
-      <c r="N7" s="15" t="inlineStr">
-        <is>
-          <t>Topic Key</t>
-        </is>
-      </c>
-      <c r="O7" s="15" t="inlineStr">
-        <is>
           <t>Overdue?</t>
         </is>
       </c>
     </row>
     <row r="8" ht="50" customHeight="1">
-      <c r="B8" s="20">
-        <f>IF($E8="","","M"&amp;TEXT(ROW()-7,"000"))</f>
-        <v/>
-      </c>
-      <c r="C8" s="16" t="n">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>Engineering confirmed the documents are being finalised.</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>Engineering to issue the documents.</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J8" s="17" t="inlineStr">
+        <is>
+          <t>01-Sep: documents missing, Engineering to provide. 01-Oct: confirmed in progress.</t>
+        </is>
+      </c>
+      <c r="K8" s="16" t="n">
         <v>46266</v>
       </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>Documents missing for the commissioning dossier.</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>Engineering to provide the missing documents.</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="n">
-        <v>46280</v>
-      </c>
-      <c r="K8" s="17" t="inlineStr">
+      <c r="L8" s="16" t="n">
+        <v>46296</v>
+      </c>
+      <c r="M8" s="20">
+        <f>IF($B8="","",IF(AND($H8&lt;&gt;"Closed",$H8&lt;&gt;"Cancelled",$G8&lt;&gt;"",$G8&lt;TODAY()),"Yes","No"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Testing / Results</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Commissioning</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>First functional test results reviewed.</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>Commissioning to issue the test report.</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>46315</v>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M8" s="17" t="inlineStr"/>
-      <c r="N8" s="25">
-        <f>IF($E8="","",$E8&amp;"|"&amp;$F8)</f>
-        <v/>
-      </c>
-      <c r="O8" s="20">
-        <f>IF($E8="","",IF(AND($K8&lt;&gt;"Closed",$K8&lt;&gt;"Cancelled",$J8&lt;&gt;"",$J8&lt;TODAY()),"Yes","No"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="50" customHeight="1">
-      <c r="B9" s="20">
-        <f>IF($E9="","","M"&amp;TEXT(ROW()-7,"000"))</f>
-        <v/>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J9" s="17" t="inlineStr"/>
+      <c r="K9" s="16" t="n">
         <v>46296</v>
       </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>Engineering confirmed the documents are being finalised.</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>Engineering to issue the documents.</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="n">
-        <v>46310</v>
-      </c>
-      <c r="K9" s="17" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="inlineStr">
-        <is>
-          <t>Continued from the 01-Sep meeting - still outstanding.</t>
-        </is>
-      </c>
-      <c r="N9" s="25">
-        <f>IF($E9="","",$E9&amp;"|"&amp;$F9)</f>
-        <v/>
-      </c>
-      <c r="O9" s="20">
-        <f>IF($E9="","",IF(AND($K9&lt;&gt;"Closed",$K9&lt;&gt;"Cancelled",$J9&lt;&gt;"",$J9&lt;TODAY()),"Yes","No"))</f>
+      <c r="L9" s="16" t="n">
+        <v>46296</v>
+      </c>
+      <c r="M9" s="20">
+        <f>IF($B9="","",IF(AND($H9&lt;&gt;"Closed",$H9&lt;&gt;"Cancelled",$G9&lt;&gt;"",$G9&lt;TODAY()),"Yes","No"))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="50" customHeight="1">
-      <c r="B10" s="20">
-        <f>IF($E10="","","M"&amp;TEXT(ROW()-7,"000"))</f>
-        <v/>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>46296</v>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Design / Engineering</t>
+        </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>HSE</t>
         </is>
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>Testing / Results</t>
+          <t>SSOW draft submitted for review.</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>Testing</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>Commissioning</t>
-        </is>
+          <t>HSE to review and approve the SSOW.</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>46285</v>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>First functional test results reviewed.</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="I10" s="17" t="inlineStr">
         <is>
-          <t>Commissioning to issue the test report.</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="n">
-        <v>46315</v>
-      </c>
-      <c r="K10" s="17" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M10" s="17" t="inlineStr"/>
-      <c r="N10" s="25">
-        <f>IF($E10="","",$E10&amp;"|"&amp;$F10)</f>
-        <v/>
-      </c>
-      <c r="O10" s="20">
-        <f>IF($E10="","",IF(AND($K10&lt;&gt;"Closed",$K10&lt;&gt;"Cancelled",$J10&lt;&gt;"",$J10&lt;TODAY()),"Yes","No"))</f>
+      <c r="J10" s="17" t="inlineStr"/>
+      <c r="K10" s="16" t="n">
+        <v>46266</v>
+      </c>
+      <c r="L10" s="16" t="n">
+        <v>46266</v>
+      </c>
+      <c r="M10" s="20">
+        <f>IF($B10="","",IF(AND($H10&lt;&gt;"Closed",$H10&lt;&gt;"Cancelled",$G10&lt;&gt;"",$G10&lt;TODAY()),"Yes","No"))</f>
         <v/>
       </c>
     </row>
@@ -2132,34 +2093,31 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B8:O10">
+  <conditionalFormatting sqref="B8:M10">
     <cfRule type="expression" priority="1" dxfId="1">
-      <formula>AND($K8&lt;&gt;"Closed",$O8="Yes")</formula>
+      <formula>AND($H8&lt;&gt;"Closed",$M8="Yes")</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="2">
-      <formula>$K8="Closed"</formula>
+      <formula>$H8="Closed"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="3">
-      <formula>OR($K8="On Hold",$K8="Cancelled")</formula>
+      <formula>OR($H8="On Hold",$H8="Cancelled")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
-    <dataValidation sqref="D8:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=LIST_MEETING_TYPE</formula1>
-    </dataValidation>
-    <dataValidation sqref="E8:E10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="5">
+    <dataValidation sqref="B8:B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LIST_SUBJECT</formula1>
     </dataValidation>
-    <dataValidation sqref="F8:F10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C8:C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LIST_SUBTOPIC</formula1>
     </dataValidation>
-    <dataValidation sqref="G8:G10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D8:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LIST_OWNER</formula1>
     </dataValidation>
-    <dataValidation sqref="K8:K10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H8:H10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LIST_STATUS</formula1>
     </dataValidation>
-    <dataValidation sqref="L8:L10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I8:I10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LIST_PRIORITY</formula1>
     </dataValidation>
   </dataValidations>
@@ -2182,7 +2140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H49"/>
+  <dimension ref="B1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -2237,7 +2195,7 @@
           <t>Meeting Date:</t>
         </is>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="25">
         <f>'Overview'!$C$5</f>
         <v/>
       </c>
@@ -2246,929 +2204,943 @@
           <t>Meeting Type:</t>
         </is>
       </c>
-      <c r="F5" s="27">
-        <f>IFERROR(INDEX(Meeting_Log[Meeting Type],MATCH($C$5,Meeting_Log[Meeting Date],0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="18" t="inlineStr">
+      <c r="F5" s="26">
+        <f>IFERROR(INDEX(Attendees_Log[Meeting Type],MATCH($C$5,Attendees_Log[Meeting Date],0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Attendees:</t>
+        </is>
+      </c>
+      <c r="C6" s="27">
+        <f>IFERROR(INDEX(Attendees_Log[Attendees],MATCH($C$5,Attendees_Log[Meeting Date],0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>1. FOLLOW-UP FROM PREVIOUS MEETING</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
-      <c r="E7" s="18" t="n"/>
-      <c r="F7" s="18" t="n"/>
-      <c r="G7" s="18" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="19" t="inlineStr">
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="18" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Sub-topic</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>Previous Discussion</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>Previous Action</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>Discussion</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
-        <is>
-          <t>Previous Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="20">
-        <f t="array" ref="B9">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="C9" s="20">
-        <f t="array" ref="C9">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="D9" s="20">
-        <f t="array" ref="D9">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="E9" s="20">
-        <f t="array" ref="E9">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="F9" s="20">
-        <f t="array" ref="F9">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="G9" s="20">
-        <f t="array" ref="G9">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="22">
-        <f t="array" ref="B10">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="C10" s="22">
-        <f t="array" ref="C10">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="D10" s="22">
-        <f t="array" ref="D10">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="E10" s="22">
-        <f t="array" ref="E10">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="F10" s="22">
-        <f t="array" ref="F10">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="G10" s="22">
-        <f t="array" ref="G10">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+      <c r="B10" s="20">
+        <f t="array" ref="B10">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="20">
+        <f t="array" ref="C10">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="20">
+        <f t="array" ref="D10">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="20">
+        <f t="array" ref="E10">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="20">
+        <f t="array" ref="F10">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="20">
+        <f t="array" ref="G10">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="B11" s="20">
-        <f t="array" ref="B11">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="C11" s="20">
-        <f t="array" ref="C11">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="D11" s="20">
-        <f t="array" ref="D11">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="E11" s="20">
-        <f t="array" ref="E11">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="F11" s="20">
-        <f t="array" ref="F11">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="G11" s="20">
-        <f t="array" ref="G11">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+      <c r="B11" s="22">
+        <f t="array" ref="B11">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="C11" s="22">
+        <f t="array" ref="C11">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="22">
+        <f t="array" ref="D11">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="22">
+        <f t="array" ref="E11">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="22">
+        <f t="array" ref="F11">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="22">
+        <f t="array" ref="G11">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="B12" s="22">
-        <f t="array" ref="B12">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="C12" s="22">
-        <f t="array" ref="C12">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="D12" s="22">
-        <f t="array" ref="D12">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="E12" s="22">
-        <f t="array" ref="E12">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="F12" s="22">
-        <f t="array" ref="F12">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="G12" s="22">
-        <f t="array" ref="G12">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+      <c r="B12" s="20">
+        <f t="array" ref="B12">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="20">
+        <f t="array" ref="C12">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="20">
+        <f t="array" ref="D12">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="20">
+        <f t="array" ref="E12">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="20">
+        <f t="array" ref="F12">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="20">
+        <f t="array" ref="G12">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="B13" s="20">
-        <f t="array" ref="B13">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="C13" s="20">
-        <f t="array" ref="C13">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="D13" s="20">
-        <f t="array" ref="D13">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="E13" s="20">
-        <f t="array" ref="E13">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="F13" s="20">
-        <f t="array" ref="F13">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="G13" s="20">
-        <f t="array" ref="G13">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+      <c r="B13" s="22">
+        <f t="array" ref="B13">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="C13" s="22">
+        <f t="array" ref="C13">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="D13" s="22">
+        <f t="array" ref="D13">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="E13" s="22">
+        <f t="array" ref="E13">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="22">
+        <f t="array" ref="F13">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="22">
+        <f t="array" ref="G13">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="B14" s="22">
-        <f t="array" ref="B14">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="C14" s="22">
-        <f t="array" ref="C14">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="D14" s="22">
-        <f t="array" ref="D14">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="E14" s="22">
-        <f t="array" ref="E14">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="F14" s="22">
-        <f t="array" ref="F14">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="G14" s="22">
-        <f t="array" ref="G14">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+      <c r="B14" s="20">
+        <f t="array" ref="B14">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="20">
+        <f t="array" ref="C14">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="20">
+        <f t="array" ref="D14">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="20">
+        <f t="array" ref="E14">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="20">
+        <f t="array" ref="F14">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="20">
+        <f t="array" ref="G14">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="B15" s="20">
-        <f t="array" ref="B15">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="C15" s="20">
-        <f t="array" ref="C15">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="20">
-        <f t="array" ref="D15">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="E15" s="20">
-        <f t="array" ref="E15">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="F15" s="20">
-        <f t="array" ref="F15">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="G15" s="20">
-        <f t="array" ref="G15">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+      <c r="B15" s="22">
+        <f t="array" ref="B15">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="C15" s="22">
+        <f t="array" ref="C15">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="22">
+        <f t="array" ref="D15">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="E15" s="22">
+        <f t="array" ref="E15">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="22">
+        <f t="array" ref="F15">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="22">
+        <f t="array" ref="G15">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="B16" s="22">
-        <f t="array" ref="B16">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="C16" s="22">
-        <f t="array" ref="C16">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="22">
-        <f t="array" ref="D16">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="E16" s="22">
-        <f t="array" ref="E16">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="F16" s="22">
-        <f t="array" ref="F16">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="22">
-        <f t="array" ref="G16">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B16" s="20">
+        <f t="array" ref="B16">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="C16" s="20">
+        <f t="array" ref="C16">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="20">
+        <f t="array" ref="D16">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="20">
+        <f t="array" ref="E16">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="20">
+        <f t="array" ref="F16">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="20">
+        <f t="array" ref="G16">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="22">
+        <f t="array" ref="B17">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="C17" s="22">
+        <f t="array" ref="C17">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="22">
+        <f t="array" ref="D17">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="22">
+        <f t="array" ref="E17">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="22">
+        <f t="array" ref="F17">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="22">
+        <f t="array" ref="G17">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>2. NEW TOPICS</t>
         </is>
       </c>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="18" t="n"/>
-      <c r="E18" s="18" t="n"/>
-      <c r="F18" s="18" t="n"/>
-      <c r="G18" s="18" t="n"/>
-      <c r="H18" s="18" t="n"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="19" t="inlineStr">
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="18" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>Sub-topic</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>Discussion / Notes</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="E20" s="19" t="inlineStr">
         <is>
           <t>Agreed Action</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G20" s="19" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="H19" s="19" t="inlineStr">
+      <c r="H20" s="19" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="B20" s="20">
-        <f t="array" ref="B20">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="C20" s="20">
-        <f t="array" ref="C20">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="D20" s="20">
-        <f t="array" ref="D20">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="E20" s="20">
-        <f t="array" ref="E20">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="F20" s="20">
-        <f t="array" ref="F20">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="G20" s="21">
-        <f t="array" ref="G20">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="20">
-        <f t="array" ref="H20">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-    </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="B21" s="22">
-        <f t="array" ref="B21">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="C21" s="22">
-        <f t="array" ref="C21">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="D21" s="22">
-        <f t="array" ref="D21">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="E21" s="22">
-        <f t="array" ref="E21">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="F21" s="22">
-        <f t="array" ref="F21">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="G21" s="23">
-        <f t="array" ref="G21">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="22">
-        <f t="array" ref="H21">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+      <c r="B21" s="20">
+        <f t="array" ref="B21">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="20">
+        <f t="array" ref="C21">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="20">
+        <f t="array" ref="D21">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="20">
+        <f t="array" ref="E21">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="20">
+        <f t="array" ref="F21">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="21">
+        <f t="array" ref="G21">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="20">
+        <f t="array" ref="H21">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="B22" s="20">
-        <f t="array" ref="B22">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="C22" s="20">
-        <f t="array" ref="C22">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="D22" s="20">
-        <f t="array" ref="D22">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="E22" s="20">
-        <f t="array" ref="E22">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="F22" s="20">
-        <f t="array" ref="F22">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="G22" s="21">
-        <f t="array" ref="G22">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="20">
-        <f t="array" ref="H22">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+      <c r="B22" s="22">
+        <f t="array" ref="B22">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="C22" s="22">
+        <f t="array" ref="C22">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="22">
+        <f t="array" ref="D22">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="22">
+        <f t="array" ref="E22">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="22">
+        <f t="array" ref="F22">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="23">
+        <f t="array" ref="G22">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="22">
+        <f t="array" ref="H22">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="B23" s="22">
-        <f t="array" ref="B23">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="C23" s="22">
-        <f t="array" ref="C23">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="D23" s="22">
-        <f t="array" ref="D23">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="E23" s="22">
-        <f t="array" ref="E23">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="F23" s="22">
-        <f t="array" ref="F23">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="G23" s="23">
-        <f t="array" ref="G23">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="22">
-        <f t="array" ref="H23">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+      <c r="B23" s="20">
+        <f t="array" ref="B23">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="20">
+        <f t="array" ref="C23">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="20">
+        <f t="array" ref="D23">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="20">
+        <f t="array" ref="E23">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="20">
+        <f t="array" ref="F23">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="21">
+        <f t="array" ref="G23">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="20">
+        <f t="array" ref="H23">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="B24" s="20">
-        <f t="array" ref="B24">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="C24" s="20">
-        <f t="array" ref="C24">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="D24" s="20">
-        <f t="array" ref="D24">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="E24" s="20">
-        <f t="array" ref="E24">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="20">
-        <f t="array" ref="F24">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="21">
-        <f t="array" ref="G24">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="20">
-        <f t="array" ref="H24">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+      <c r="B24" s="22">
+        <f t="array" ref="B24">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="C24" s="22">
+        <f t="array" ref="C24">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="D24" s="22">
+        <f t="array" ref="D24">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="22">
+        <f t="array" ref="E24">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="22">
+        <f t="array" ref="F24">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="23">
+        <f t="array" ref="G24">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="22">
+        <f t="array" ref="H24">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="B25" s="22">
-        <f t="array" ref="B25">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="C25" s="22">
-        <f t="array" ref="C25">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="D25" s="22">
-        <f t="array" ref="D25">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="E25" s="22">
-        <f t="array" ref="E25">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="22">
-        <f t="array" ref="F25">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="23">
-        <f t="array" ref="G25">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="22">
-        <f t="array" ref="H25">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B25" s="20">
+        <f t="array" ref="B25">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="C25" s="20">
+        <f t="array" ref="C25">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="D25" s="20">
+        <f t="array" ref="D25">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="20">
+        <f t="array" ref="E25">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="20">
+        <f t="array" ref="F25">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="21">
+        <f t="array" ref="G25">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="20">
+        <f t="array" ref="H25">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="B26" s="22">
+        <f t="array" ref="B26">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="22">
+        <f t="array" ref="C26">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="22">
+        <f t="array" ref="D26">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="22">
+        <f t="array" ref="E26">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="22">
+        <f t="array" ref="F26">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="23">
+        <f t="array" ref="G26">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="22">
+        <f t="array" ref="H26">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>3. ACTION SUMMARY</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n"/>
-      <c r="D27" s="18" t="n"/>
-      <c r="E27" s="18" t="n"/>
-      <c r="F27" s="18" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="19" t="inlineStr">
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="C28" s="19" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="D28" s="19" t="inlineStr">
+      <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="E28" s="19" t="inlineStr">
+      <c r="E29" s="19" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="B29" s="20">
-        <f t="array" ref="B29">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="C29" s="20">
-        <f t="array" ref="C29">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="D29" s="21">
-        <f t="array" ref="D29">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="E29" s="20">
-        <f t="array" ref="E29">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="20">
-        <f t="array" ref="F29">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-    </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="B30" s="22">
-        <f t="array" ref="B30">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="C30" s="22">
-        <f t="array" ref="C30">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="D30" s="23">
-        <f t="array" ref="D30">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="E30" s="22">
-        <f t="array" ref="E30">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="F30" s="22">
-        <f t="array" ref="F30">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+      <c r="B30" s="20">
+        <f t="array" ref="B30">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="20">
+        <f t="array" ref="C30">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="21">
+        <f t="array" ref="D30">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="20">
+        <f t="array" ref="E30">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="20">
+        <f t="array" ref="F30">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="B31" s="20">
-        <f t="array" ref="B31">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="C31" s="20">
-        <f t="array" ref="C31">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="D31" s="21">
-        <f t="array" ref="D31">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="E31" s="20">
-        <f t="array" ref="E31">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="F31" s="20">
-        <f t="array" ref="F31">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+      <c r="B31" s="22">
+        <f t="array" ref="B31">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="C31" s="22">
+        <f t="array" ref="C31">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="23">
+        <f t="array" ref="D31">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="22">
+        <f t="array" ref="E31">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="22">
+        <f t="array" ref="F31">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="B32" s="22">
-        <f t="array" ref="B32">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="C32" s="22">
-        <f t="array" ref="C32">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="D32" s="23">
-        <f t="array" ref="D32">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="E32" s="22">
-        <f t="array" ref="E32">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="22">
-        <f t="array" ref="F32">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+      <c r="B32" s="20">
+        <f t="array" ref="B32">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="20">
+        <f t="array" ref="C32">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="21">
+        <f t="array" ref="D32">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="20">
+        <f t="array" ref="E32">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="20">
+        <f t="array" ref="F32">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="B33" s="20">
-        <f t="array" ref="B33">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="C33" s="20">
-        <f t="array" ref="C33">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="D33" s="21">
-        <f t="array" ref="D33">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="E33" s="20">
-        <f t="array" ref="E33">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="F33" s="20">
-        <f t="array" ref="F33">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+      <c r="B33" s="22">
+        <f t="array" ref="B33">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="22">
+        <f t="array" ref="C33">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="23">
+        <f t="array" ref="D33">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="22">
+        <f t="array" ref="E33">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="22">
+        <f t="array" ref="F33">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="B34" s="22">
-        <f t="array" ref="B34">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="C34" s="22">
-        <f t="array" ref="C34">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="D34" s="23">
-        <f t="array" ref="D34">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="22">
-        <f t="array" ref="E34">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="F34" s="22">
-        <f t="array" ref="F34">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+      <c r="B34" s="20">
+        <f t="array" ref="B34">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="20">
+        <f t="array" ref="C34">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="21">
+        <f t="array" ref="D34">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="20">
+        <f t="array" ref="E34">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="20">
+        <f t="array" ref="F34">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="B35" s="20">
-        <f t="array" ref="B35">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="C35" s="20">
-        <f t="array" ref="C35">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="D35" s="21">
-        <f t="array" ref="D35">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="E35" s="20">
-        <f t="array" ref="E35">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="20">
-        <f t="array" ref="F35">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+      <c r="B35" s="22">
+        <f t="array" ref="B35">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="22">
+        <f t="array" ref="C35">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="23">
+        <f t="array" ref="D35">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="22">
+        <f t="array" ref="E35">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="22">
+        <f t="array" ref="F35">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
-      <c r="B36" s="22">
-        <f t="array" ref="B36">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="C36" s="22">
-        <f t="array" ref="C36">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="D36" s="23">
-        <f t="array" ref="D36">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="E36" s="22">
-        <f t="array" ref="E36">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="22">
-        <f t="array" ref="F36">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B36" s="20">
+        <f t="array" ref="B36">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="20">
+        <f t="array" ref="C36">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="21">
+        <f t="array" ref="D36">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="20">
+        <f t="array" ref="E36">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="20">
+        <f t="array" ref="F36">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="B37" s="22">
+        <f t="array" ref="B37">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="22">
+        <f t="array" ref="C37">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="23">
+        <f t="array" ref="D37">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="22">
+        <f t="array" ref="E37">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="22">
+        <f t="array" ref="F37">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="B39" s="18" t="inlineStr">
         <is>
           <t>4. OPEN / OVERDUE ACTIONS</t>
         </is>
       </c>
-      <c r="C38" s="18" t="n"/>
-      <c r="D38" s="18" t="n"/>
-      <c r="E38" s="18" t="n"/>
-      <c r="F38" s="18" t="n"/>
-    </row>
-    <row r="39">
-      <c r="B39" s="19" t="inlineStr">
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="18" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="C39" s="19" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D39" s="19" t="inlineStr">
+      <c r="D40" s="19" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E39" s="19" t="inlineStr">
+      <c r="E40" s="19" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="F39" s="19" t="inlineStr">
+      <c r="F40" s="19" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="26" customHeight="1">
-      <c r="B40" s="20">
-        <f t="array" ref="B40">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="20">
-        <f t="array" ref="C40">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="20">
-        <f t="array" ref="D40">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="21">
-        <f t="array" ref="E40">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="20">
-        <f t="array" ref="F40">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
-        <v/>
-      </c>
-    </row>
     <row r="41" ht="26" customHeight="1">
-      <c r="B41" s="22">
-        <f t="array" ref="B41">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="C41" s="22">
-        <f t="array" ref="C41">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="D41" s="22">
-        <f t="array" ref="D41">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="E41" s="23">
-        <f t="array" ref="E41">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="F41" s="22">
-        <f t="array" ref="F41">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+      <c r="B41" s="20">
+        <f t="array" ref="B41">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="20">
+        <f t="array" ref="C41">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="20">
+        <f t="array" ref="D41">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="21">
+        <f t="array" ref="E41">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="20">
+        <f t="array" ref="F41">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
-      <c r="B42" s="20">
-        <f t="array" ref="B42">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="C42" s="20">
-        <f t="array" ref="C42">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="D42" s="20">
-        <f t="array" ref="D42">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="E42" s="21">
-        <f t="array" ref="E42">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="20">
-        <f t="array" ref="F42">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+      <c r="B42" s="22">
+        <f t="array" ref="B42">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="C42" s="22">
+        <f t="array" ref="C42">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="D42" s="22">
+        <f t="array" ref="D42">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="23">
+        <f t="array" ref="E42">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="22">
+        <f t="array" ref="F42">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="B43" s="22">
-        <f t="array" ref="B43">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="C43" s="22">
-        <f t="array" ref="C43">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="D43" s="22">
-        <f t="array" ref="D43">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="E43" s="23">
-        <f t="array" ref="E43">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="22">
-        <f t="array" ref="F43">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+      <c r="B43" s="20">
+        <f t="array" ref="B43">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="20">
+        <f t="array" ref="C43">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="20">
+        <f t="array" ref="D43">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="21">
+        <f t="array" ref="E43">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="20">
+        <f t="array" ref="F43">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
-      <c r="B44" s="20">
-        <f t="array" ref="B44">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="C44" s="20">
-        <f t="array" ref="C44">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="D44" s="20">
-        <f t="array" ref="D44">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="E44" s="21">
-        <f t="array" ref="E44">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="F44" s="20">
-        <f t="array" ref="F44">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+      <c r="B44" s="22">
+        <f t="array" ref="B44">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="22">
+        <f t="array" ref="C44">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="22">
+        <f t="array" ref="D44">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="23">
+        <f t="array" ref="E44">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="22">
+        <f t="array" ref="F44">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
-      <c r="B45" s="22">
-        <f t="array" ref="B45">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="C45" s="22">
-        <f t="array" ref="C45">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="D45" s="22">
-        <f t="array" ref="D45">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="23">
-        <f t="array" ref="E45">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="22">
-        <f t="array" ref="F45">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+      <c r="B45" s="20">
+        <f t="array" ref="B45">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="20">
+        <f t="array" ref="C45">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="D45" s="20">
+        <f t="array" ref="D45">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="21">
+        <f t="array" ref="E45">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="20">
+        <f t="array" ref="F45">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
-      <c r="B46" s="20">
-        <f t="array" ref="B46">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="C46" s="20">
-        <f t="array" ref="C46">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="D46" s="20">
-        <f t="array" ref="D46">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="E46" s="21">
-        <f t="array" ref="E46">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="F46" s="20">
-        <f t="array" ref="F46">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+      <c r="B46" s="22">
+        <f t="array" ref="B46">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="C46" s="22">
+        <f t="array" ref="C46">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="22">
+        <f t="array" ref="D46">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="23">
+        <f t="array" ref="E46">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="22">
+        <f t="array" ref="F46">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="26" customHeight="1">
-      <c r="B47" s="22">
-        <f t="array" ref="B47">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="C47" s="22">
-        <f t="array" ref="C47">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="D47" s="22">
-        <f t="array" ref="D47">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="E47" s="23">
-        <f t="array" ref="E47">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="F47" s="22">
-        <f t="array" ref="F47">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="24" t="inlineStr">
+      <c r="B47" s="20">
+        <f t="array" ref="B47">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="C47" s="20">
+        <f t="array" ref="C47">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="D47" s="20">
+        <f t="array" ref="D47">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="21">
+        <f t="array" ref="E47">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="20">
+        <f t="array" ref="F47">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="B48" s="22">
+        <f t="array" ref="B48">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="C48" s="22">
+        <f t="array" ref="C48">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="D48" s="22">
+        <f t="array" ref="D48">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="E48" s="23">
+        <f t="array" ref="E48">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="F48" s="22">
+        <f t="array" ref="F48">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="24" t="inlineStr">
         <is>
           <t>Legend: Blue = fill in yourself | Black = automatic, do not overtype | Grey columns = automation helpers, leave untouched | New row: type directly below the table and Excel extends it automatically</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C6:H6"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>

--- a/HBX Commissioning Review.xlsx
+++ b/HBX Commissioning Review.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Meeting Log" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Meeting Report" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lists &amp; Config" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="History" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Meeting Report" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Lists &amp; Config" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="LIST_SUBJECT">'Lists &amp; Config'!$B$6:$B$16</definedName>
@@ -444,6 +445,20 @@
 </table>
 </file>
 
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="History_Log" displayName="History_Log" ref="B7:F10" headerRowCount="1">
+  <autoFilter ref="B7:F10"/>
+  <tableColumns count="5">
+    <tableColumn id="2" name="Meeting Date"/>
+    <tableColumn id="3" name="Subject"/>
+    <tableColumn id="4" name="Sub-topic"/>
+    <tableColumn id="5" name="Update / Discussion"/>
+    <tableColumn id="6" name="Decision"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -766,10 +781,15 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Meeting Report</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Lists &amp; Config</t>
         </is>
@@ -1798,10 +1818,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1843,10 +1864,15 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Meeting Report</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Lists &amp; Config</t>
         </is>
@@ -1862,7 +1888,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>The single database. One row per topic, forever - never recreate a row to continue a topic. Each meeting, just update Discussion/Action/Status/Due Date on the topic's existing row and set Last Update Date to today. Add a brand new row only for a topic that has never been raised before.</t>
+          <t>The current state. One row per topic, forever - never recreate a row to continue a topic. Each meeting: update Discussion/Action/Status/Due Date on the topic's existing row, set Last Update Date to today, then add one line to History with what was actually said - that keeps every past meeting's record without retyping anything here. Add a brand new row only for a topic that has never been raised before.</t>
         </is>
       </c>
     </row>
@@ -2126,15 +2152,206 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.5" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Meeting Log</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Meeting Report</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Lists &amp; Config</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>The full past record. Every time you touch a topic in Meeting Log, add one line here too - date, topic, what was said or decided. Never edit or delete a past row; just keep adding new ones underneath.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Meeting Date</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Sub-topic</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Update / Discussion</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="16" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>Documents missing for the commissioning dossier.</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>Engineering to provide the missing documents by 15-Sep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="16" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>Engineering confirmed the documents are being finalised.</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>New target date 15-Oct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="B10" s="16" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Testing / Results</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>First functional test results reviewed.</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>Commissioning to issue the test report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>Legend: Blue = fill in yourself | Black = automatic, do not overtype | Grey columns = automation helpers, leave untouched | New row: type directly below the table and Excel extends it automatically</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="C8:C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=LIST_SUBJECT</formula1>
+    </dataValidation>
+    <dataValidation sqref="D8:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=LIST_SUBTOPIC</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId5"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2164,12 +2381,17 @@
           <t>Meeting Log</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Meeting Report</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Lists &amp; Config</t>
         </is>
@@ -2705,214 +2927,176 @@
     <row r="28" ht="22" customHeight="1">
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>3. ACTION SUMMARY</t>
+          <t>3. DISCUSSION LOG FOR THIS MEETING</t>
         </is>
       </c>
       <c r="C28" s="18" t="n"/>
       <c r="D28" s="18" t="n"/>
       <c r="E28" s="18" t="n"/>
-      <c r="F28" s="18" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Subject</t>
         </is>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Sub-topic</t>
         </is>
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
-          <t>Due Date</t>
+          <t>Update / Discussion</t>
         </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>Priority</t>
+          <t>Decision</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="B30" s="20">
-        <f t="array" ref="B30">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="B30">IFERROR(INDEX(History_Log[Subject],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="C30" s="20">
-        <f t="array" ref="C30">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="D30" s="21">
-        <f t="array" ref="D30">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="C30">IFERROR(INDEX(History_Log[Sub-topic],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="20">
+        <f t="array" ref="D30">IFERROR(INDEX(History_Log[Update / Discussion],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="E30" s="20">
-        <f t="array" ref="E30">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
-        <v/>
-      </c>
-      <c r="F30" s="20">
-        <f t="array" ref="F30">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="E30">IFERROR(INDEX(History_Log[Decision],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="B31" s="22">
-        <f t="array" ref="B31">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="B31">IFERROR(INDEX(History_Log[Subject],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="C31" s="22">
-        <f t="array" ref="C31">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="D31" s="23">
-        <f t="array" ref="D31">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="C31">IFERROR(INDEX(History_Log[Sub-topic],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="22">
+        <f t="array" ref="D31">IFERROR(INDEX(History_Log[Update / Discussion],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="E31" s="22">
-        <f t="array" ref="E31">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
-        <v/>
-      </c>
-      <c r="F31" s="22">
-        <f t="array" ref="F31">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="E31">IFERROR(INDEX(History_Log[Decision],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="B32" s="20">
-        <f t="array" ref="B32">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="B32">IFERROR(INDEX(History_Log[Subject],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="C32" s="20">
-        <f t="array" ref="C32">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="D32" s="21">
-        <f t="array" ref="D32">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="C32">IFERROR(INDEX(History_Log[Sub-topic],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="20">
+        <f t="array" ref="D32">IFERROR(INDEX(History_Log[Update / Discussion],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="E32" s="20">
-        <f t="array" ref="E32">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="20">
-        <f t="array" ref="F32">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="E32">IFERROR(INDEX(History_Log[Decision],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="B33" s="22">
-        <f t="array" ref="B33">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="B33">IFERROR(INDEX(History_Log[Subject],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="C33" s="22">
-        <f t="array" ref="C33">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="D33" s="23">
-        <f t="array" ref="D33">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="C33">IFERROR(INDEX(History_Log[Sub-topic],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="22">
+        <f t="array" ref="D33">IFERROR(INDEX(History_Log[Update / Discussion],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="E33" s="22">
-        <f t="array" ref="E33">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
-        <v/>
-      </c>
-      <c r="F33" s="22">
-        <f t="array" ref="F33">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="E33">IFERROR(INDEX(History_Log[Decision],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="B34" s="20">
-        <f t="array" ref="B34">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="B34">IFERROR(INDEX(History_Log[Subject],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="C34" s="20">
-        <f t="array" ref="C34">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="D34" s="21">
-        <f t="array" ref="D34">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="C34">IFERROR(INDEX(History_Log[Sub-topic],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="20">
+        <f t="array" ref="D34">IFERROR(INDEX(History_Log[Update / Discussion],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="E34" s="20">
-        <f t="array" ref="E34">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
-        <v/>
-      </c>
-      <c r="F34" s="20">
-        <f t="array" ref="F34">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="E34">IFERROR(INDEX(History_Log[Decision],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="B35" s="22">
-        <f t="array" ref="B35">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="B35">IFERROR(INDEX(History_Log[Subject],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="C35" s="22">
-        <f t="array" ref="C35">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="D35" s="23">
-        <f t="array" ref="D35">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="C35">IFERROR(INDEX(History_Log[Sub-topic],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="22">
+        <f t="array" ref="D35">IFERROR(INDEX(History_Log[Update / Discussion],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="E35" s="22">
-        <f t="array" ref="E35">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="22">
-        <f t="array" ref="F35">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="E35">IFERROR(INDEX(History_Log[Decision],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="B36" s="20">
-        <f t="array" ref="B36">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="B36">IFERROR(INDEX(History_Log[Subject],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="C36" s="20">
-        <f t="array" ref="C36">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="D36" s="21">
-        <f t="array" ref="D36">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="C36">IFERROR(INDEX(History_Log[Sub-topic],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="20">
+        <f t="array" ref="D36">IFERROR(INDEX(History_Log[Update / Discussion],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="E36" s="20">
-        <f t="array" ref="E36">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="20">
-        <f t="array" ref="F36">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="E36">IFERROR(INDEX(History_Log[Decision],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="B37" s="22">
-        <f t="array" ref="B37">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="B37">IFERROR(INDEX(History_Log[Subject],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="C37" s="22">
-        <f t="array" ref="C37">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="D37" s="23">
-        <f t="array" ref="D37">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="C37">IFERROR(INDEX(History_Log[Sub-topic],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="22">
+        <f t="array" ref="D37">IFERROR(INDEX(History_Log[Update / Discussion],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="E37" s="22">
-        <f t="array" ref="E37">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="22">
-        <f t="array" ref="F37">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="E37">IFERROR(INDEX(History_Log[Decision],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
     </row>
@@ -3146,12 +3330,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3182,10 +3367,15 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Meeting Report</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lists &amp; Config</t>
         </is>
@@ -3515,6 +3705,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/HBX Commissioning Review.xlsx
+++ b/HBX Commissioning Review.xlsx
@@ -425,9 +425,9 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Meeting_Log" displayName="Meeting_Log" ref="B7:M10" headerRowCount="1">
-  <autoFilter ref="B7:M10"/>
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Meeting_Log" displayName="Meeting_Log" ref="B7:L10" headerRowCount="1">
+  <autoFilter ref="B7:L10"/>
+  <tableColumns count="11">
     <tableColumn id="2" name="Subject"/>
     <tableColumn id="3" name="Sub-topic"/>
     <tableColumn id="4" name="Owner"/>
@@ -436,10 +436,9 @@
     <tableColumn id="7" name="Due Date"/>
     <tableColumn id="8" name="Status"/>
     <tableColumn id="9" name="Priority"/>
-    <tableColumn id="10" name="Follow-up / Update"/>
-    <tableColumn id="11" name="Added Date"/>
-    <tableColumn id="12" name="Last Update Date"/>
-    <tableColumn id="13" name="Overdue?"/>
+    <tableColumn id="10" name="Added Date"/>
+    <tableColumn id="11" name="Last Update Date"/>
+    <tableColumn id="12" name="Overdue?"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1833,22 +1832,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:M12"/>
+  <dimension ref="B1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -1935,20 +1933,15 @@
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
-          <t>Follow-up / Update</t>
+          <t>Added Date</t>
         </is>
       </c>
       <c r="K7" s="15" t="inlineStr">
         <is>
-          <t>Added Date</t>
+          <t>Last Update Date</t>
         </is>
       </c>
       <c r="L7" s="15" t="inlineStr">
-        <is>
-          <t>Last Update Date</t>
-        </is>
-      </c>
-      <c r="M7" s="15" t="inlineStr">
         <is>
           <t>Overdue?</t>
         </is>
@@ -1993,18 +1986,13 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t>01-Sep: documents missing, Engineering to provide. 01-Oct: confirmed in progress.</t>
-        </is>
+      <c r="J8" s="16" t="n">
+        <v>46266</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>46266</v>
-      </c>
-      <c r="L8" s="16" t="n">
         <v>46296</v>
       </c>
-      <c r="M8" s="20">
+      <c r="L8" s="20">
         <f>IF($B8="","",IF(AND($H8&lt;&gt;"Closed",$H8&lt;&gt;"Cancelled",$G8&lt;&gt;"",$G8&lt;TODAY()),"Yes","No"))</f>
         <v/>
       </c>
@@ -2048,14 +2036,13 @@
           <t>High</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr"/>
+      <c r="J9" s="16" t="n">
+        <v>46296</v>
+      </c>
       <c r="K9" s="16" t="n">
         <v>46296</v>
       </c>
-      <c r="L9" s="16" t="n">
-        <v>46296</v>
-      </c>
-      <c r="M9" s="20">
+      <c r="L9" s="20">
         <f>IF($B9="","",IF(AND($H9&lt;&gt;"Closed",$H9&lt;&gt;"Cancelled",$G9&lt;&gt;"",$G9&lt;TODAY()),"Yes","No"))</f>
         <v/>
       </c>
@@ -2099,14 +2086,13 @@
           <t>High</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr"/>
+      <c r="J10" s="16" t="n">
+        <v>46266</v>
+      </c>
       <c r="K10" s="16" t="n">
         <v>46266</v>
       </c>
-      <c r="L10" s="16" t="n">
-        <v>46266</v>
-      </c>
-      <c r="M10" s="20">
+      <c r="L10" s="20">
         <f>IF($B10="","",IF(AND($H10&lt;&gt;"Closed",$H10&lt;&gt;"Cancelled",$G10&lt;&gt;"",$G10&lt;TODAY()),"Yes","No"))</f>
         <v/>
       </c>
@@ -2119,9 +2105,9 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B8:M10">
+  <conditionalFormatting sqref="B8:L10">
     <cfRule type="expression" priority="1" dxfId="1">
-      <formula>AND($H8&lt;&gt;"Closed",$M8="Yes")</formula>
+      <formula>AND($H8&lt;&gt;"Closed",$L8="Yes")</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="2">
       <formula>$H8="Closed"</formula>

--- a/HBX Commissioning Review.xlsx
+++ b/HBX Commissioning Review.xlsx
@@ -16,10 +16,9 @@
   <definedNames>
     <definedName name="LIST_SUBJECT">'Lists &amp; Config'!$B$6:$B$16</definedName>
     <definedName name="LIST_SUBTOPIC">'Lists &amp; Config'!$C$6:$C$20</definedName>
-    <definedName name="LIST_OWNER">'Lists &amp; Config'!$D$6:$D$14</definedName>
-    <definedName name="LIST_STATUS">'Lists &amp; Config'!$E$6:$E$10</definedName>
-    <definedName name="LIST_PRIORITY">'Lists &amp; Config'!$F$6:$F$9</definedName>
-    <definedName name="LIST_MEETING_TYPE">'Lists &amp; Config'!$G$6:$G$8</definedName>
+    <definedName name="LIST_STATUS">'Lists &amp; Config'!$D$6:$D$10</definedName>
+    <definedName name="LIST_PRIORITY">'Lists &amp; Config'!$E$6:$E$9</definedName>
+    <definedName name="LIST_MEETING_TYPE">'Lists &amp; Config'!$F$6:$F$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1960,22 +1959,20 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>J. Smith</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>Engineering confirmed the documents are being finalised.</t>
+          <t>Document A cannot be validated - missing the calibration certificate.</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>Engineering to issue the documents.</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>46310</v>
-      </c>
+          <t>J. Smith to retrieve the missing calibration certificate.</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="n"/>
       <c r="H8" s="17" t="inlineStr">
         <is>
           <t>In Progress</t>
@@ -2010,7 +2007,7 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>Commissioning</t>
+          <t>A. Brown</t>
         </is>
       </c>
       <c r="E9" s="17" t="inlineStr">
@@ -2020,7 +2017,7 @@
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>Commissioning to issue the test report.</t>
+          <t>A. Brown to issue the test report.</t>
         </is>
       </c>
       <c r="G9" s="16" t="n">
@@ -2060,7 +2057,7 @@
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>HSE</t>
+          <t>R. Taylor</t>
         </is>
       </c>
       <c r="E10" s="17" t="inlineStr">
@@ -2070,12 +2067,10 @@
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>HSE to review and approve the SSOW.</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>46285</v>
-      </c>
+          <t>R. Taylor to review and approve the SSOW.</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="n"/>
       <c r="H10" s="17" t="inlineStr">
         <is>
           <t>Open</t>
@@ -2116,15 +2111,12 @@
       <formula>OR($H8="On Hold",$H8="Cancelled")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
+  <dataValidations count="4">
     <dataValidation sqref="B8:B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LIST_SUBJECT</formula1>
     </dataValidation>
     <dataValidation sqref="C8:C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LIST_SUBTOPIC</formula1>
-    </dataValidation>
-    <dataValidation sqref="D8:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=LIST_OWNER</formula1>
     </dataValidation>
     <dataValidation sqref="H8:H10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LIST_STATUS</formula1>
@@ -2248,12 +2240,12 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>Documents missing for the commissioning dossier.</t>
+          <t>Document A cannot be validated - the calibration certificate is missing.</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>Engineering to provide the missing documents by 15-Sep.</t>
+          <t>J. Smith to retrieve the missing certificate.</t>
         </is>
       </c>
     </row>
@@ -2273,12 +2265,12 @@
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>Engineering confirmed the documents are being finalised.</t>
+          <t>Still waiting on the calibration certificate from the supplier.</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>New target date 15-Oct.</t>
+          <t>No change - carried to next meeting.</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2295,7 @@
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>Commissioning to issue the test report.</t>
+          <t>A. Brown to issue the test report by 20-Oct.</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G22"/>
+  <dimension ref="B1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -3337,7 +3329,6 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -3394,20 +3385,15 @@
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="G5" s="28" t="inlineStr">
         <is>
           <t>Meeting Type</t>
         </is>
@@ -3426,20 +3412,15 @@
       </c>
       <c r="D6" s="29" t="inlineStr">
         <is>
-          <t>Commissioning</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E6" s="29" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F6" s="29" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G6" s="29" t="inlineStr">
         <is>
           <t>Weekly</t>
         </is>
@@ -3458,20 +3439,15 @@
       </c>
       <c r="D7" s="30" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E7" s="30" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F7" s="30" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G7" s="30" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
@@ -3490,20 +3466,15 @@
       </c>
       <c r="D8" s="29" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E8" s="29" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F8" s="29" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G8" s="29" t="inlineStr">
         <is>
           <t>Ad hoc</t>
         </is>
@@ -3522,15 +3493,10 @@
       </c>
       <c r="D9" s="30" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>On Hold</t>
         </is>
       </c>
       <c r="E9" s="30" t="inlineStr">
-        <is>
-          <t>On Hold</t>
-        </is>
-      </c>
-      <c r="F9" s="30" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -3549,11 +3515,6 @@
       </c>
       <c r="D10" s="29" t="inlineStr">
         <is>
-          <t>HSE</t>
-        </is>
-      </c>
-      <c r="E10" s="29" t="inlineStr">
-        <is>
           <t>Cancelled</t>
         </is>
       </c>
@@ -3569,11 +3530,6 @@
           <t>Punch List</t>
         </is>
       </c>
-      <c r="D11" s="30" t="inlineStr">
-        <is>
-          <t>Planning</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="B12" s="29" t="inlineStr">
@@ -3586,11 +3542,6 @@
           <t>Documentation</t>
         </is>
       </c>
-      <c r="D12" s="29" t="inlineStr">
-        <is>
-          <t>Document Control</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="B13" s="30" t="inlineStr">
@@ -3603,11 +3554,6 @@
           <t>NCR / Quality</t>
         </is>
       </c>
-      <c r="D13" s="30" t="inlineStr">
-        <is>
-          <t>Project Team</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="B14" s="29" t="inlineStr">
@@ -3618,11 +3564,6 @@
       <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Design / Engineering</t>
-        </is>
-      </c>
-      <c r="D14" s="29" t="inlineStr">
-        <is>
-          <t>Other</t>
         </is>
       </c>
     </row>

--- a/HBX Commissioning Review.xlsx
+++ b/HBX Commissioning Review.xlsx
@@ -9,9 +9,8 @@
   <sheets>
     <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Meeting Log" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="History" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Meeting Report" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Lists &amp; Config" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Meeting Report" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lists &amp; Config" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="LIST_SUBJECT">'Lists &amp; Config'!$B$6:$B$16</definedName>
@@ -30,7 +29,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd-mmm-yy"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,6 +88,12 @@
       <name val="Arial"/>
       <color rgb="001155CC"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -157,7 +162,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -177,6 +182,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F5FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
     <fill>
@@ -221,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -231,15 +241,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -249,10 +256,13 @@
     <xf numFmtId="1" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -262,8 +272,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -272,15 +282,16 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -424,34 +435,20 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Meeting_Log" displayName="Meeting_Log" ref="B7:L10" headerRowCount="1">
-  <autoFilter ref="B7:L10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Meeting_Log" displayName="Meeting_Log" ref="B7:L11" headerRowCount="1">
+  <autoFilter ref="B7:L11"/>
   <tableColumns count="11">
     <tableColumn id="2" name="Subject"/>
     <tableColumn id="3" name="Sub-topic"/>
-    <tableColumn id="4" name="Owner"/>
+    <tableColumn id="4" name="Meeting Date"/>
     <tableColumn id="5" name="Discussion / Notes"/>
     <tableColumn id="6" name="Agreed Action"/>
-    <tableColumn id="7" name="Due Date"/>
-    <tableColumn id="8" name="Status"/>
-    <tableColumn id="9" name="Priority"/>
-    <tableColumn id="10" name="Added Date"/>
-    <tableColumn id="11" name="Last Update Date"/>
+    <tableColumn id="7" name="Owner"/>
+    <tableColumn id="8" name="Due Date"/>
+    <tableColumn id="9" name="Status"/>
+    <tableColumn id="10" name="Priority"/>
+    <tableColumn id="11" name="Topic Key"/>
     <tableColumn id="12" name="Overdue?"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="History_Log" displayName="History_Log" ref="B7:F10" headerRowCount="1">
-  <autoFilter ref="B7:F10"/>
-  <tableColumns count="5">
-    <tableColumn id="2" name="Meeting Date"/>
-    <tableColumn id="3" name="Subject"/>
-    <tableColumn id="4" name="Sub-topic"/>
-    <tableColumn id="5" name="Update / Discussion"/>
-    <tableColumn id="6" name="Decision"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -779,15 +776,10 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Meeting Report</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Meeting Report</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Lists &amp; Config</t>
         </is>
@@ -819,32 +811,32 @@
     </row>
     <row r="8">
       <c r="B8" s="7">
-        <f>SUMPRODUCT((Meeting_Log[Subject]&lt;&gt;""))</f>
+        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5)))</f>
         <v/>
       </c>
       <c r="C8" s="8" t="n"/>
       <c r="E8" s="7">
-        <f>SUMPRODUCT((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"))</f>
+        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"))</f>
         <v/>
       </c>
       <c r="F8" s="8" t="n"/>
       <c r="H8" s="9">
-        <f>SUMPRODUCT((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Overdue?]="Yes"))</f>
+        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Overdue?]="Yes"))</f>
         <v/>
       </c>
       <c r="I8" s="8" t="n"/>
       <c r="K8" s="10">
-        <f>SUMPRODUCT((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]="Closed"))</f>
+        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]="Closed"))</f>
         <v/>
       </c>
       <c r="L8" s="8" t="n"/>
       <c r="N8" s="11">
-        <f>SUMPRODUCT((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5))</f>
+        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"))</f>
         <v/>
       </c>
       <c r="O8" s="8" t="n"/>
       <c r="Q8" s="12">
-        <f>SUMPRODUCT((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5))</f>
+        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0))</f>
         <v/>
       </c>
       <c r="R8" s="8" t="n"/>
@@ -1000,241 +992,241 @@
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="B19" s="20">
-        <f t="array" ref="B19">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="B19">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="C19" s="20">
-        <f t="array" ref="C19">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="C19">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="D19" s="20">
-        <f t="array" ref="D19">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="D19">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="E19" s="20">
-        <f t="array" ref="E19">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="E19">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="F19" s="20">
-        <f t="array" ref="F19">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="F19">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="G19" s="21">
-        <f t="array" ref="G19">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="G19">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="H19" s="20">
-        <f t="array" ref="H19">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="H19">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="B20" s="22">
-        <f t="array" ref="B20">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="B20">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="C20" s="22">
-        <f t="array" ref="C20">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="C20">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="D20" s="22">
-        <f t="array" ref="D20">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="D20">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="E20" s="22">
-        <f t="array" ref="E20">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="E20">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="F20" s="22">
-        <f t="array" ref="F20">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="F20">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="G20" s="23">
-        <f t="array" ref="G20">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="G20">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="H20" s="22">
-        <f t="array" ref="H20">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="H20">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="B21" s="20">
-        <f t="array" ref="B21">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="B21">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="C21" s="20">
-        <f t="array" ref="C21">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="C21">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="D21" s="20">
-        <f t="array" ref="D21">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="D21">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="E21" s="20">
-        <f t="array" ref="E21">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="E21">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="F21" s="20">
-        <f t="array" ref="F21">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="F21">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="G21" s="21">
-        <f t="array" ref="G21">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="G21">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="H21" s="20">
-        <f t="array" ref="H21">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="H21">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="B22" s="22">
-        <f t="array" ref="B22">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="B22">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="C22" s="22">
-        <f t="array" ref="C22">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="C22">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="D22" s="22">
-        <f t="array" ref="D22">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="D22">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="E22" s="22">
-        <f t="array" ref="E22">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="E22">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="F22" s="22">
-        <f t="array" ref="F22">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="F22">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="G22" s="23">
-        <f t="array" ref="G22">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="G22">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="H22" s="22">
-        <f t="array" ref="H22">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="H22">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="B23" s="20">
-        <f t="array" ref="B23">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="B23">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="C23" s="20">
-        <f t="array" ref="C23">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="C23">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="D23" s="20">
-        <f t="array" ref="D23">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="D23">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="E23" s="20">
-        <f t="array" ref="E23">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="E23">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="F23" s="20">
-        <f t="array" ref="F23">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="F23">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="G23" s="21">
-        <f t="array" ref="G23">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="G23">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="H23" s="20">
-        <f t="array" ref="H23">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="H23">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="B24" s="22">
-        <f t="array" ref="B24">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="B24">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="C24" s="22">
-        <f t="array" ref="C24">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="C24">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="D24" s="22">
-        <f t="array" ref="D24">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="D24">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="E24" s="22">
-        <f t="array" ref="E24">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="E24">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="F24" s="22">
-        <f t="array" ref="F24">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="F24">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="G24" s="23">
-        <f t="array" ref="G24">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="G24">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="H24" s="22">
-        <f t="array" ref="H24">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="H24">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="B25" s="20">
-        <f t="array" ref="B25">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="B25">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="C25" s="20">
-        <f t="array" ref="C25">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="C25">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="D25" s="20">
-        <f t="array" ref="D25">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="D25">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="E25" s="20">
-        <f t="array" ref="E25">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="E25">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="F25" s="20">
-        <f t="array" ref="F25">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="F25">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="G25" s="21">
-        <f t="array" ref="G25">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="G25">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="H25" s="20">
-        <f t="array" ref="H25">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="H25">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="B26" s="22">
-        <f t="array" ref="B26">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="B26">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="C26" s="22">
-        <f t="array" ref="C26">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="C26">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="D26" s="22">
-        <f t="array" ref="D26">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="D26">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="E26" s="22">
-        <f t="array" ref="E26">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="E26">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="F26" s="22">
-        <f t="array" ref="F26">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="F26">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="G26" s="23">
-        <f t="array" ref="G26">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="G26">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="H26" s="22">
-        <f t="array" ref="H26">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="H26">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
     </row>
@@ -1290,188 +1282,188 @@
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="B30" s="20">
-        <f t="array" ref="B30">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="B30">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="C30" s="20">
-        <f t="array" ref="C30">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="C30">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="D30" s="20">
-        <f t="array" ref="D30">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="D30">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="E30" s="20">
-        <f t="array" ref="E30">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="E30">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="F30" s="20">
-        <f t="array" ref="F30">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="F30">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="G30" s="21">
-        <f t="array" ref="G30">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="G30">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="H30" s="20">
-        <f t="array" ref="H30">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="H30">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="B31" s="22">
-        <f t="array" ref="B31">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="B31">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="C31" s="22">
-        <f t="array" ref="C31">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="C31">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="D31" s="22">
-        <f t="array" ref="D31">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="D31">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="E31" s="22">
-        <f t="array" ref="E31">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="E31">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="F31" s="22">
-        <f t="array" ref="F31">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="F31">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="G31" s="23">
-        <f t="array" ref="G31">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="G31">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="H31" s="22">
-        <f t="array" ref="H31">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="H31">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="B32" s="20">
-        <f t="array" ref="B32">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="B32">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="C32" s="20">
-        <f t="array" ref="C32">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="C32">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="D32" s="20">
-        <f t="array" ref="D32">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="D32">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="E32" s="20">
-        <f t="array" ref="E32">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="E32">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="F32" s="20">
-        <f t="array" ref="F32">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="F32">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="G32" s="21">
-        <f t="array" ref="G32">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="G32">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="H32" s="20">
-        <f t="array" ref="H32">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="H32">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="B33" s="22">
-        <f t="array" ref="B33">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="B33">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="C33" s="22">
-        <f t="array" ref="C33">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="C33">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="D33" s="22">
-        <f t="array" ref="D33">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="D33">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="E33" s="22">
-        <f t="array" ref="E33">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="E33">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="F33" s="22">
-        <f t="array" ref="F33">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="F33">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="G33" s="23">
-        <f t="array" ref="G33">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="G33">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="H33" s="22">
-        <f t="array" ref="H33">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="H33">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="B34" s="20">
-        <f t="array" ref="B34">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="B34">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="C34" s="20">
-        <f t="array" ref="C34">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="C34">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="D34" s="20">
-        <f t="array" ref="D34">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="D34">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="E34" s="20">
-        <f t="array" ref="E34">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="E34">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="F34" s="20">
-        <f t="array" ref="F34">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="F34">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="G34" s="21">
-        <f t="array" ref="G34">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="G34">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="H34" s="20">
-        <f t="array" ref="H34">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="H34">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="B35" s="22">
-        <f t="array" ref="B35">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="B35">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="C35" s="22">
-        <f t="array" ref="C35">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="C35">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="D35" s="22">
-        <f t="array" ref="D35">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="D35">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="E35" s="22">
-        <f t="array" ref="E35">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="E35">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="F35" s="22">
-        <f t="array" ref="F35">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="F35">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="G35" s="23">
-        <f t="array" ref="G35">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="G35">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="H35" s="22">
-        <f t="array" ref="H35">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="H35">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>To continue a topic above: edit its row directly in Meeting Log (Discussion/Action/Status/Due Date) and set Last Update Date to today - do not create a new row. Only add a new row for a topic never raised before, with today as its Added Date.</t>
+          <t>To continue a topic above: add a new row in Meeting Log with the SAME Subject/Sub-topic (pick from the dropdown) and today's date. Sort Meeting Log by Subject any time to see a topic's full history together.</t>
         </is>
       </c>
     </row>
@@ -1521,261 +1513,261 @@
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="B41" s="20">
-        <f t="array" ref="B41">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="B41">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="C41" s="20">
-        <f t="array" ref="C41">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="C41">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="D41" s="20">
-        <f t="array" ref="D41">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="D41">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="E41" s="21">
-        <f t="array" ref="E41">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="E41">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="F41" s="20">
-        <f t="array" ref="F41">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="F41">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="G41" s="20">
-        <f t="array" ref="G41">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="G41">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="B42" s="22">
-        <f t="array" ref="B42">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="B42">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="C42" s="22">
-        <f t="array" ref="C42">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="C42">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f t="array" ref="D42">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="D42">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f t="array" ref="E42">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="E42">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f t="array" ref="F42">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="F42">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f t="array" ref="G42">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="G42">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="B43" s="20">
-        <f t="array" ref="B43">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="B43">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="C43" s="20">
-        <f t="array" ref="C43">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="C43">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="D43" s="20">
-        <f t="array" ref="D43">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="D43">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="E43" s="21">
-        <f t="array" ref="E43">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="E43">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="F43" s="20">
-        <f t="array" ref="F43">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="F43">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="G43" s="20">
-        <f t="array" ref="G43">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="G43">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="B44" s="22">
-        <f t="array" ref="B44">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="B44">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="C44" s="22">
-        <f t="array" ref="C44">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="C44">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f t="array" ref="D44">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="D44">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="E44" s="23">
-        <f t="array" ref="E44">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="E44">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f t="array" ref="F44">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="F44">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f t="array" ref="G44">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="G44">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="B45" s="20">
-        <f t="array" ref="B45">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="B45">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="C45" s="20">
-        <f t="array" ref="C45">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="C45">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="D45" s="20">
-        <f t="array" ref="D45">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="D45">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="E45" s="21">
-        <f t="array" ref="E45">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="E45">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="F45" s="20">
-        <f t="array" ref="F45">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="F45">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="G45" s="20">
-        <f t="array" ref="G45">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="G45">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="B46" s="22">
-        <f t="array" ref="B46">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="B46">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="C46" s="22">
-        <f t="array" ref="C46">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="C46">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="D46" s="22">
-        <f t="array" ref="D46">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="D46">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="E46" s="23">
-        <f t="array" ref="E46">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="E46">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="F46" s="22">
-        <f t="array" ref="F46">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="F46">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="G46" s="22">
-        <f t="array" ref="G46">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="G46">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="B47" s="20">
-        <f t="array" ref="B47">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="B47">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="C47" s="20">
-        <f t="array" ref="C47">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="C47">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="D47" s="20">
-        <f t="array" ref="D47">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="D47">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="E47" s="21">
-        <f t="array" ref="E47">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="E47">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="F47" s="20">
-        <f t="array" ref="F47">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="F47">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="G47" s="20">
-        <f t="array" ref="G47">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="G47">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="26" customHeight="1">
       <c r="B48" s="22">
-        <f t="array" ref="B48">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="B48">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="C48" s="22">
-        <f t="array" ref="C48">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="C48">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="D48" s="22">
-        <f t="array" ref="D48">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="D48">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="E48" s="23">
-        <f t="array" ref="E48">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="E48">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="F48" s="22">
-        <f t="array" ref="F48">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="F48">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="G48" s="22">
-        <f t="array" ref="G48">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="G48">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="B49" s="20">
-        <f t="array" ref="B49">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),9)),"")</f>
+        <f t="array" ref="B49">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
         <v/>
       </c>
       <c r="C49" s="20">
-        <f t="array" ref="C49">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),9)),"")</f>
+        <f t="array" ref="C49">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
         <v/>
       </c>
       <c r="D49" s="20">
-        <f t="array" ref="D49">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),9)),"")</f>
+        <f t="array" ref="D49">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
         <v/>
       </c>
       <c r="E49" s="21">
-        <f t="array" ref="E49">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),9)),"")</f>
+        <f t="array" ref="E49">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
         <v/>
       </c>
       <c r="F49" s="20">
-        <f t="array" ref="F49">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),9)),"")</f>
+        <f t="array" ref="F49">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
         <v/>
       </c>
       <c r="G49" s="20">
-        <f t="array" ref="G49">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),9)),"")</f>
+        <f t="array" ref="G49">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="B50" s="22">
-        <f t="array" ref="B50">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),10)),"")</f>
+        <f t="array" ref="B50">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
         <v/>
       </c>
       <c r="C50" s="22">
-        <f t="array" ref="C50">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),10)),"")</f>
+        <f t="array" ref="C50">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
         <v/>
       </c>
       <c r="D50" s="22">
-        <f t="array" ref="D50">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),10)),"")</f>
+        <f t="array" ref="D50">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
         <v/>
       </c>
       <c r="E50" s="23">
-        <f t="array" ref="E50">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),10)),"")</f>
+        <f t="array" ref="E50">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
         <v/>
       </c>
       <c r="F50" s="22">
-        <f t="array" ref="F50">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),10)),"")</f>
+        <f t="array" ref="F50">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
         <v/>
       </c>
       <c r="G50" s="22">
-        <f t="array" ref="G50">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),10)),"")</f>
+        <f t="array" ref="G50">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
         <v/>
       </c>
     </row>
@@ -1816,11 +1808,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1831,20 +1822,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L12"/>
+  <dimension ref="B1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="36" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -1861,15 +1852,10 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Meeting Report</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Meeting Report</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Lists &amp; Config</t>
         </is>
@@ -1885,7 +1871,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>The current state. One row per topic, forever - never recreate a row to continue a topic. Each meeting: update Discussion/Action/Status/Due Date on the topic's existing row, set Last Update Date to today, then add one line to History with what was actually said - that keeps every past meeting's record without retyping anything here. Add a brand new row only for a topic that has never been raised before.</t>
+          <t>The single database. One row per subject discussed at one meeting - never overwritten, never deleted. To see a topic's full history, sort by Subject (click the column header's sort button): every past entry for that topic groups together on screen, no other sheet needed.</t>
         </is>
       </c>
     </row>
@@ -1902,42 +1888,42 @@
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
+          <t>Meeting Date</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Discussion / Notes</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Agreed Action</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>Discussion / Notes</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>Agreed Action</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I7" s="15" t="inlineStr">
+      <c r="J7" s="15" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="J7" s="15" t="inlineStr">
-        <is>
-          <t>Added Date</t>
-        </is>
-      </c>
       <c r="K7" s="15" t="inlineStr">
         <is>
-          <t>Last Update Date</t>
+          <t>Topic Key</t>
         </is>
       </c>
       <c r="L7" s="15" t="inlineStr">
@@ -1957,90 +1943,90 @@
           <t>Documentation</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="16" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>Document A cannot be validated - missing the calibration certificate.</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>J. Smith to retrieve the missing certificate.</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>J. Smith</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>Document A cannot be validated - missing the calibration certificate.</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>J. Smith to retrieve the missing calibration certificate.</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="n"/>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
+      <c r="H8" s="16" t="n"/>
       <c r="I8" s="17" t="inlineStr">
         <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J8" s="17" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J8" s="16" t="n">
-        <v>46266</v>
-      </c>
-      <c r="K8" s="16" t="n">
-        <v>46296</v>
-      </c>
-      <c r="L8" s="20">
-        <f>IF($B8="","",IF(AND($H8&lt;&gt;"Closed",$H8&lt;&gt;"Cancelled",$G8&lt;&gt;"",$G8&lt;TODAY()),"Yes","No"))</f>
+      <c r="K8" s="25">
+        <f>IF($B8="","",$B8&amp;"|"&amp;$C8)</f>
+        <v/>
+      </c>
+      <c r="L8" s="25">
+        <f>IF($B8="","",IF(AND($I8&lt;&gt;"Closed",$I8&lt;&gt;"Cancelled",$H8&lt;&gt;"",$H8&lt;TODAY()),"Yes","No"))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="50" customHeight="1">
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Testing / Results</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Testing</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>A. Brown</t>
-        </is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>46296</v>
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>First functional test results reviewed.</t>
+          <t>Still waiting on the calibration certificate from the supplier.</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>A. Brown to issue the test report.</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>46315</v>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+          <t>J. Smith to chase the supplier.</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>J. Smith</t>
+        </is>
+      </c>
+      <c r="H9" s="16" t="n"/>
       <c r="I9" s="17" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="n">
-        <v>46296</v>
-      </c>
-      <c r="K9" s="16" t="n">
-        <v>46296</v>
-      </c>
-      <c r="L9" s="20">
-        <f>IF($B9="","",IF(AND($H9&lt;&gt;"Closed",$H9&lt;&gt;"Cancelled",$G9&lt;&gt;"",$G9&lt;TODAY()),"Yes","No"))</f>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K9" s="25">
+        <f>IF($B9="","",$B9&amp;"|"&amp;$C9)</f>
+        <v/>
+      </c>
+      <c r="L9" s="25">
+        <f>IF($B9="","",IF(AND($I9&lt;&gt;"Closed",$I9&lt;&gt;"Cancelled",$H9&lt;&gt;"",$H9&lt;TODAY()),"Yes","No"))</f>
         <v/>
       </c>
     </row>
@@ -2055,73 +2041,127 @@
           <t>Design / Engineering</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="16" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>SSOW draft submitted for review.</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>R. Taylor to review and approve the SSOW.</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>R. Taylor</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>SSOW draft submitted for review.</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>R. Taylor to review and approve the SSOW.</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="n"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="16" t="n">
+        <v>46285</v>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J10" s="16" t="n">
-        <v>46266</v>
-      </c>
-      <c r="K10" s="16" t="n">
-        <v>46266</v>
-      </c>
-      <c r="L10" s="20">
-        <f>IF($B10="","",IF(AND($H10&lt;&gt;"Closed",$H10&lt;&gt;"Cancelled",$G10&lt;&gt;"",$G10&lt;TODAY()),"Yes","No"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="24" t="inlineStr">
+      <c r="K10" s="25">
+        <f>IF($B10="","",$B10&amp;"|"&amp;$C10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="25">
+        <f>IF($B10="","",IF(AND($I10&lt;&gt;"Closed",$I10&lt;&gt;"Cancelled",$H10&lt;&gt;"",$H10&lt;TODAY()),"Yes","No"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Testing / Results</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>First functional test results reviewed.</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>A. Brown to issue the test report.</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>A. Brown</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>46315</v>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="J11" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K11" s="25">
+        <f>IF($B11="","",$B11&amp;"|"&amp;$C11)</f>
+        <v/>
+      </c>
+      <c r="L11" s="25">
+        <f>IF($B11="","",IF(AND($I11&lt;&gt;"Closed",$I11&lt;&gt;"Cancelled",$H11&lt;&gt;"",$H11&lt;TODAY()),"Yes","No"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>Legend: Blue = fill in yourself | Black = automatic, do not overtype | Grey columns = automation helpers, leave untouched | New row: type directly below the table and Excel extends it automatically</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B8:L10">
+  <conditionalFormatting sqref="B8:L11">
     <cfRule type="expression" priority="1" dxfId="1">
-      <formula>AND($H8&lt;&gt;"Closed",$L8="Yes")</formula>
+      <formula>AND($I8&lt;&gt;"Closed",$L8="Yes")</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="2">
-      <formula>$H8="Closed"</formula>
+      <formula>$I8="Closed"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="3">
-      <formula>OR($H8="On Hold",$H8="Cancelled")</formula>
+      <formula>OR($I8="On Hold",$I8="Cancelled")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="B8:B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B8:B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LIST_SUBJECT</formula1>
     </dataValidation>
-    <dataValidation sqref="C8:C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C8:C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LIST_SUBTOPIC</formula1>
     </dataValidation>
-    <dataValidation sqref="H8:H10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I8:I11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LIST_STATUS</formula1>
     </dataValidation>
-    <dataValidation sqref="I8:I10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J8:J11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LIST_PRIORITY</formula1>
     </dataValidation>
   </dataValidations>
@@ -2130,206 +2170,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B1:F12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2.5" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Overview</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Meeting Log</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Meeting Report</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Lists &amp; Config</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>The full past record. Every time you touch a topic in Meeting Log, add one line here too - date, topic, what was said or decided. Never edit or delete a past row; just keep adding new ones underneath.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>Meeting Date</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Subject</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Sub-topic</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
-        <is>
-          <t>Update / Discussion</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="16" t="n">
-        <v>46266</v>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>Document A cannot be validated - the calibration certificate is missing.</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>J. Smith to retrieve the missing certificate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="16" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>Still waiting on the calibration certificate from the supplier.</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>No change - carried to next meeting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="50" customHeight="1">
-      <c r="B10" s="16" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>Testing / Results</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>Testing</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>First functional test results reviewed.</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>A. Brown to issue the test report by 20-Oct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>Legend: Blue = fill in yourself | Black = automatic, do not overtype | Grey columns = automation helpers, leave untouched | New row: type directly below the table and Excel extends it automatically</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="C8:C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=LIST_SUBJECT</formula1>
-    </dataValidation>
-    <dataValidation sqref="D8:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=LIST_SUBTOPIC</formula1>
-    </dataValidation>
-  </dataValidations>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId5"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2359,17 +2208,12 @@
           <t>Meeting Log</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Meeting Report</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Lists &amp; Config</t>
         </is>
@@ -2395,7 +2239,7 @@
           <t>Meeting Date:</t>
         </is>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <f>'Overview'!$C$5</f>
         <v/>
       </c>
@@ -2404,7 +2248,7 @@
           <t>Meeting Type:</t>
         </is>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="27">
         <f>IFERROR(INDEX(Attendees_Log[Meeting Type],MATCH($C$5,Attendees_Log[Meeting Date],0)),"")</f>
         <v/>
       </c>
@@ -2415,7 +2259,7 @@
           <t>Attendees:</t>
         </is>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <f>IFERROR(INDEX(Attendees_Log[Attendees],MATCH($C$5,Attendees_Log[Meeting Date],0)),"")</f>
         <v/>
       </c>
@@ -2466,209 +2310,209 @@
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="B10" s="20">
-        <f t="array" ref="B10">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="B10">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="C10" s="20">
-        <f t="array" ref="C10">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="C10">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="D10" s="20">
-        <f t="array" ref="D10">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="D10">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="E10" s="20">
-        <f t="array" ref="E10">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="E10">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="F10" s="20">
-        <f t="array" ref="F10">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="F10">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="G10" s="20">
-        <f t="array" ref="G10">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="G10">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="B11" s="22">
-        <f t="array" ref="B11">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="B11">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="C11" s="22">
-        <f t="array" ref="C11">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="C11">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="D11" s="22">
-        <f t="array" ref="D11">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="D11">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="E11" s="22">
-        <f t="array" ref="E11">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="E11">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="F11" s="22">
-        <f t="array" ref="F11">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="F11">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="G11" s="22">
-        <f t="array" ref="G11">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="G11">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="B12" s="20">
-        <f t="array" ref="B12">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="B12">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="C12" s="20">
-        <f t="array" ref="C12">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="C12">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="D12" s="20">
-        <f t="array" ref="D12">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="D12">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="E12" s="20">
-        <f t="array" ref="E12">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="E12">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="F12" s="20">
-        <f t="array" ref="F12">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="F12">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="G12" s="20">
-        <f t="array" ref="G12">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="G12">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="B13" s="22">
-        <f t="array" ref="B13">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="B13">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="C13" s="22">
-        <f t="array" ref="C13">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="C13">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="D13" s="22">
-        <f t="array" ref="D13">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="D13">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="E13" s="22">
-        <f t="array" ref="E13">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="E13">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="F13" s="22">
-        <f t="array" ref="F13">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="F13">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="G13" s="22">
-        <f t="array" ref="G13">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="G13">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="B14" s="20">
-        <f t="array" ref="B14">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="B14">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="C14" s="20">
-        <f t="array" ref="C14">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="C14">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="D14" s="20">
-        <f t="array" ref="D14">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="D14">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="E14" s="20">
-        <f t="array" ref="E14">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="E14">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="F14" s="20">
-        <f t="array" ref="F14">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="F14">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="G14" s="20">
-        <f t="array" ref="G14">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="G14">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="B15" s="22">
-        <f t="array" ref="B15">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="B15">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="C15" s="22">
-        <f t="array" ref="C15">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="C15">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="D15" s="22">
-        <f t="array" ref="D15">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="D15">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="E15" s="22">
-        <f t="array" ref="E15">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="E15">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="F15" s="22">
-        <f t="array" ref="F15">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="F15">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="G15" s="22">
-        <f t="array" ref="G15">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="G15">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="B16" s="20">
-        <f t="array" ref="B16">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="B16">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="C16" s="20">
-        <f t="array" ref="C16">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="C16">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="D16" s="20">
-        <f t="array" ref="D16">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="D16">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="E16" s="20">
-        <f t="array" ref="E16">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="E16">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="F16" s="20">
-        <f t="array" ref="F16">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="F16">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="G16" s="20">
-        <f t="array" ref="G16">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="G16">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="B17" s="22">
-        <f t="array" ref="B17">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="B17">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="C17" s="22">
-        <f t="array" ref="C17">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="C17">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="D17" s="22">
-        <f t="array" ref="D17">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="D17">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="E17" s="22">
-        <f t="array" ref="E17">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="E17">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="F17" s="22">
-        <f t="array" ref="F17">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="F17">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="G17" s="22">
-        <f t="array" ref="G17">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="G17">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
     </row>
@@ -2724,181 +2568,181 @@
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="B21" s="20">
-        <f t="array" ref="B21">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="B21">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="C21" s="20">
-        <f t="array" ref="C21">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="C21">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="D21" s="20">
-        <f t="array" ref="D21">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="D21">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="E21" s="20">
-        <f t="array" ref="E21">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="E21">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="F21" s="20">
-        <f t="array" ref="F21">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="F21">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="G21" s="21">
-        <f t="array" ref="G21">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="G21">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="H21" s="20">
-        <f t="array" ref="H21">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="H21">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="B22" s="22">
-        <f t="array" ref="B22">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="B22">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="C22" s="22">
-        <f t="array" ref="C22">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="C22">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="D22" s="22">
-        <f t="array" ref="D22">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="D22">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="E22" s="22">
-        <f t="array" ref="E22">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="E22">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="F22" s="22">
-        <f t="array" ref="F22">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="F22">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="G22" s="23">
-        <f t="array" ref="G22">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="G22">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="H22" s="22">
-        <f t="array" ref="H22">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="H22">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="B23" s="20">
-        <f t="array" ref="B23">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="B23">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="C23" s="20">
-        <f t="array" ref="C23">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="C23">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="D23" s="20">
-        <f t="array" ref="D23">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="D23">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="E23" s="20">
-        <f t="array" ref="E23">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="E23">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="F23" s="20">
-        <f t="array" ref="F23">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="F23">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="G23" s="21">
-        <f t="array" ref="G23">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="G23">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="H23" s="20">
-        <f t="array" ref="H23">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="H23">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="B24" s="22">
-        <f t="array" ref="B24">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="B24">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="C24" s="22">
-        <f t="array" ref="C24">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="C24">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="D24" s="22">
-        <f t="array" ref="D24">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="D24">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="E24" s="22">
-        <f t="array" ref="E24">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="E24">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="F24" s="22">
-        <f t="array" ref="F24">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="F24">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="G24" s="23">
-        <f t="array" ref="G24">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="G24">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="H24" s="22">
-        <f t="array" ref="H24">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="H24">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="B25" s="20">
-        <f t="array" ref="B25">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="B25">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="C25" s="20">
-        <f t="array" ref="C25">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="C25">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="D25" s="20">
-        <f t="array" ref="D25">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="D25">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="E25" s="20">
-        <f t="array" ref="E25">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="E25">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="F25" s="20">
-        <f t="array" ref="F25">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="F25">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="G25" s="21">
-        <f t="array" ref="G25">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="G25">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="H25" s="20">
-        <f t="array" ref="H25">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="H25">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="B26" s="22">
-        <f t="array" ref="B26">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="B26">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="C26" s="22">
-        <f t="array" ref="C26">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="C26">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="D26" s="22">
-        <f t="array" ref="D26">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="D26">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="E26" s="22">
-        <f t="array" ref="E26">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="E26">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="F26" s="22">
-        <f t="array" ref="F26">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="F26">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="G26" s="23">
-        <f t="array" ref="G26">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="G26">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="H26" s="22">
-        <f t="array" ref="H26">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="H26">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
     </row>
@@ -2911,6 +2755,7 @@
       <c r="C28" s="18" t="n"/>
       <c r="D28" s="18" t="n"/>
       <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="19" t="inlineStr">
@@ -2925,156 +2770,193 @@
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
-          <t>Update / Discussion</t>
+          <t>Discussion / Notes</t>
         </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Agreed Action</t>
+        </is>
+      </c>
+      <c r="F29" s="19" t="inlineStr">
+        <is>
+          <t>Owner</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="B30" s="20">
-        <f t="array" ref="B30">IFERROR(INDEX(History_Log[Subject],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="B30">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="C30" s="20">
-        <f t="array" ref="C30">IFERROR(INDEX(History_Log[Sub-topic],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="C30">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="D30" s="20">
-        <f t="array" ref="D30">IFERROR(INDEX(History_Log[Update / Discussion],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="D30">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="E30" s="20">
-        <f t="array" ref="E30">IFERROR(INDEX(History_Log[Decision],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="E30">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="20">
+        <f t="array" ref="F30">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="B31" s="22">
-        <f t="array" ref="B31">IFERROR(INDEX(History_Log[Subject],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="B31">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="C31" s="22">
-        <f t="array" ref="C31">IFERROR(INDEX(History_Log[Sub-topic],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="C31">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="D31" s="22">
-        <f t="array" ref="D31">IFERROR(INDEX(History_Log[Update / Discussion],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="D31">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="E31" s="22">
-        <f t="array" ref="E31">IFERROR(INDEX(History_Log[Decision],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="E31">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="22">
+        <f t="array" ref="F31">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="B32" s="20">
-        <f t="array" ref="B32">IFERROR(INDEX(History_Log[Subject],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="B32">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="C32" s="20">
-        <f t="array" ref="C32">IFERROR(INDEX(History_Log[Sub-topic],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="C32">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="D32" s="20">
-        <f t="array" ref="D32">IFERROR(INDEX(History_Log[Update / Discussion],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="D32">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="E32" s="20">
-        <f t="array" ref="E32">IFERROR(INDEX(History_Log[Decision],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="E32">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="20">
+        <f t="array" ref="F32">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="B33" s="22">
-        <f t="array" ref="B33">IFERROR(INDEX(History_Log[Subject],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="B33">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="C33" s="22">
-        <f t="array" ref="C33">IFERROR(INDEX(History_Log[Sub-topic],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="C33">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="D33" s="22">
-        <f t="array" ref="D33">IFERROR(INDEX(History_Log[Update / Discussion],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="D33">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="E33" s="22">
-        <f t="array" ref="E33">IFERROR(INDEX(History_Log[Decision],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="E33">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="22">
+        <f t="array" ref="F33">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="B34" s="20">
-        <f t="array" ref="B34">IFERROR(INDEX(History_Log[Subject],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="B34">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="C34" s="20">
-        <f t="array" ref="C34">IFERROR(INDEX(History_Log[Sub-topic],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="C34">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="D34" s="20">
-        <f t="array" ref="D34">IFERROR(INDEX(History_Log[Update / Discussion],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="D34">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="E34" s="20">
-        <f t="array" ref="E34">IFERROR(INDEX(History_Log[Decision],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="E34">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="20">
+        <f t="array" ref="F34">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="B35" s="22">
-        <f t="array" ref="B35">IFERROR(INDEX(History_Log[Subject],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="B35">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="C35" s="22">
-        <f t="array" ref="C35">IFERROR(INDEX(History_Log[Sub-topic],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="C35">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="D35" s="22">
-        <f t="array" ref="D35">IFERROR(INDEX(History_Log[Update / Discussion],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="D35">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="E35" s="22">
-        <f t="array" ref="E35">IFERROR(INDEX(History_Log[Decision],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="E35">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="22">
+        <f t="array" ref="F35">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="B36" s="20">
-        <f t="array" ref="B36">IFERROR(INDEX(History_Log[Subject],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="B36">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="C36" s="20">
-        <f t="array" ref="C36">IFERROR(INDEX(History_Log[Sub-topic],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="C36">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="D36" s="20">
-        <f t="array" ref="D36">IFERROR(INDEX(History_Log[Update / Discussion],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="D36">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="E36" s="20">
-        <f t="array" ref="E36">IFERROR(INDEX(History_Log[Decision],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="E36">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="20">
+        <f t="array" ref="F36">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="B37" s="22">
-        <f t="array" ref="B37">IFERROR(INDEX(History_Log[Subject],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="B37">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="C37" s="22">
-        <f t="array" ref="C37">IFERROR(INDEX(History_Log[Sub-topic],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="C37">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="D37" s="22">
-        <f t="array" ref="D37">IFERROR(INDEX(History_Log[Update / Discussion],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="D37">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="E37" s="22">
-        <f t="array" ref="E37">IFERROR(INDEX(History_Log[Decision],SMALL(IF((History_Log[Subject]&lt;&gt;"")*(History_Log[Meeting Date]=$C$5),ROW(History_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="E37">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="22">
+        <f t="array" ref="F37">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
     </row>
@@ -3118,177 +3000,177 @@
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="B41" s="20">
-        <f t="array" ref="B41">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="B41">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="C41" s="20">
-        <f t="array" ref="C41">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="C41">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="D41" s="20">
-        <f t="array" ref="D41">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="D41">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="E41" s="21">
-        <f t="array" ref="E41">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="E41">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
       <c r="F41" s="20">
-        <f t="array" ref="F41">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
+        <f t="array" ref="F41">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="B42" s="22">
-        <f t="array" ref="B42">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="B42">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="C42" s="22">
-        <f t="array" ref="C42">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="C42">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f t="array" ref="D42">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="D42">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f t="array" ref="E42">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="E42">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f t="array" ref="F42">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
+        <f t="array" ref="F42">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="B43" s="20">
-        <f t="array" ref="B43">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="B43">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="C43" s="20">
-        <f t="array" ref="C43">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="C43">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="D43" s="20">
-        <f t="array" ref="D43">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="D43">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="E43" s="21">
-        <f t="array" ref="E43">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="E43">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
       <c r="F43" s="20">
-        <f t="array" ref="F43">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
+        <f t="array" ref="F43">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="B44" s="22">
-        <f t="array" ref="B44">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="B44">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="C44" s="22">
-        <f t="array" ref="C44">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="C44">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f t="array" ref="D44">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="D44">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="E44" s="23">
-        <f t="array" ref="E44">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="E44">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f t="array" ref="F44">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
+        <f t="array" ref="F44">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="B45" s="20">
-        <f t="array" ref="B45">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="B45">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="C45" s="20">
-        <f t="array" ref="C45">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="C45">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="D45" s="20">
-        <f t="array" ref="D45">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="D45">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="E45" s="21">
-        <f t="array" ref="E45">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="E45">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
       <c r="F45" s="20">
-        <f t="array" ref="F45">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
+        <f t="array" ref="F45">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="B46" s="22">
-        <f t="array" ref="B46">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="B46">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="C46" s="22">
-        <f t="array" ref="C46">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="C46">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="D46" s="22">
-        <f t="array" ref="D46">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="D46">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="E46" s="23">
-        <f t="array" ref="E46">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="E46">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
       <c r="F46" s="22">
-        <f t="array" ref="F46">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
+        <f t="array" ref="F46">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="B47" s="20">
-        <f t="array" ref="B47">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="B47">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="C47" s="20">
-        <f t="array" ref="C47">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="C47">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="D47" s="20">
-        <f t="array" ref="D47">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="D47">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="E47" s="21">
-        <f t="array" ref="E47">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="E47">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
       <c r="F47" s="20">
-        <f t="array" ref="F47">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
+        <f t="array" ref="F47">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="26" customHeight="1">
       <c r="B48" s="22">
-        <f t="array" ref="B48">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="B48">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="C48" s="22">
-        <f t="array" ref="C48">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="C48">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="D48" s="22">
-        <f t="array" ref="D48">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="D48">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="E48" s="23">
-        <f t="array" ref="E48">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="E48">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
       <c r="F48" s="22">
-        <f t="array" ref="F48">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
+        <f t="array" ref="F48">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
         <v/>
       </c>
     </row>
@@ -3308,13 +3190,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3344,15 +3225,10 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
           <t>Meeting Report</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Lists &amp; Config</t>
         </is>
@@ -3368,252 +3244,252 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Dropdown values used on Meeting Log. Add or remove values here - every dropdown updates automatically. No formulas here need to change.</t>
+          <t>Dropdown values used across the workbook. Add or remove values here - every dropdown updates automatically. No formulas here need to change.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>Sub-topic</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E5" s="28" t="inlineStr">
+      <c r="E5" s="29" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="F5" s="28" t="inlineStr">
+      <c r="F5" s="29" t="inlineStr">
         <is>
           <t>Meeting Type</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Commissioning Planning</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="D6" s="29" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="E6" s="29" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F6" s="29" t="inlineStr">
+      <c r="F6" s="30" t="inlineStr">
         <is>
           <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>Site / Field Activities</t>
         </is>
       </c>
-      <c r="C7" s="30" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
-      <c r="D7" s="30" t="inlineStr">
+      <c r="D7" s="31" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="E7" s="30" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F7" s="30" t="inlineStr">
+      <c r="F7" s="31" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>Preparation</t>
         </is>
       </c>
-      <c r="D8" s="29" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="E8" s="29" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F8" s="29" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>Ad hoc</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>Testing / Results</t>
         </is>
       </c>
-      <c r="C9" s="30" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t>Execution</t>
         </is>
       </c>
-      <c r="D9" s="30" t="inlineStr">
+      <c r="D9" s="31" t="inlineStr">
         <is>
           <t>On Hold</t>
         </is>
       </c>
-      <c r="E9" s="30" t="inlineStr">
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Interfaces</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
-      <c r="D10" s="29" t="inlineStr">
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>Cancelled</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="C11" s="30" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>Punch List</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="C13" s="30" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t>NCR / Quality</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>Resources / Manpower</t>
         </is>
       </c>
-      <c r="C14" s="29" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
         <is>
           <t>Design / Engineering</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="30" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="C15" s="30" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
         <is>
           <t>Interface</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C16" s="29" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
         <is>
           <t>Resource</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="30" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="29" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
         <is>
           <t>Risk / Issue</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="30" t="inlineStr">
+      <c r="C19" s="31" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="29" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -3632,7 +3508,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/HBX Commissioning Review.xlsx
+++ b/HBX Commissioning Review.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Meeting Log" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Meeting Report" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lists &amp; Config" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Archive" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Meeting Report" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Lists &amp; Config" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="LIST_SUBJECT">'Lists &amp; Config'!$B$6:$B$16</definedName>
@@ -29,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd-mmm-yy"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -88,12 +89,6 @@
       <name val="Arial"/>
       <color rgb="001155CC"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00808080"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -162,7 +157,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -182,11 +177,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F5FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
     <fill>
@@ -231,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -241,12 +231,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -256,13 +249,10 @@
     <xf numFmtId="1" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -272,8 +262,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -282,16 +272,15 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -435,20 +424,39 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Meeting_Log" displayName="Meeting_Log" ref="B7:L11" headerRowCount="1">
-  <autoFilter ref="B7:L11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Meeting_Log" displayName="Meeting_Log" ref="B7:L10" headerRowCount="1">
+  <autoFilter ref="B7:L10"/>
   <tableColumns count="11">
     <tableColumn id="2" name="Subject"/>
     <tableColumn id="3" name="Sub-topic"/>
-    <tableColumn id="4" name="Meeting Date"/>
+    <tableColumn id="4" name="Owner"/>
     <tableColumn id="5" name="Discussion / Notes"/>
     <tableColumn id="6" name="Agreed Action"/>
-    <tableColumn id="7" name="Owner"/>
-    <tableColumn id="8" name="Due Date"/>
-    <tableColumn id="9" name="Status"/>
-    <tableColumn id="10" name="Priority"/>
-    <tableColumn id="11" name="Topic Key"/>
+    <tableColumn id="7" name="Due Date"/>
+    <tableColumn id="8" name="Status"/>
+    <tableColumn id="9" name="Priority"/>
+    <tableColumn id="10" name="Added Date"/>
+    <tableColumn id="11" name="Last Update Date"/>
     <tableColumn id="12" name="Overdue?"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Archive_Log" displayName="Archive_Log" ref="B7:K8" headerRowCount="1">
+  <autoFilter ref="B7:K8"/>
+  <tableColumns count="10">
+    <tableColumn id="2" name="Subject"/>
+    <tableColumn id="3" name="Sub-topic"/>
+    <tableColumn id="4" name="Owner"/>
+    <tableColumn id="5" name="Discussion / Notes"/>
+    <tableColumn id="6" name="Agreed Action"/>
+    <tableColumn id="7" name="Due Date"/>
+    <tableColumn id="8" name="Status"/>
+    <tableColumn id="9" name="Priority"/>
+    <tableColumn id="10" name="Added Date"/>
+    <tableColumn id="11" name="Last Update Date"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -776,10 +784,15 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Meeting Report</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Lists &amp; Config</t>
         </is>
@@ -811,32 +824,32 @@
     </row>
     <row r="8">
       <c r="B8" s="7">
-        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5)))</f>
+        <f>SUMPRODUCT((Meeting_Log[Subject]&lt;&gt;""))</f>
         <v/>
       </c>
       <c r="C8" s="8" t="n"/>
       <c r="E8" s="7">
-        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"))</f>
+        <f>SUMPRODUCT((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"))</f>
         <v/>
       </c>
       <c r="F8" s="8" t="n"/>
       <c r="H8" s="9">
-        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Overdue?]="Yes"))</f>
+        <f>SUMPRODUCT((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Overdue?]="Yes"))</f>
         <v/>
       </c>
       <c r="I8" s="8" t="n"/>
       <c r="K8" s="10">
-        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]="Closed"))</f>
+        <f>SUMPRODUCT((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]="Closed"))</f>
         <v/>
       </c>
       <c r="L8" s="8" t="n"/>
       <c r="N8" s="11">
-        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"))</f>
+        <f>SUMPRODUCT((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5))</f>
         <v/>
       </c>
       <c r="O8" s="8" t="n"/>
       <c r="Q8" s="12">
-        <f>SUMPRODUCT((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0))</f>
+        <f>SUMPRODUCT((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5))</f>
         <v/>
       </c>
       <c r="R8" s="8" t="n"/>
@@ -992,241 +1005,241 @@
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="B19" s="20">
-        <f t="array" ref="B19">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="B19">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="C19" s="20">
-        <f t="array" ref="C19">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="C19">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="D19" s="20">
-        <f t="array" ref="D19">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="D19">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="E19" s="20">
-        <f t="array" ref="E19">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="E19">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="F19" s="20">
-        <f t="array" ref="F19">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="F19">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="G19" s="21">
-        <f t="array" ref="G19">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="G19">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="H19" s="20">
-        <f t="array" ref="H19">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="H19">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="B20" s="22">
-        <f t="array" ref="B20">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="B20">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="C20" s="22">
-        <f t="array" ref="C20">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="C20">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="D20" s="22">
-        <f t="array" ref="D20">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="D20">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="E20" s="22">
-        <f t="array" ref="E20">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="E20">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="F20" s="22">
-        <f t="array" ref="F20">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="F20">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="G20" s="23">
-        <f t="array" ref="G20">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="G20">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="H20" s="22">
-        <f t="array" ref="H20">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="H20">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="B21" s="20">
-        <f t="array" ref="B21">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="B21">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="C21" s="20">
-        <f t="array" ref="C21">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="C21">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="D21" s="20">
-        <f t="array" ref="D21">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="D21">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="E21" s="20">
-        <f t="array" ref="E21">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="E21">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="F21" s="20">
-        <f t="array" ref="F21">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="F21">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="G21" s="21">
-        <f t="array" ref="G21">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="G21">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="H21" s="20">
-        <f t="array" ref="H21">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="H21">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="B22" s="22">
-        <f t="array" ref="B22">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="B22">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="C22" s="22">
-        <f t="array" ref="C22">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="C22">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="D22" s="22">
-        <f t="array" ref="D22">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="D22">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="E22" s="22">
-        <f t="array" ref="E22">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="E22">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="F22" s="22">
-        <f t="array" ref="F22">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="F22">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="G22" s="23">
-        <f t="array" ref="G22">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="G22">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="H22" s="22">
-        <f t="array" ref="H22">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="H22">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="B23" s="20">
-        <f t="array" ref="B23">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="B23">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="C23" s="20">
-        <f t="array" ref="C23">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="C23">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="D23" s="20">
-        <f t="array" ref="D23">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="D23">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="E23" s="20">
-        <f t="array" ref="E23">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="E23">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="F23" s="20">
-        <f t="array" ref="F23">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="F23">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="G23" s="21">
-        <f t="array" ref="G23">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="G23">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="H23" s="20">
-        <f t="array" ref="H23">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="H23">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="B24" s="22">
-        <f t="array" ref="B24">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="B24">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="C24" s="22">
-        <f t="array" ref="C24">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="C24">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="D24" s="22">
-        <f t="array" ref="D24">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="D24">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="E24" s="22">
-        <f t="array" ref="E24">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="E24">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="F24" s="22">
-        <f t="array" ref="F24">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="F24">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="G24" s="23">
-        <f t="array" ref="G24">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="G24">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="H24" s="22">
-        <f t="array" ref="H24">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="H24">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="B25" s="20">
-        <f t="array" ref="B25">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="B25">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="C25" s="20">
-        <f t="array" ref="C25">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="C25">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="D25" s="20">
-        <f t="array" ref="D25">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="D25">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="E25" s="20">
-        <f t="array" ref="E25">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="E25">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="F25" s="20">
-        <f t="array" ref="F25">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="F25">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="G25" s="21">
-        <f t="array" ref="G25">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="G25">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="H25" s="20">
-        <f t="array" ref="H25">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="H25">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="B26" s="22">
-        <f t="array" ref="B26">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="B26">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="C26" s="22">
-        <f t="array" ref="C26">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="C26">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="D26" s="22">
-        <f t="array" ref="D26">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="D26">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="E26" s="22">
-        <f t="array" ref="E26">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="E26">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="F26" s="22">
-        <f t="array" ref="F26">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="F26">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="G26" s="23">
-        <f t="array" ref="G26">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="G26">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="H26" s="22">
-        <f t="array" ref="H26">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="H26">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
     </row>
@@ -1282,188 +1295,188 @@
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="B30" s="20">
-        <f t="array" ref="B30">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="B30">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="C30" s="20">
-        <f t="array" ref="C30">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="C30">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="D30" s="20">
-        <f t="array" ref="D30">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="D30">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="E30" s="20">
-        <f t="array" ref="E30">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="E30">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="F30" s="20">
-        <f t="array" ref="F30">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="F30">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="G30" s="21">
-        <f t="array" ref="G30">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="G30">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="H30" s="20">
-        <f t="array" ref="H30">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="H30">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="B31" s="22">
-        <f t="array" ref="B31">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="B31">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="C31" s="22">
-        <f t="array" ref="C31">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="C31">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="D31" s="22">
-        <f t="array" ref="D31">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="D31">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="E31" s="22">
-        <f t="array" ref="E31">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="E31">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="F31" s="22">
-        <f t="array" ref="F31">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="F31">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="G31" s="23">
-        <f t="array" ref="G31">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="G31">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="H31" s="22">
-        <f t="array" ref="H31">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="H31">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="B32" s="20">
-        <f t="array" ref="B32">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="B32">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="C32" s="20">
-        <f t="array" ref="C32">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="C32">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="D32" s="20">
-        <f t="array" ref="D32">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="D32">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="E32" s="20">
-        <f t="array" ref="E32">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="E32">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="F32" s="20">
-        <f t="array" ref="F32">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="F32">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="G32" s="21">
-        <f t="array" ref="G32">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="G32">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="H32" s="20">
-        <f t="array" ref="H32">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="H32">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="B33" s="22">
-        <f t="array" ref="B33">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="B33">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="C33" s="22">
-        <f t="array" ref="C33">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="C33">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="D33" s="22">
-        <f t="array" ref="D33">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="D33">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="E33" s="22">
-        <f t="array" ref="E33">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="E33">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="F33" s="22">
-        <f t="array" ref="F33">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="F33">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="G33" s="23">
-        <f t="array" ref="G33">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="G33">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="H33" s="22">
-        <f t="array" ref="H33">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="H33">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="B34" s="20">
-        <f t="array" ref="B34">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="B34">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="C34" s="20">
-        <f t="array" ref="C34">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="C34">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="D34" s="20">
-        <f t="array" ref="D34">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="D34">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="E34" s="20">
-        <f t="array" ref="E34">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="E34">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="F34" s="20">
-        <f t="array" ref="F34">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="F34">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="G34" s="21">
-        <f t="array" ref="G34">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="G34">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="H34" s="20">
-        <f t="array" ref="H34">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="H34">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="B35" s="22">
-        <f t="array" ref="B35">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="B35">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="C35" s="22">
-        <f t="array" ref="C35">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="C35">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="D35" s="22">
-        <f t="array" ref="D35">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="D35">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="E35" s="22">
-        <f t="array" ref="E35">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="E35">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="F35" s="22">
-        <f t="array" ref="F35">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="F35">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="G35" s="23">
-        <f t="array" ref="G35">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="G35">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="H35" s="22">
-        <f t="array" ref="H35">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="H35">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>To continue a topic above: add a new row in Meeting Log with the SAME Subject/Sub-topic (pick from the dropdown) and today's date. Sort Meeting Log by Subject any time to see a topic's full history together.</t>
+          <t>To continue a topic above: edit its row directly in Meeting Log (Discussion/Action/Status/Due Date) and set Last Update Date to today - do not create a new row. Only add a new row for a topic never raised before, with today as its Added Date. Once a topic is finished, copy its row into Archive yourself.</t>
         </is>
       </c>
     </row>
@@ -1513,261 +1526,261 @@
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="B41" s="20">
-        <f t="array" ref="B41">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="B41">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="C41" s="20">
-        <f t="array" ref="C41">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="C41">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="D41" s="20">
-        <f t="array" ref="D41">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="D41">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="E41" s="21">
-        <f t="array" ref="E41">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="E41">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="F41" s="20">
-        <f t="array" ref="F41">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="F41">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="G41" s="20">
-        <f t="array" ref="G41">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="G41">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="B42" s="22">
-        <f t="array" ref="B42">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="B42">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="C42" s="22">
-        <f t="array" ref="C42">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="C42">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f t="array" ref="D42">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="D42">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f t="array" ref="E42">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="E42">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f t="array" ref="F42">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="F42">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f t="array" ref="G42">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="G42">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="B43" s="20">
-        <f t="array" ref="B43">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="B43">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="C43" s="20">
-        <f t="array" ref="C43">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="C43">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="D43" s="20">
-        <f t="array" ref="D43">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="D43">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="E43" s="21">
-        <f t="array" ref="E43">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="E43">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="F43" s="20">
-        <f t="array" ref="F43">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="F43">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="G43" s="20">
-        <f t="array" ref="G43">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="G43">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="B44" s="22">
-        <f t="array" ref="B44">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="B44">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="C44" s="22">
-        <f t="array" ref="C44">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="C44">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f t="array" ref="D44">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="D44">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="E44" s="23">
-        <f t="array" ref="E44">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="E44">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f t="array" ref="F44">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="F44">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f t="array" ref="G44">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="G44">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="B45" s="20">
-        <f t="array" ref="B45">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="B45">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="C45" s="20">
-        <f t="array" ref="C45">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="C45">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="D45" s="20">
-        <f t="array" ref="D45">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="D45">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="E45" s="21">
-        <f t="array" ref="E45">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="E45">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="F45" s="20">
-        <f t="array" ref="F45">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="F45">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="G45" s="20">
-        <f t="array" ref="G45">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="G45">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="B46" s="22">
-        <f t="array" ref="B46">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="B46">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="C46" s="22">
-        <f t="array" ref="C46">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="C46">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="D46" s="22">
-        <f t="array" ref="D46">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="D46">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="E46" s="23">
-        <f t="array" ref="E46">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="E46">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="F46" s="22">
-        <f t="array" ref="F46">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="F46">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="G46" s="22">
-        <f t="array" ref="G46">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="G46">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="B47" s="20">
-        <f t="array" ref="B47">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="B47">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="C47" s="20">
-        <f t="array" ref="C47">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="C47">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="D47" s="20">
-        <f t="array" ref="D47">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="D47">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="E47" s="21">
-        <f t="array" ref="E47">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="E47">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="F47" s="20">
-        <f t="array" ref="F47">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="F47">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="G47" s="20">
-        <f t="array" ref="G47">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="G47">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="26" customHeight="1">
       <c r="B48" s="22">
-        <f t="array" ref="B48">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="B48">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="C48" s="22">
-        <f t="array" ref="C48">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="C48">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="D48" s="22">
-        <f t="array" ref="D48">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="D48">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="E48" s="23">
-        <f t="array" ref="E48">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="E48">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="F48" s="22">
-        <f t="array" ref="F48">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="F48">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="G48" s="22">
-        <f t="array" ref="G48">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="G48">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="B49" s="20">
-        <f t="array" ref="B49">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <f t="array" ref="B49">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),9)),"")</f>
         <v/>
       </c>
       <c r="C49" s="20">
-        <f t="array" ref="C49">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <f t="array" ref="C49">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),9)),"")</f>
         <v/>
       </c>
       <c r="D49" s="20">
-        <f t="array" ref="D49">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <f t="array" ref="D49">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),9)),"")</f>
         <v/>
       </c>
       <c r="E49" s="21">
-        <f t="array" ref="E49">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <f t="array" ref="E49">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),9)),"")</f>
         <v/>
       </c>
       <c r="F49" s="20">
-        <f t="array" ref="F49">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <f t="array" ref="F49">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),9)),"")</f>
         <v/>
       </c>
       <c r="G49" s="20">
-        <f t="array" ref="G49">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),9)),"")</f>
+        <f t="array" ref="G49">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),9)),"")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="B50" s="22">
-        <f t="array" ref="B50">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <f t="array" ref="B50">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),10)),"")</f>
         <v/>
       </c>
       <c r="C50" s="22">
-        <f t="array" ref="C50">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <f t="array" ref="C50">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),10)),"")</f>
         <v/>
       </c>
       <c r="D50" s="22">
-        <f t="array" ref="D50">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <f t="array" ref="D50">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),10)),"")</f>
         <v/>
       </c>
       <c r="E50" s="23">
-        <f t="array" ref="E50">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <f t="array" ref="E50">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),10)),"")</f>
         <v/>
       </c>
       <c r="F50" s="22">
-        <f t="array" ref="F50">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <f t="array" ref="F50">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),10)),"")</f>
         <v/>
       </c>
       <c r="G50" s="22">
-        <f t="array" ref="G50">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),10)),"")</f>
+        <f t="array" ref="G50">IFERROR(INDEX(Meeting_Log[Priority],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Subject])-7),10)),"")</f>
         <v/>
       </c>
     </row>
@@ -1808,10 +1821,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1822,20 +1836,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L13"/>
+  <dimension ref="B1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="36" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -1852,10 +1866,15 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Meeting Report</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Lists &amp; Config</t>
         </is>
@@ -1871,7 +1890,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>The single database. One row per subject discussed at one meeting - never overwritten, never deleted. To see a topic's full history, sort by Subject (click the column header's sort button): every past entry for that topic groups together on screen, no other sheet needed.</t>
+          <t>One row per topic, forever - never a new row to continue a topic. Each meeting: update Discussion/Action/Status/Due Date on the topic's existing row and set Last Update Date to today. Once a topic is finished, copy its row into Archive yourself, then delete it here if you want to. Add a brand new row only for a topic never raised before.</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1907,7 @@
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>Meeting Date</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -1903,27 +1922,27 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Due Date</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>Due Date</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="J7" s="15" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Added Date</t>
         </is>
       </c>
       <c r="K7" s="15" t="inlineStr">
         <is>
-          <t>Topic Key</t>
+          <t>Last Update Date</t>
         </is>
       </c>
       <c r="L7" s="15" t="inlineStr">
@@ -1943,90 +1962,90 @@
           <t>Documentation</t>
         </is>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>J. Smith</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>Document A cannot be validated - missing the calibration certificate. Still waiting on the supplier.</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>J. Smith to chase the supplier for the certificate.</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="n">
         <v>46266</v>
       </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>Document A cannot be validated - missing the calibration certificate.</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>J. Smith to retrieve the missing certificate.</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>J. Smith</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="n"/>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K8" s="25">
-        <f>IF($B8="","",$B8&amp;"|"&amp;$C8)</f>
-        <v/>
-      </c>
-      <c r="L8" s="25">
-        <f>IF($B8="","",IF(AND($I8&lt;&gt;"Closed",$I8&lt;&gt;"Cancelled",$H8&lt;&gt;"",$H8&lt;TODAY()),"Yes","No"))</f>
+      <c r="K8" s="16" t="n">
+        <v>46296</v>
+      </c>
+      <c r="L8" s="20">
+        <f>IF($B8="","",IF(AND($H8&lt;&gt;"Closed",$H8&lt;&gt;"Cancelled",$G8&lt;&gt;"",$G8&lt;TODAY()),"Yes","No"))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="50" customHeight="1">
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing / Results</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Documentation</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="n">
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>A. Brown</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>First functional test results reviewed.</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>A. Brown to issue the test report.</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>46315</v>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="n">
         <v>46296</v>
       </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>Still waiting on the calibration certificate from the supplier.</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>J. Smith to chase the supplier.</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>J. Smith</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="n"/>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K9" s="25">
-        <f>IF($B9="","",$B9&amp;"|"&amp;$C9)</f>
-        <v/>
-      </c>
-      <c r="L9" s="25">
-        <f>IF($B9="","",IF(AND($I9&lt;&gt;"Closed",$I9&lt;&gt;"Cancelled",$H9&lt;&gt;"",$H9&lt;TODAY()),"Yes","No"))</f>
+      <c r="K9" s="16" t="n">
+        <v>46296</v>
+      </c>
+      <c r="L9" s="20">
+        <f>IF($B9="","",IF(AND($H9&lt;&gt;"Closed",$H9&lt;&gt;"Cancelled",$G9&lt;&gt;"",$G9&lt;TODAY()),"Yes","No"))</f>
         <v/>
       </c>
     </row>
@@ -2041,127 +2060,75 @@
           <t>Design / Engineering</t>
         </is>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>R. Taylor</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>SSOW draft submitted for review.</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>R. Taylor to review and approve the SSOW.</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>46285</v>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="n">
         <v>46266</v>
       </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>SSOW draft submitted for review.</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>R. Taylor to review and approve the SSOW.</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>R. Taylor</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="n">
-        <v>46285</v>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="J10" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K10" s="25">
-        <f>IF($B10="","",$B10&amp;"|"&amp;$C10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="25">
-        <f>IF($B10="","",IF(AND($I10&lt;&gt;"Closed",$I10&lt;&gt;"Cancelled",$H10&lt;&gt;"",$H10&lt;TODAY()),"Yes","No"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Testing / Results</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>Testing</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>46296</v>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>First functional test results reviewed.</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>A. Brown to issue the test report.</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>A. Brown</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="n">
-        <v>46315</v>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K11" s="25">
-        <f>IF($B11="","",$B11&amp;"|"&amp;$C11)</f>
-        <v/>
-      </c>
-      <c r="L11" s="25">
-        <f>IF($B11="","",IF(AND($I11&lt;&gt;"Closed",$I11&lt;&gt;"Cancelled",$H11&lt;&gt;"",$H11&lt;TODAY()),"Yes","No"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="24" t="inlineStr">
+      <c r="K10" s="16" t="n">
+        <v>46266</v>
+      </c>
+      <c r="L10" s="20">
+        <f>IF($B10="","",IF(AND($H10&lt;&gt;"Closed",$H10&lt;&gt;"Cancelled",$G10&lt;&gt;"",$G10&lt;TODAY()),"Yes","No"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>Legend: Blue = fill in yourself | Black = automatic, do not overtype | Grey columns = automation helpers, leave untouched | New row: type directly below the table and Excel extends it automatically</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B8:L11">
+  <conditionalFormatting sqref="B8:L10">
     <cfRule type="expression" priority="1" dxfId="1">
-      <formula>AND($I8&lt;&gt;"Closed",$L8="Yes")</formula>
+      <formula>AND($H8&lt;&gt;"Closed",$L8="Yes")</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="2">
-      <formula>$I8="Closed"</formula>
+      <formula>$H8="Closed"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="3">
-      <formula>OR($I8="On Hold",$I8="Cancelled")</formula>
+      <formula>OR($H8="On Hold",$H8="Cancelled")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="B8:B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B8:B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LIST_SUBJECT</formula1>
     </dataValidation>
-    <dataValidation sqref="C8:C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C8:C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LIST_SUBTOPIC</formula1>
     </dataValidation>
-    <dataValidation sqref="I8:I11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H8:H10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LIST_STATUS</formula1>
     </dataValidation>
-    <dataValidation sqref="J8:J11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I8:I10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=LIST_PRIORITY</formula1>
     </dataValidation>
   </dataValidations>
@@ -2170,15 +2137,189 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:K10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Meeting Log</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Meeting Report</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Lists &amp; Config</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>When a topic in Meeting Log is finished, copy its row here yourself for the permanent record, then delete it from Meeting Log if you like. Purely manual - nothing here is read automatically by Overview or Meeting Report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Sub-topic</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Discussion / Notes</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Agreed Action</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>Due Date</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t>Added Date</t>
+        </is>
+      </c>
+      <c r="K7" s="15" t="inlineStr">
+        <is>
+          <t>Last Update Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Design / Engineering</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>R. Taylor</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>Example only - paste a finished topic's row here.</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>SSOW approved and filed.</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="n"/>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I8" s="17" t="n"/>
+      <c r="J8" s="17" t="n"/>
+      <c r="K8" s="17" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>Legend: Blue = fill in yourself | Black = automatic, do not overtype | Grey columns = automation helpers, leave untouched | New row: type directly below the table and Excel extends it automatically</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId5"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2208,12 +2349,17 @@
           <t>Meeting Log</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Meeting Report</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Lists &amp; Config</t>
         </is>
@@ -2239,7 +2385,7 @@
           <t>Meeting Date:</t>
         </is>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="25">
         <f>'Overview'!$C$5</f>
         <v/>
       </c>
@@ -2248,7 +2394,7 @@
           <t>Meeting Type:</t>
         </is>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="26">
         <f>IFERROR(INDEX(Attendees_Log[Meeting Type],MATCH($C$5,Attendees_Log[Meeting Date],0)),"")</f>
         <v/>
       </c>
@@ -2259,7 +2405,7 @@
           <t>Attendees:</t>
         </is>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="27">
         <f>IFERROR(INDEX(Attendees_Log[Attendees],MATCH($C$5,Attendees_Log[Meeting Date],0)),"")</f>
         <v/>
       </c>
@@ -2310,209 +2456,209 @@
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="B10" s="20">
-        <f t="array" ref="B10">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="B10">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="C10" s="20">
-        <f t="array" ref="C10">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="C10">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="D10" s="20">
-        <f t="array" ref="D10">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="D10">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="E10" s="20">
-        <f t="array" ref="E10">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="E10">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="F10" s="20">
-        <f t="array" ref="F10">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="F10">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="G10" s="20">
-        <f t="array" ref="G10">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="G10">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="B11" s="22">
-        <f t="array" ref="B11">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="B11">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="C11" s="22">
-        <f t="array" ref="C11">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="C11">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="D11" s="22">
-        <f t="array" ref="D11">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="D11">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="E11" s="22">
-        <f t="array" ref="E11">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="E11">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="F11" s="22">
-        <f t="array" ref="F11">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="F11">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="G11" s="22">
-        <f t="array" ref="G11">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="G11">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="B12" s="20">
-        <f t="array" ref="B12">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="B12">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="C12" s="20">
-        <f t="array" ref="C12">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="C12">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="D12" s="20">
-        <f t="array" ref="D12">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="D12">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="E12" s="20">
-        <f t="array" ref="E12">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="E12">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="F12" s="20">
-        <f t="array" ref="F12">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="F12">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="G12" s="20">
-        <f t="array" ref="G12">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="G12">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="B13" s="22">
-        <f t="array" ref="B13">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="B13">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="C13" s="22">
-        <f t="array" ref="C13">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="C13">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="D13" s="22">
-        <f t="array" ref="D13">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="D13">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="E13" s="22">
-        <f t="array" ref="E13">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="E13">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="F13" s="22">
-        <f t="array" ref="F13">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="F13">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="G13" s="22">
-        <f t="array" ref="G13">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="G13">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="B14" s="20">
-        <f t="array" ref="B14">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="B14">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="C14" s="20">
-        <f t="array" ref="C14">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="C14">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="D14" s="20">
-        <f t="array" ref="D14">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="D14">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="E14" s="20">
-        <f t="array" ref="E14">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="E14">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="F14" s="20">
-        <f t="array" ref="F14">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="F14">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="G14" s="20">
-        <f t="array" ref="G14">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="G14">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="B15" s="22">
-        <f t="array" ref="B15">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="B15">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="C15" s="22">
-        <f t="array" ref="C15">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="C15">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="D15" s="22">
-        <f t="array" ref="D15">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="D15">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="E15" s="22">
-        <f t="array" ref="E15">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="E15">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="F15" s="22">
-        <f t="array" ref="F15">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="F15">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="G15" s="22">
-        <f t="array" ref="G15">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="G15">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="B16" s="20">
-        <f t="array" ref="B16">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="B16">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="C16" s="20">
-        <f t="array" ref="C16">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="C16">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="D16" s="20">
-        <f t="array" ref="D16">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="D16">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="E16" s="20">
-        <f t="array" ref="E16">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="E16">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="F16" s="20">
-        <f t="array" ref="F16">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="F16">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="G16" s="20">
-        <f t="array" ref="G16">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="G16">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="B17" s="22">
-        <f t="array" ref="B17">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="B17">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="C17" s="22">
-        <f t="array" ref="C17">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="C17">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="D17" s="22">
-        <f t="array" ref="D17">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="D17">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="E17" s="22">
-        <f t="array" ref="E17">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="E17">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="F17" s="22">
-        <f t="array" ref="F17">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="F17">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="G17" s="22">
-        <f t="array" ref="G17">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled"),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="G17">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Last Update Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
     </row>
@@ -2568,188 +2714,188 @@
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="B21" s="20">
-        <f t="array" ref="B21">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="B21">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="C21" s="20">
-        <f t="array" ref="C21">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="C21">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="D21" s="20">
-        <f t="array" ref="D21">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="D21">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="E21" s="20">
-        <f t="array" ref="E21">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="E21">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="F21" s="20">
-        <f t="array" ref="F21">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="F21">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="G21" s="21">
-        <f t="array" ref="G21">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="G21">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="H21" s="20">
-        <f t="array" ref="H21">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="H21">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="B22" s="22">
-        <f t="array" ref="B22">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="B22">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="C22" s="22">
-        <f t="array" ref="C22">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="C22">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="D22" s="22">
-        <f t="array" ref="D22">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="D22">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="E22" s="22">
-        <f t="array" ref="E22">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="E22">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="F22" s="22">
-        <f t="array" ref="F22">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="F22">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="G22" s="23">
-        <f t="array" ref="G22">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="G22">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="H22" s="22">
-        <f t="array" ref="H22">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="H22">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="B23" s="20">
-        <f t="array" ref="B23">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="B23">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="C23" s="20">
-        <f t="array" ref="C23">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="C23">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="D23" s="20">
-        <f t="array" ref="D23">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="D23">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="E23" s="20">
-        <f t="array" ref="E23">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="E23">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="F23" s="20">
-        <f t="array" ref="F23">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="F23">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="G23" s="21">
-        <f t="array" ref="G23">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="G23">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="H23" s="20">
-        <f t="array" ref="H23">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="H23">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="B24" s="22">
-        <f t="array" ref="B24">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="B24">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="C24" s="22">
-        <f t="array" ref="C24">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="C24">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="D24" s="22">
-        <f t="array" ref="D24">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="D24">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="E24" s="22">
-        <f t="array" ref="E24">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="E24">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="F24" s="22">
-        <f t="array" ref="F24">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="F24">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="G24" s="23">
-        <f t="array" ref="G24">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="G24">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="H24" s="22">
-        <f t="array" ref="H24">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="H24">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="B25" s="20">
-        <f t="array" ref="B25">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="B25">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="C25" s="20">
-        <f t="array" ref="C25">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="C25">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="D25" s="20">
-        <f t="array" ref="D25">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="D25">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="E25" s="20">
-        <f t="array" ref="E25">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="E25">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="F25" s="20">
-        <f t="array" ref="F25">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="F25">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="G25" s="21">
-        <f t="array" ref="G25">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="G25">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="H25" s="20">
-        <f t="array" ref="H25">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="H25">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="B26" s="22">
-        <f t="array" ref="B26">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="B26">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="C26" s="22">
-        <f t="array" ref="C26">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="C26">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="D26" s="22">
-        <f t="array" ref="D26">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="D26">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="E26" s="22">
-        <f t="array" ref="E26">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="E26">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="F26" s="22">
-        <f t="array" ref="F26">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="F26">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="G26" s="23">
-        <f t="array" ref="G26">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="G26">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="H26" s="22">
-        <f t="array" ref="H26">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5)*(COUNTIFS(Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;"&amp;$C$5)=0),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="H26">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Added Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>3. DISCUSSION LOG FOR THIS MEETING</t>
+          <t>3. DISCUSSION LOG FOR THIS MEETING (topics touched today)</t>
         </is>
       </c>
       <c r="C28" s="18" t="n"/>
@@ -2786,177 +2932,177 @@
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="B30" s="20">
-        <f t="array" ref="B30">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="B30">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="C30" s="20">
-        <f t="array" ref="C30">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="C30">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="D30" s="20">
-        <f t="array" ref="D30">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="D30">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="E30" s="20">
-        <f t="array" ref="E30">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="E30">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="F30" s="20">
-        <f t="array" ref="F30">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="F30">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="B31" s="22">
-        <f t="array" ref="B31">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="B31">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="C31" s="22">
-        <f t="array" ref="C31">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="C31">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="D31" s="22">
-        <f t="array" ref="D31">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="D31">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="E31" s="22">
-        <f t="array" ref="E31">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="E31">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="F31" s="22">
-        <f t="array" ref="F31">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="F31">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="B32" s="20">
-        <f t="array" ref="B32">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="B32">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="C32" s="20">
-        <f t="array" ref="C32">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="C32">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="D32" s="20">
-        <f t="array" ref="D32">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="D32">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="E32" s="20">
-        <f t="array" ref="E32">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="E32">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="F32" s="20">
-        <f t="array" ref="F32">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="F32">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="B33" s="22">
-        <f t="array" ref="B33">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="B33">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="C33" s="22">
-        <f t="array" ref="C33">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="C33">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="D33" s="22">
-        <f t="array" ref="D33">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="D33">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="E33" s="22">
-        <f t="array" ref="E33">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="E33">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="F33" s="22">
-        <f t="array" ref="F33">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="F33">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="B34" s="20">
-        <f t="array" ref="B34">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="B34">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="C34" s="20">
-        <f t="array" ref="C34">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="C34">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="D34" s="20">
-        <f t="array" ref="D34">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="D34">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="E34" s="20">
-        <f t="array" ref="E34">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="E34">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="F34" s="20">
-        <f t="array" ref="F34">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="F34">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="B35" s="22">
-        <f t="array" ref="B35">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="B35">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="C35" s="22">
-        <f t="array" ref="C35">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="C35">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="D35" s="22">
-        <f t="array" ref="D35">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="D35">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="E35" s="22">
-        <f t="array" ref="E35">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="E35">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="F35" s="22">
-        <f t="array" ref="F35">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="F35">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="B36" s="20">
-        <f t="array" ref="B36">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="B36">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="C36" s="20">
-        <f t="array" ref="C36">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="C36">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="D36" s="20">
-        <f t="array" ref="D36">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="D36">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="E36" s="20">
-        <f t="array" ref="E36">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="E36">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="F36" s="20">
-        <f t="array" ref="F36">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="F36">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="B37" s="22">
-        <f t="array" ref="B37">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="B37">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="C37" s="22">
-        <f t="array" ref="C37">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="C37">IFERROR(INDEX(Meeting_Log[Sub-topic],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="D37" s="22">
-        <f t="array" ref="D37">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="D37">IFERROR(INDEX(Meeting_Log[Discussion / Notes],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="E37" s="22">
-        <f t="array" ref="E37">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="E37">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="F37" s="22">
-        <f t="array" ref="F37">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]=$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="F37">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Last Update Date]=$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
     </row>
@@ -3000,177 +3146,177 @@
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="B41" s="20">
-        <f t="array" ref="B41">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="B41">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="C41" s="20">
-        <f t="array" ref="C41">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="C41">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="D41" s="20">
-        <f t="array" ref="D41">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="D41">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="E41" s="21">
-        <f t="array" ref="E41">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="E41">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
       <c r="F41" s="20">
-        <f t="array" ref="F41">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),1)),"")</f>
+        <f t="array" ref="F41">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),1)),"")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="B42" s="22">
-        <f t="array" ref="B42">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="B42">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="C42" s="22">
-        <f t="array" ref="C42">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="C42">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f t="array" ref="D42">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="D42">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f t="array" ref="E42">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="E42">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f t="array" ref="F42">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),2)),"")</f>
+        <f t="array" ref="F42">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),2)),"")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="B43" s="20">
-        <f t="array" ref="B43">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="B43">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="C43" s="20">
-        <f t="array" ref="C43">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="C43">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="D43" s="20">
-        <f t="array" ref="D43">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="D43">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="E43" s="21">
-        <f t="array" ref="E43">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="E43">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
       <c r="F43" s="20">
-        <f t="array" ref="F43">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),3)),"")</f>
+        <f t="array" ref="F43">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),3)),"")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="B44" s="22">
-        <f t="array" ref="B44">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="B44">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="C44" s="22">
-        <f t="array" ref="C44">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="C44">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f t="array" ref="D44">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="D44">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="E44" s="23">
-        <f t="array" ref="E44">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="E44">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f t="array" ref="F44">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),4)),"")</f>
+        <f t="array" ref="F44">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),4)),"")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="B45" s="20">
-        <f t="array" ref="B45">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="B45">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="C45" s="20">
-        <f t="array" ref="C45">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="C45">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="D45" s="20">
-        <f t="array" ref="D45">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="D45">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="E45" s="21">
-        <f t="array" ref="E45">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="E45">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
       <c r="F45" s="20">
-        <f t="array" ref="F45">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),5)),"")</f>
+        <f t="array" ref="F45">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),5)),"")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="B46" s="22">
-        <f t="array" ref="B46">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="B46">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="C46" s="22">
-        <f t="array" ref="C46">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="C46">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="D46" s="22">
-        <f t="array" ref="D46">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="D46">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="E46" s="23">
-        <f t="array" ref="E46">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="E46">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
       <c r="F46" s="22">
-        <f t="array" ref="F46">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),6)),"")</f>
+        <f t="array" ref="F46">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),6)),"")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="B47" s="20">
-        <f t="array" ref="B47">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="B47">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="C47" s="20">
-        <f t="array" ref="C47">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="C47">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="D47" s="20">
-        <f t="array" ref="D47">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="D47">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="E47" s="21">
-        <f t="array" ref="E47">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="E47">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
       <c r="F47" s="20">
-        <f t="array" ref="F47">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),7)),"")</f>
+        <f t="array" ref="F47">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),7)),"")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="26" customHeight="1">
       <c r="B48" s="22">
-        <f t="array" ref="B48">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="B48">IFERROR(INDEX(Meeting_Log[Subject],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="C48" s="22">
-        <f t="array" ref="C48">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="C48">IFERROR(INDEX(Meeting_Log[Agreed Action],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="D48" s="22">
-        <f t="array" ref="D48">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="D48">IFERROR(INDEX(Meeting_Log[Owner],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="E48" s="23">
-        <f t="array" ref="E48">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="E48">IFERROR(INDEX(Meeting_Log[Due Date],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
       <c r="F48" s="22">
-        <f t="array" ref="F48">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Topic Key]&lt;&gt;"")*(Meeting_Log[Meeting Date]&lt;=$C$5)*(Meeting_Log[Meeting Date]=_xlfn.MAXIFS(Meeting_Log[Meeting Date],Meeting_Log[Topic Key],Meeting_Log[Topic Key],Meeting_Log[Meeting Date],"&lt;="&amp;$C$5))*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Topic Key])-7),8)),"")</f>
+        <f t="array" ref="F48">IFERROR(INDEX(Meeting_Log[Status],SMALL(IF((Meeting_Log[Subject]&lt;&gt;"")*(Meeting_Log[Status]&lt;&gt;"Closed")*(Meeting_Log[Status]&lt;&gt;"Cancelled")*(Meeting_Log[Due Date]&lt;&gt;"")*(Meeting_Log[Due Date]&lt;$C$5),ROW(Meeting_Log[Subject])-7),8)),"")</f>
         <v/>
       </c>
     </row>
@@ -3190,12 +3336,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3225,10 +3372,15 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Meeting Report</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lists &amp; Config</t>
         </is>
@@ -3249,247 +3401,247 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>Sub-topic</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="F5" s="29" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>Meeting Type</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Commissioning Planning</t>
         </is>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>Planning</t>
         </is>
       </c>
-      <c r="D6" s="30" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="E6" s="30" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F6" s="30" t="inlineStr">
+      <c r="F6" s="29" t="inlineStr">
         <is>
           <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Site / Field Activities</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
-      <c r="D7" s="31" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F7" s="31" t="inlineStr">
+      <c r="F7" s="30" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Preparation</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="F8" s="29" t="inlineStr">
         <is>
           <t>Ad hoc</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Testing / Results</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>Execution</t>
         </is>
       </c>
-      <c r="D9" s="31" t="inlineStr">
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>On Hold</t>
         </is>
       </c>
-      <c r="E9" s="31" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>Interfaces</t>
         </is>
       </c>
-      <c r="C10" s="30" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
-      <c r="D10" s="30" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>Cancelled</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="31" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>Punch List</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
-      <c r="C12" s="30" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Documentation</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>NCR / Quality</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Resources / Manpower</t>
         </is>
       </c>
-      <c r="C14" s="30" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>Design / Engineering</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="31" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="C15" s="31" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
         <is>
           <t>Interface</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C16" s="30" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>Resource</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="31" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="30" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>Risk / Issue</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="31" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="30" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -3508,6 +3660,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/HBX Commissioning Review.xlsx
+++ b/HBX Commissioning Review.xlsx
@@ -9,8 +9,13 @@
   <sheets>
     <sheet name="Meeting Log" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Overview" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Lists &amp; Config" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="LIST_SUJET">'Lists &amp; Config'!$B$6:$B$14</definedName>
+    <definedName name="LIST_SOUS_SUJET">'Lists &amp; Config'!$C$6:$C$11</definedName>
+    <definedName name="LIST_RESPONSABLE">'Lists &amp; Config'!$D$6:$D$8</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +26,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd-mmm-yy"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,15 +36,15 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00BFD3F2"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00BFD3F2"/>
-      <sz val="9"/>
-      <u val="single"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -56,6 +61,23 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001A1A1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="10"/>
     </font>
@@ -63,12 +85,6 @@
       <name val="Arial"/>
       <color rgb="001155CC"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00595959"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -112,11 +128,6 @@
       <color rgb="0044546A"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="001A1A1A"/>
-      <sz val="10"/>
-    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -127,12 +138,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="003B6EC4"/>
+        <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="003B6EC4"/>
       </patternFill>
     </fill>
     <fill>
@@ -177,19 +188,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -198,38 +236,20 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -679,6 +699,11 @@
           <t>Overview</t>
         </is>
       </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Lists &amp; Config</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="3" t="inlineStr">
@@ -690,7 +715,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>The only sheet you type into. One row per action. If a subject comes back at a later meeting, just add a new row below - don't edit an old one. Status is the one thing to keep current: set it to Closed once an action is done, so it drops off Overview automatically.</t>
+          <t>The only sheet you type into. One row per action - pick Sujet/Sous-sujet/Responsable from the dropdowns (edit the lists on Lists &amp; Config), free-type the rest. If a subject comes back at a later meeting, just add a new row below - don't edit an old one. Status is the one thing to keep current: set it to Closed once an action is done, so it drops off Overview automatically.</t>
         </is>
       </c>
     </row>
@@ -910,7 +935,16 @@
       <formula>$H8="Closed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations count="4">
+    <dataValidation sqref="B8:B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=LIST_SUJET</formula1>
+    </dataValidation>
+    <dataValidation sqref="C8:C12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=LIST_SOUS_SUJET</formula1>
+    </dataValidation>
+    <dataValidation sqref="F8:F12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=LIST_RESPONSABLE</formula1>
+    </dataValidation>
     <dataValidation sqref="H8:H12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,Closed"</formula1>
     </dataValidation>
@@ -918,10 +952,11 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
@@ -959,6 +994,11 @@
           <t>Overview</t>
         </is>
       </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Lists &amp; Config</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="3" t="inlineStr">
@@ -1455,6 +1495,205 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.5" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Meeting Log</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Lists &amp; Config</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Lists &amp; Config</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Dropdown values used on Meeting Log. Add or remove values here - every dropdown updates automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>Sujet</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>Sous-sujet</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Commissioning Dossier</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>John Smith</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>Test Reports</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>Sarah Williams</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>SSOW Approval</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>Robert Taylor</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Commissioning Planning</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>Interfaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Legend: Blue = fill in yourself | Black = automatic | New row: type directly below the table and Excel extends it automatically</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Add more Subjects/Sub-topics/People any time - just type a new value in the next blank cell in that column.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:H3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
